--- a/builder/travel-template.xlsx
+++ b/builder/travel-template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="457">
   <si>
     <t>旅遊網站資料模板</t>
   </si>
@@ -681,6 +681,12 @@
     <t>同一格裡換行，網站上就會分段。</t>
   </si>
   <si>
+    <t>打包清單的「連結」欄</t>
+  </si>
+  <si>
+    <t>待辦事項如果要連到某個網站（例如線上填寫入境手續），把網址填在這一欄，網站上該項目旁邊會多一顆「開啟」。留空就是一般的勾選項目。</t>
+  </si>
+  <si>
     <t>項目</t>
   </si>
   <si>
@@ -1804,6 +1810,9 @@
     <t>分類</t>
   </si>
   <si>
+    <t>連結</t>
+  </si>
+  <si>
     <t>出發前準備</t>
   </si>
   <si>
@@ -1814,6 +1823,9 @@
   </si>
   <si>
     <t>線上申辦入境卡</t>
+  </si>
+  <si>
+    <t>https://services.digital.go.jp/zh-cmn-hant/visit-japan-web/</t>
   </si>
   <si>
     <r>
@@ -2402,7 +2414,7 @@
   <sheetPr>
     <tabColor rgb="FF154570"/>
   </sheetPr>
-  <dimension ref="A2:D105"/>
+  <dimension ref="A2:D108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
@@ -3176,6 +3188,16 @@
     <row r="105" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C105" s="13" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C108" s="13" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3204,46 +3226,46 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3251,101 +3273,101 @@
         <v>108</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B9" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="24" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="24" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3354,7 +3376,7 @@
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3363,7 +3385,7 @@
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3397,40 +3419,40 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B7" s="24"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B8" s="24"/>
     </row>
@@ -3464,44 +3486,43 @@
     <col min="14" max="14" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" ht="19.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="11:11" x14ac:dyDescent="0.25"/>
+        <v>216</v>
+      </c>
+    </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>163</v>
@@ -3510,13 +3531,13 @@
         <v>165</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3524,40 +3545,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C5" s="26">
         <v>20</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3574,15 +3595,15 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
@@ -3600,13 +3621,13 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
@@ -3626,17 +3647,17 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
@@ -3656,15 +3677,15 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
@@ -3682,13 +3703,13 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -3708,13 +3729,13 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -3734,17 +3755,17 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
@@ -3764,25 +3785,25 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N13" s="13" t="s">
         <v>77</v>
@@ -3800,23 +3821,23 @@
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N14" s="13" t="s">
         <v>77</v>
@@ -3827,25 +3848,25 @@
         <v>2</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C15" s="26">
         <v>12</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
@@ -3863,13 +3884,13 @@
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -3889,17 +3910,17 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
@@ -3917,17 +3938,17 @@
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
@@ -3947,26 +3968,26 @@
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>77</v>
@@ -3986,24 +4007,24 @@
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -4020,24 +4041,24 @@
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N21" s="13" t="s">
         <v>77</v>
@@ -4060,11 +4081,11 @@
         <v>57</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J22" s="13"/>
       <c r="L22" s="13"/>
@@ -4083,21 +4104,21 @@
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="L23" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>77</v>
@@ -4115,21 +4136,21 @@
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="L24" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>77</v>
@@ -4149,25 +4170,25 @@
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N25" s="13" t="s">
         <v>77</v>
@@ -4187,23 +4208,23 @@
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>77</v>
@@ -4221,20 +4242,20 @@
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="28" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="L27" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -4242,27 +4263,27 @@
         <v>3</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C28" s="26">
         <v>150</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
@@ -4282,25 +4303,25 @@
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>80</v>
@@ -4320,17 +4341,17 @@
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="15" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
@@ -4350,15 +4371,15 @@
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
@@ -4378,25 +4399,25 @@
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="I32" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="G32" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>248</v>
-      </c>
       <c r="J32" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N32" s="13" t="s">
         <v>77</v>
@@ -4407,31 +4428,31 @@
         <v>4</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C33" s="26">
         <v>90</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
@@ -4451,15 +4472,15 @@
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
@@ -4477,13 +4498,13 @@
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
@@ -4503,17 +4524,17 @@
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
@@ -4533,23 +4554,23 @@
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J37" s="13"/>
       <c r="L37" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N37" s="13" t="s">
         <v>77</v>
@@ -4569,19 +4590,19 @@
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
@@ -4599,25 +4620,25 @@
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N39" s="13" t="s">
         <v>71</v>
@@ -4628,35 +4649,35 @@
         <v>5</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C40" s="26">
         <v>75</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N40" s="13" t="s">
         <v>77</v>
@@ -4676,15 +4697,15 @@
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
@@ -4702,13 +4723,13 @@
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
@@ -4728,17 +4749,17 @@
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L43" s="13"/>
       <c r="M43" s="13"/>
@@ -4758,19 +4779,19 @@
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
@@ -4790,19 +4811,19 @@
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
@@ -4813,35 +4834,35 @@
         <v>6</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C46" s="26">
         <v>180</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N46" s="13" t="s">
         <v>77</v>
@@ -4861,15 +4882,15 @@
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="13" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
@@ -4887,13 +4908,13 @@
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
@@ -4913,13 +4934,13 @@
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H49" s="15" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
@@ -4939,17 +4960,17 @@
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
@@ -4969,25 +4990,25 @@
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N51" s="13" t="s">
         <v>77</v>
@@ -5007,17 +5028,17 @@
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
@@ -5028,35 +5049,35 @@
         <v>7</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C53" s="26">
         <v>90</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H53" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N53" s="13" t="s">
         <v>77</v>
@@ -5076,21 +5097,21 @@
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
       <c r="J54" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N54" s="13" t="s">
         <v>80</v>
@@ -5108,13 +5129,13 @@
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H55" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
@@ -5134,17 +5155,17 @@
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
@@ -5164,17 +5185,17 @@
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
@@ -5860,1819 +5881,1819 @@
       <c r="M97" s="30"/>
       <c r="N97" s="30"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C98" s="33"/>
       <c r="D98" s="34">
         <f>IF($A98&lt;&gt;$A97,"",IFERROR(TEXT(TIMEVALUE($D97)+IF($C97="",0,$C97)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C99" s="33"/>
       <c r="D99" s="34">
         <f>IF($A99&lt;&gt;$A98,"",IFERROR(TEXT(TIMEVALUE($D98)+IF($C98="",0,$C98)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C100" s="33"/>
       <c r="D100" s="34">
         <f>IF($A100&lt;&gt;$A99,"",IFERROR(TEXT(TIMEVALUE($D99)+IF($C99="",0,$C99)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C101" s="33"/>
       <c r="D101" s="34">
         <f>IF($A101&lt;&gt;$A100,"",IFERROR(TEXT(TIMEVALUE($D100)+IF($C100="",0,$C100)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C102" s="33"/>
       <c r="D102" s="34">
         <f>IF($A102&lt;&gt;$A101,"",IFERROR(TEXT(TIMEVALUE($D101)+IF($C101="",0,$C101)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C103" s="33"/>
       <c r="D103" s="34">
         <f>IF($A103&lt;&gt;$A102,"",IFERROR(TEXT(TIMEVALUE($D102)+IF($C102="",0,$C102)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C104" s="33"/>
       <c r="D104" s="34">
         <f>IF($A104&lt;&gt;$A103,"",IFERROR(TEXT(TIMEVALUE($D103)+IF($C103="",0,$C103)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C105" s="33"/>
       <c r="D105" s="34">
         <f>IF($A105&lt;&gt;$A104,"",IFERROR(TEXT(TIMEVALUE($D104)+IF($C104="",0,$C104)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C106" s="33"/>
       <c r="D106" s="34">
         <f>IF($A106&lt;&gt;$A105,"",IFERROR(TEXT(TIMEVALUE($D105)+IF($C105="",0,$C105)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C107" s="33"/>
       <c r="D107" s="34">
         <f>IF($A107&lt;&gt;$A106,"",IFERROR(TEXT(TIMEVALUE($D106)+IF($C106="",0,$C106)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C108" s="33"/>
       <c r="D108" s="34">
         <f>IF($A108&lt;&gt;$A107,"",IFERROR(TEXT(TIMEVALUE($D107)+IF($C107="",0,$C107)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C109" s="33"/>
       <c r="D109" s="34">
         <f>IF($A109&lt;&gt;$A108,"",IFERROR(TEXT(TIMEVALUE($D108)+IF($C108="",0,$C108)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="110" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="110" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C110" s="33"/>
       <c r="D110" s="34">
         <f>IF($A110&lt;&gt;$A109,"",IFERROR(TEXT(TIMEVALUE($D109)+IF($C109="",0,$C109)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="111" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="111" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C111" s="33"/>
       <c r="D111" s="34">
         <f>IF($A111&lt;&gt;$A110,"",IFERROR(TEXT(TIMEVALUE($D110)+IF($C110="",0,$C110)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="112" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="112" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C112" s="33"/>
       <c r="D112" s="34">
         <f>IF($A112&lt;&gt;$A111,"",IFERROR(TEXT(TIMEVALUE($D111)+IF($C111="",0,$C111)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="113" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="113" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C113" s="33"/>
       <c r="D113" s="34">
         <f>IF($A113&lt;&gt;$A112,"",IFERROR(TEXT(TIMEVALUE($D112)+IF($C112="",0,$C112)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="114" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="114" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C114" s="33"/>
       <c r="D114" s="34">
         <f>IF($A114&lt;&gt;$A113,"",IFERROR(TEXT(TIMEVALUE($D113)+IF($C113="",0,$C113)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="115" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="115" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C115" s="33"/>
       <c r="D115" s="34">
         <f>IF($A115&lt;&gt;$A114,"",IFERROR(TEXT(TIMEVALUE($D114)+IF($C114="",0,$C114)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="116" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="116" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C116" s="33"/>
       <c r="D116" s="34">
         <f>IF($A116&lt;&gt;$A115,"",IFERROR(TEXT(TIMEVALUE($D115)+IF($C115="",0,$C115)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="117" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C117" s="33"/>
       <c r="D117" s="34">
         <f>IF($A117&lt;&gt;$A116,"",IFERROR(TEXT(TIMEVALUE($D116)+IF($C116="",0,$C116)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="118" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C118" s="33"/>
       <c r="D118" s="34">
         <f>IF($A118&lt;&gt;$A117,"",IFERROR(TEXT(TIMEVALUE($D117)+IF($C117="",0,$C117)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="119" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C119" s="33"/>
       <c r="D119" s="34">
         <f>IF($A119&lt;&gt;$A118,"",IFERROR(TEXT(TIMEVALUE($D118)+IF($C118="",0,$C118)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="120" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C120" s="33"/>
       <c r="D120" s="34">
         <f>IF($A120&lt;&gt;$A119,"",IFERROR(TEXT(TIMEVALUE($D119)+IF($C119="",0,$C119)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="121" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="121" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C121" s="33"/>
       <c r="D121" s="34">
         <f>IF($A121&lt;&gt;$A120,"",IFERROR(TEXT(TIMEVALUE($D120)+IF($C120="",0,$C120)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="122" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C122" s="33"/>
       <c r="D122" s="34">
         <f>IF($A122&lt;&gt;$A121,"",IFERROR(TEXT(TIMEVALUE($D121)+IF($C121="",0,$C121)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="123" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C123" s="33"/>
       <c r="D123" s="34">
         <f>IF($A123&lt;&gt;$A122,"",IFERROR(TEXT(TIMEVALUE($D122)+IF($C122="",0,$C122)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="124" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="124" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C124" s="33"/>
       <c r="D124" s="34">
         <f>IF($A124&lt;&gt;$A123,"",IFERROR(TEXT(TIMEVALUE($D123)+IF($C123="",0,$C123)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="125" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="125" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C125" s="33"/>
       <c r="D125" s="34">
         <f>IF($A125&lt;&gt;$A124,"",IFERROR(TEXT(TIMEVALUE($D124)+IF($C124="",0,$C124)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="126" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="126" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C126" s="33"/>
       <c r="D126" s="34">
         <f>IF($A126&lt;&gt;$A125,"",IFERROR(TEXT(TIMEVALUE($D125)+IF($C125="",0,$C125)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="127" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="127" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C127" s="33"/>
       <c r="D127" s="34">
         <f>IF($A127&lt;&gt;$A126,"",IFERROR(TEXT(TIMEVALUE($D126)+IF($C126="",0,$C126)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="128" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="128" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C128" s="33"/>
       <c r="D128" s="34">
         <f>IF($A128&lt;&gt;$A127,"",IFERROR(TEXT(TIMEVALUE($D127)+IF($C127="",0,$C127)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="129" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="129" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C129" s="33"/>
       <c r="D129" s="34">
         <f>IF($A129&lt;&gt;$A128,"",IFERROR(TEXT(TIMEVALUE($D128)+IF($C128="",0,$C128)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="130" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C130" s="33"/>
       <c r="D130" s="34">
         <f>IF($A130&lt;&gt;$A129,"",IFERROR(TEXT(TIMEVALUE($D129)+IF($C129="",0,$C129)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="131" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="131" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C131" s="33"/>
       <c r="D131" s="34">
         <f>IF($A131&lt;&gt;$A130,"",IFERROR(TEXT(TIMEVALUE($D130)+IF($C130="",0,$C130)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="132" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="132" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C132" s="33"/>
       <c r="D132" s="34">
         <f>IF($A132&lt;&gt;$A131,"",IFERROR(TEXT(TIMEVALUE($D131)+IF($C131="",0,$C131)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C133" s="33"/>
       <c r="D133" s="34">
         <f>IF($A133&lt;&gt;$A132,"",IFERROR(TEXT(TIMEVALUE($D132)+IF($C132="",0,$C132)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="134" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C134" s="33"/>
       <c r="D134" s="34">
         <f>IF($A134&lt;&gt;$A133,"",IFERROR(TEXT(TIMEVALUE($D133)+IF($C133="",0,$C133)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="135" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="135" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C135" s="33"/>
       <c r="D135" s="34">
         <f>IF($A135&lt;&gt;$A134,"",IFERROR(TEXT(TIMEVALUE($D134)+IF($C134="",0,$C134)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="136" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="136" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C136" s="33"/>
       <c r="D136" s="34">
         <f>IF($A136&lt;&gt;$A135,"",IFERROR(TEXT(TIMEVALUE($D135)+IF($C135="",0,$C135)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="137" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="137" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C137" s="33"/>
       <c r="D137" s="34">
         <f>IF($A137&lt;&gt;$A136,"",IFERROR(TEXT(TIMEVALUE($D136)+IF($C136="",0,$C136)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="138" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="138" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C138" s="33"/>
       <c r="D138" s="34">
         <f>IF($A138&lt;&gt;$A137,"",IFERROR(TEXT(TIMEVALUE($D137)+IF($C137="",0,$C137)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="139" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C139" s="33"/>
       <c r="D139" s="34">
         <f>IF($A139&lt;&gt;$A138,"",IFERROR(TEXT(TIMEVALUE($D138)+IF($C138="",0,$C138)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="140" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="140" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C140" s="33"/>
       <c r="D140" s="34">
         <f>IF($A140&lt;&gt;$A139,"",IFERROR(TEXT(TIMEVALUE($D139)+IF($C139="",0,$C139)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="141" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="141" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C141" s="33"/>
       <c r="D141" s="34">
         <f>IF($A141&lt;&gt;$A140,"",IFERROR(TEXT(TIMEVALUE($D140)+IF($C140="",0,$C140)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="142" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="142" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C142" s="33"/>
       <c r="D142" s="34">
         <f>IF($A142&lt;&gt;$A141,"",IFERROR(TEXT(TIMEVALUE($D141)+IF($C141="",0,$C141)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="143" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="143" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C143" s="33"/>
       <c r="D143" s="34">
         <f>IF($A143&lt;&gt;$A142,"",IFERROR(TEXT(TIMEVALUE($D142)+IF($C142="",0,$C142)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="144" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="144" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C144" s="33"/>
       <c r="D144" s="34">
         <f>IF($A144&lt;&gt;$A143,"",IFERROR(TEXT(TIMEVALUE($D143)+IF($C143="",0,$C143)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="145" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="145" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C145" s="33"/>
       <c r="D145" s="34">
         <f>IF($A145&lt;&gt;$A144,"",IFERROR(TEXT(TIMEVALUE($D144)+IF($C144="",0,$C144)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="146" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="146" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C146" s="33"/>
       <c r="D146" s="34">
         <f>IF($A146&lt;&gt;$A145,"",IFERROR(TEXT(TIMEVALUE($D145)+IF($C145="",0,$C145)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="147" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="147" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C147" s="33"/>
       <c r="D147" s="34">
         <f>IF($A147&lt;&gt;$A146,"",IFERROR(TEXT(TIMEVALUE($D146)+IF($C146="",0,$C146)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="148" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="148" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C148" s="33"/>
       <c r="D148" s="34">
         <f>IF($A148&lt;&gt;$A147,"",IFERROR(TEXT(TIMEVALUE($D147)+IF($C147="",0,$C147)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="149" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C149" s="33"/>
       <c r="D149" s="34">
         <f>IF($A149&lt;&gt;$A148,"",IFERROR(TEXT(TIMEVALUE($D148)+IF($C148="",0,$C148)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="150" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="150" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C150" s="33"/>
       <c r="D150" s="34">
         <f>IF($A150&lt;&gt;$A149,"",IFERROR(TEXT(TIMEVALUE($D149)+IF($C149="",0,$C149)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="151" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C151" s="33"/>
       <c r="D151" s="34">
         <f>IF($A151&lt;&gt;$A150,"",IFERROR(TEXT(TIMEVALUE($D150)+IF($C150="",0,$C150)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="152" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="152" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C152" s="33"/>
       <c r="D152" s="34">
         <f>IF($A152&lt;&gt;$A151,"",IFERROR(TEXT(TIMEVALUE($D151)+IF($C151="",0,$C151)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="153" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="153" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C153" s="33"/>
       <c r="D153" s="34">
         <f>IF($A153&lt;&gt;$A152,"",IFERROR(TEXT(TIMEVALUE($D152)+IF($C152="",0,$C152)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="154" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C154" s="33"/>
       <c r="D154" s="34">
         <f>IF($A154&lt;&gt;$A153,"",IFERROR(TEXT(TIMEVALUE($D153)+IF($C153="",0,$C153)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="155" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C155" s="33"/>
       <c r="D155" s="34">
         <f>IF($A155&lt;&gt;$A154,"",IFERROR(TEXT(TIMEVALUE($D154)+IF($C154="",0,$C154)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="156" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C156" s="33"/>
       <c r="D156" s="34">
         <f>IF($A156&lt;&gt;$A155,"",IFERROR(TEXT(TIMEVALUE($D155)+IF($C155="",0,$C155)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="157" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="157" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C157" s="33"/>
       <c r="D157" s="34">
         <f>IF($A157&lt;&gt;$A156,"",IFERROR(TEXT(TIMEVALUE($D156)+IF($C156="",0,$C156)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="158" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C158" s="33"/>
       <c r="D158" s="34">
         <f>IF($A158&lt;&gt;$A157,"",IFERROR(TEXT(TIMEVALUE($D157)+IF($C157="",0,$C157)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="159" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C159" s="33"/>
       <c r="D159" s="34">
         <f>IF($A159&lt;&gt;$A158,"",IFERROR(TEXT(TIMEVALUE($D158)+IF($C158="",0,$C158)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="160" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C160" s="33"/>
       <c r="D160" s="34">
         <f>IF($A160&lt;&gt;$A159,"",IFERROR(TEXT(TIMEVALUE($D159)+IF($C159="",0,$C159)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="161" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="161" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C161" s="33"/>
       <c r="D161" s="34">
         <f>IF($A161&lt;&gt;$A160,"",IFERROR(TEXT(TIMEVALUE($D160)+IF($C160="",0,$C160)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="162" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="162" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C162" s="33"/>
       <c r="D162" s="34">
         <f>IF($A162&lt;&gt;$A161,"",IFERROR(TEXT(TIMEVALUE($D161)+IF($C161="",0,$C161)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="163" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="163" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C163" s="33"/>
       <c r="D163" s="34">
         <f>IF($A163&lt;&gt;$A162,"",IFERROR(TEXT(TIMEVALUE($D162)+IF($C162="",0,$C162)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="164" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="164" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C164" s="33"/>
       <c r="D164" s="34">
         <f>IF($A164&lt;&gt;$A163,"",IFERROR(TEXT(TIMEVALUE($D163)+IF($C163="",0,$C163)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="165" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C165" s="33"/>
       <c r="D165" s="34">
         <f>IF($A165&lt;&gt;$A164,"",IFERROR(TEXT(TIMEVALUE($D164)+IF($C164="",0,$C164)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="166" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="166" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C166" s="33"/>
       <c r="D166" s="34">
         <f>IF($A166&lt;&gt;$A165,"",IFERROR(TEXT(TIMEVALUE($D165)+IF($C165="",0,$C165)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="167" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="167" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C167" s="33"/>
       <c r="D167" s="34">
         <f>IF($A167&lt;&gt;$A166,"",IFERROR(TEXT(TIMEVALUE($D166)+IF($C166="",0,$C166)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="168" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="168" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C168" s="33"/>
       <c r="D168" s="34">
         <f>IF($A168&lt;&gt;$A167,"",IFERROR(TEXT(TIMEVALUE($D167)+IF($C167="",0,$C167)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="169" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="169" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C169" s="33"/>
       <c r="D169" s="34">
         <f>IF($A169&lt;&gt;$A168,"",IFERROR(TEXT(TIMEVALUE($D168)+IF($C168="",0,$C168)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="170" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="170" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C170" s="33"/>
       <c r="D170" s="34">
         <f>IF($A170&lt;&gt;$A169,"",IFERROR(TEXT(TIMEVALUE($D169)+IF($C169="",0,$C169)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="171" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="171" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C171" s="33"/>
       <c r="D171" s="34">
         <f>IF($A171&lt;&gt;$A170,"",IFERROR(TEXT(TIMEVALUE($D170)+IF($C170="",0,$C170)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="172" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="172" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C172" s="33"/>
       <c r="D172" s="34">
         <f>IF($A172&lt;&gt;$A171,"",IFERROR(TEXT(TIMEVALUE($D171)+IF($C171="",0,$C171)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="173" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="173" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C173" s="33"/>
       <c r="D173" s="34">
         <f>IF($A173&lt;&gt;$A172,"",IFERROR(TEXT(TIMEVALUE($D172)+IF($C172="",0,$C172)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="174" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="174" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C174" s="33"/>
       <c r="D174" s="34">
         <f>IF($A174&lt;&gt;$A173,"",IFERROR(TEXT(TIMEVALUE($D173)+IF($C173="",0,$C173)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="175" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="175" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C175" s="33"/>
       <c r="D175" s="34">
         <f>IF($A175&lt;&gt;$A174,"",IFERROR(TEXT(TIMEVALUE($D174)+IF($C174="",0,$C174)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="176" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="176" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C176" s="33"/>
       <c r="D176" s="34">
         <f>IF($A176&lt;&gt;$A175,"",IFERROR(TEXT(TIMEVALUE($D175)+IF($C175="",0,$C175)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="177" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="177" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C177" s="33"/>
       <c r="D177" s="34">
         <f>IF($A177&lt;&gt;$A176,"",IFERROR(TEXT(TIMEVALUE($D176)+IF($C176="",0,$C176)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="178" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="178" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C178" s="33"/>
       <c r="D178" s="34">
         <f>IF($A178&lt;&gt;$A177,"",IFERROR(TEXT(TIMEVALUE($D177)+IF($C177="",0,$C177)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="179" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="179" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C179" s="33"/>
       <c r="D179" s="34">
         <f>IF($A179&lt;&gt;$A178,"",IFERROR(TEXT(TIMEVALUE($D178)+IF($C178="",0,$C178)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="180" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="180" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C180" s="33"/>
       <c r="D180" s="34">
         <f>IF($A180&lt;&gt;$A179,"",IFERROR(TEXT(TIMEVALUE($D179)+IF($C179="",0,$C179)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="181" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="181" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C181" s="33"/>
       <c r="D181" s="34">
         <f>IF($A181&lt;&gt;$A180,"",IFERROR(TEXT(TIMEVALUE($D180)+IF($C180="",0,$C180)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="182" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="182" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C182" s="33"/>
       <c r="D182" s="34">
         <f>IF($A182&lt;&gt;$A181,"",IFERROR(TEXT(TIMEVALUE($D181)+IF($C181="",0,$C181)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="183" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="183" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C183" s="33"/>
       <c r="D183" s="34">
         <f>IF($A183&lt;&gt;$A182,"",IFERROR(TEXT(TIMEVALUE($D182)+IF($C182="",0,$C182)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="184" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="184" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C184" s="33"/>
       <c r="D184" s="34">
         <f>IF($A184&lt;&gt;$A183,"",IFERROR(TEXT(TIMEVALUE($D183)+IF($C183="",0,$C183)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="185" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="185" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C185" s="33"/>
       <c r="D185" s="34">
         <f>IF($A185&lt;&gt;$A184,"",IFERROR(TEXT(TIMEVALUE($D184)+IF($C184="",0,$C184)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="186" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="186" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C186" s="33"/>
       <c r="D186" s="34">
         <f>IF($A186&lt;&gt;$A185,"",IFERROR(TEXT(TIMEVALUE($D185)+IF($C185="",0,$C185)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="187" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="187" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C187" s="33"/>
       <c r="D187" s="34">
         <f>IF($A187&lt;&gt;$A186,"",IFERROR(TEXT(TIMEVALUE($D186)+IF($C186="",0,$C186)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="188" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="188" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C188" s="33"/>
       <c r="D188" s="34">
         <f>IF($A188&lt;&gt;$A187,"",IFERROR(TEXT(TIMEVALUE($D187)+IF($C187="",0,$C187)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="189" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="189" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C189" s="33"/>
       <c r="D189" s="34">
         <f>IF($A189&lt;&gt;$A188,"",IFERROR(TEXT(TIMEVALUE($D188)+IF($C188="",0,$C188)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="190" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="190" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C190" s="33"/>
       <c r="D190" s="34">
         <f>IF($A190&lt;&gt;$A189,"",IFERROR(TEXT(TIMEVALUE($D189)+IF($C189="",0,$C189)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="191" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="191" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C191" s="33"/>
       <c r="D191" s="34">
         <f>IF($A191&lt;&gt;$A190,"",IFERROR(TEXT(TIMEVALUE($D190)+IF($C190="",0,$C190)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="192" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="192" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C192" s="33"/>
       <c r="D192" s="34">
         <f>IF($A192&lt;&gt;$A191,"",IFERROR(TEXT(TIMEVALUE($D191)+IF($C191="",0,$C191)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="193" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="193" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C193" s="33"/>
       <c r="D193" s="34">
         <f>IF($A193&lt;&gt;$A192,"",IFERROR(TEXT(TIMEVALUE($D192)+IF($C192="",0,$C192)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="194" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="194" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C194" s="33"/>
       <c r="D194" s="34">
         <f>IF($A194&lt;&gt;$A193,"",IFERROR(TEXT(TIMEVALUE($D193)+IF($C193="",0,$C193)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="195" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="195" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C195" s="33"/>
       <c r="D195" s="34">
         <f>IF($A195&lt;&gt;$A194,"",IFERROR(TEXT(TIMEVALUE($D194)+IF($C194="",0,$C194)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="196" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="196" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C196" s="33"/>
       <c r="D196" s="34">
         <f>IF($A196&lt;&gt;$A195,"",IFERROR(TEXT(TIMEVALUE($D195)+IF($C195="",0,$C195)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="197" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="197" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C197" s="33"/>
       <c r="D197" s="34">
         <f>IF($A197&lt;&gt;$A196,"",IFERROR(TEXT(TIMEVALUE($D196)+IF($C196="",0,$C196)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="198" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="198" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C198" s="33"/>
       <c r="D198" s="34">
         <f>IF($A198&lt;&gt;$A197,"",IFERROR(TEXT(TIMEVALUE($D197)+IF($C197="",0,$C197)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="199" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="199" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C199" s="33"/>
       <c r="D199" s="34">
         <f>IF($A199&lt;&gt;$A198,"",IFERROR(TEXT(TIMEVALUE($D198)+IF($C198="",0,$C198)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="200" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="200" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C200" s="33"/>
       <c r="D200" s="34">
         <f>IF($A200&lt;&gt;$A199,"",IFERROR(TEXT(TIMEVALUE($D199)+IF($C199="",0,$C199)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="201" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="201" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C201" s="33"/>
       <c r="D201" s="34">
         <f>IF($A201&lt;&gt;$A200,"",IFERROR(TEXT(TIMEVALUE($D200)+IF($C200="",0,$C200)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="202" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="202" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C202" s="33"/>
       <c r="D202" s="34">
         <f>IF($A202&lt;&gt;$A201,"",IFERROR(TEXT(TIMEVALUE($D201)+IF($C201="",0,$C201)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="203" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="203" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C203" s="33"/>
       <c r="D203" s="34">
         <f>IF($A203&lt;&gt;$A202,"",IFERROR(TEXT(TIMEVALUE($D202)+IF($C202="",0,$C202)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="204" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="204" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C204" s="33"/>
       <c r="D204" s="34">
         <f>IF($A204&lt;&gt;$A203,"",IFERROR(TEXT(TIMEVALUE($D203)+IF($C203="",0,$C203)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="205" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="205" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C205" s="33"/>
       <c r="D205" s="34">
         <f>IF($A205&lt;&gt;$A204,"",IFERROR(TEXT(TIMEVALUE($D204)+IF($C204="",0,$C204)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="206" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="206" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C206" s="33"/>
       <c r="D206" s="34">
         <f>IF($A206&lt;&gt;$A205,"",IFERROR(TEXT(TIMEVALUE($D205)+IF($C205="",0,$C205)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="207" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="207" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C207" s="33"/>
       <c r="D207" s="34">
         <f>IF($A207&lt;&gt;$A206,"",IFERROR(TEXT(TIMEVALUE($D206)+IF($C206="",0,$C206)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="208" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="208" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C208" s="33"/>
       <c r="D208" s="34">
         <f>IF($A208&lt;&gt;$A207,"",IFERROR(TEXT(TIMEVALUE($D207)+IF($C207="",0,$C207)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="209" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="209" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C209" s="33"/>
       <c r="D209" s="34">
         <f>IF($A209&lt;&gt;$A208,"",IFERROR(TEXT(TIMEVALUE($D208)+IF($C208="",0,$C208)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="210" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="210" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C210" s="33"/>
       <c r="D210" s="34">
         <f>IF($A210&lt;&gt;$A209,"",IFERROR(TEXT(TIMEVALUE($D209)+IF($C209="",0,$C209)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="211" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="211" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C211" s="33"/>
       <c r="D211" s="34">
         <f>IF($A211&lt;&gt;$A210,"",IFERROR(TEXT(TIMEVALUE($D210)+IF($C210="",0,$C210)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="212" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="212" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C212" s="33"/>
       <c r="D212" s="34">
         <f>IF($A212&lt;&gt;$A211,"",IFERROR(TEXT(TIMEVALUE($D211)+IF($C211="",0,$C211)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="213" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="213" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C213" s="33"/>
       <c r="D213" s="34">
         <f>IF($A213&lt;&gt;$A212,"",IFERROR(TEXT(TIMEVALUE($D212)+IF($C212="",0,$C212)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="214" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="214" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C214" s="33"/>
       <c r="D214" s="34">
         <f>IF($A214&lt;&gt;$A213,"",IFERROR(TEXT(TIMEVALUE($D213)+IF($C213="",0,$C213)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="215" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="215" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C215" s="33"/>
       <c r="D215" s="34">
         <f>IF($A215&lt;&gt;$A214,"",IFERROR(TEXT(TIMEVALUE($D214)+IF($C214="",0,$C214)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="216" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="216" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C216" s="33"/>
       <c r="D216" s="34">
         <f>IF($A216&lt;&gt;$A215,"",IFERROR(TEXT(TIMEVALUE($D215)+IF($C215="",0,$C215)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="217" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="217" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C217" s="33"/>
       <c r="D217" s="34">
         <f>IF($A217&lt;&gt;$A216,"",IFERROR(TEXT(TIMEVALUE($D216)+IF($C216="",0,$C216)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="218" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="218" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C218" s="33"/>
       <c r="D218" s="34">
         <f>IF($A218&lt;&gt;$A217,"",IFERROR(TEXT(TIMEVALUE($D217)+IF($C217="",0,$C217)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="219" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="219" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C219" s="33"/>
       <c r="D219" s="34">
         <f>IF($A219&lt;&gt;$A218,"",IFERROR(TEXT(TIMEVALUE($D218)+IF($C218="",0,$C218)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="220" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="220" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C220" s="33"/>
       <c r="D220" s="34">
         <f>IF($A220&lt;&gt;$A219,"",IFERROR(TEXT(TIMEVALUE($D219)+IF($C219="",0,$C219)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="221" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="221" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C221" s="33"/>
       <c r="D221" s="34">
         <f>IF($A221&lt;&gt;$A220,"",IFERROR(TEXT(TIMEVALUE($D220)+IF($C220="",0,$C220)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="222" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="222" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C222" s="33"/>
       <c r="D222" s="34">
         <f>IF($A222&lt;&gt;$A221,"",IFERROR(TEXT(TIMEVALUE($D221)+IF($C221="",0,$C221)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="223" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="223" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C223" s="33"/>
       <c r="D223" s="34">
         <f>IF($A223&lt;&gt;$A222,"",IFERROR(TEXT(TIMEVALUE($D222)+IF($C222="",0,$C222)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="224" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="224" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C224" s="33"/>
       <c r="D224" s="34">
         <f>IF($A224&lt;&gt;$A223,"",IFERROR(TEXT(TIMEVALUE($D223)+IF($C223="",0,$C223)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="225" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="225" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C225" s="33"/>
       <c r="D225" s="34">
         <f>IF($A225&lt;&gt;$A224,"",IFERROR(TEXT(TIMEVALUE($D224)+IF($C224="",0,$C224)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="226" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="226" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C226" s="33"/>
       <c r="D226" s="34">
         <f>IF($A226&lt;&gt;$A225,"",IFERROR(TEXT(TIMEVALUE($D225)+IF($C225="",0,$C225)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="227" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="227" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C227" s="33"/>
       <c r="D227" s="34">
         <f>IF($A227&lt;&gt;$A226,"",IFERROR(TEXT(TIMEVALUE($D226)+IF($C226="",0,$C226)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="228" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="228" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C228" s="33"/>
       <c r="D228" s="34">
         <f>IF($A228&lt;&gt;$A227,"",IFERROR(TEXT(TIMEVALUE($D227)+IF($C227="",0,$C227)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="229" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="229" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C229" s="33"/>
       <c r="D229" s="34">
         <f>IF($A229&lt;&gt;$A228,"",IFERROR(TEXT(TIMEVALUE($D228)+IF($C228="",0,$C228)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="230" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="230" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C230" s="33"/>
       <c r="D230" s="34">
         <f>IF($A230&lt;&gt;$A229,"",IFERROR(TEXT(TIMEVALUE($D229)+IF($C229="",0,$C229)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="231" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="231" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C231" s="33"/>
       <c r="D231" s="34">
         <f>IF($A231&lt;&gt;$A230,"",IFERROR(TEXT(TIMEVALUE($D230)+IF($C230="",0,$C230)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="232" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="232" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C232" s="33"/>
       <c r="D232" s="34">
         <f>IF($A232&lt;&gt;$A231,"",IFERROR(TEXT(TIMEVALUE($D231)+IF($C231="",0,$C231)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="233" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="233" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C233" s="33"/>
       <c r="D233" s="34">
         <f>IF($A233&lt;&gt;$A232,"",IFERROR(TEXT(TIMEVALUE($D232)+IF($C232="",0,$C232)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="234" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="234" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C234" s="33"/>
       <c r="D234" s="34">
         <f>IF($A234&lt;&gt;$A233,"",IFERROR(TEXT(TIMEVALUE($D233)+IF($C233="",0,$C233)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="235" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="235" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C235" s="33"/>
       <c r="D235" s="34">
         <f>IF($A235&lt;&gt;$A234,"",IFERROR(TEXT(TIMEVALUE($D234)+IF($C234="",0,$C234)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="236" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="236" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C236" s="33"/>
       <c r="D236" s="34">
         <f>IF($A236&lt;&gt;$A235,"",IFERROR(TEXT(TIMEVALUE($D235)+IF($C235="",0,$C235)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="237" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="237" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C237" s="33"/>
       <c r="D237" s="34">
         <f>IF($A237&lt;&gt;$A236,"",IFERROR(TEXT(TIMEVALUE($D236)+IF($C236="",0,$C236)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="238" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="238" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C238" s="33"/>
       <c r="D238" s="34">
         <f>IF($A238&lt;&gt;$A237,"",IFERROR(TEXT(TIMEVALUE($D237)+IF($C237="",0,$C237)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="239" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="239" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C239" s="33"/>
       <c r="D239" s="34">
         <f>IF($A239&lt;&gt;$A238,"",IFERROR(TEXT(TIMEVALUE($D238)+IF($C238="",0,$C238)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="240" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="240" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C240" s="33"/>
       <c r="D240" s="34">
         <f>IF($A240&lt;&gt;$A239,"",IFERROR(TEXT(TIMEVALUE($D239)+IF($C239="",0,$C239)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="241" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="241" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C241" s="33"/>
       <c r="D241" s="34">
         <f>IF($A241&lt;&gt;$A240,"",IFERROR(TEXT(TIMEVALUE($D240)+IF($C240="",0,$C240)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="242" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="242" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C242" s="33"/>
       <c r="D242" s="34">
         <f>IF($A242&lt;&gt;$A241,"",IFERROR(TEXT(TIMEVALUE($D241)+IF($C241="",0,$C241)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="243" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="243" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C243" s="33"/>
       <c r="D243" s="34">
         <f>IF($A243&lt;&gt;$A242,"",IFERROR(TEXT(TIMEVALUE($D242)+IF($C242="",0,$C242)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="244" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="244" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C244" s="33"/>
       <c r="D244" s="34">
         <f>IF($A244&lt;&gt;$A243,"",IFERROR(TEXT(TIMEVALUE($D243)+IF($C243="",0,$C243)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="245" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="245" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C245" s="33"/>
       <c r="D245" s="34">
         <f>IF($A245&lt;&gt;$A244,"",IFERROR(TEXT(TIMEVALUE($D244)+IF($C244="",0,$C244)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="246" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="246" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C246" s="33"/>
       <c r="D246" s="34">
         <f>IF($A246&lt;&gt;$A245,"",IFERROR(TEXT(TIMEVALUE($D245)+IF($C245="",0,$C245)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="247" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="247" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C247" s="33"/>
       <c r="D247" s="34">
         <f>IF($A247&lt;&gt;$A246,"",IFERROR(TEXT(TIMEVALUE($D246)+IF($C246="",0,$C246)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="248" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="248" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C248" s="33"/>
       <c r="D248" s="34">
         <f>IF($A248&lt;&gt;$A247,"",IFERROR(TEXT(TIMEVALUE($D247)+IF($C247="",0,$C247)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="249" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="249" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C249" s="33"/>
       <c r="D249" s="34">
         <f>IF($A249&lt;&gt;$A248,"",IFERROR(TEXT(TIMEVALUE($D248)+IF($C248="",0,$C248)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="250" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="250" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C250" s="33"/>
       <c r="D250" s="34">
         <f>IF($A250&lt;&gt;$A249,"",IFERROR(TEXT(TIMEVALUE($D249)+IF($C249="",0,$C249)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="251" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="251" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C251" s="33"/>
       <c r="D251" s="34">
         <f>IF($A251&lt;&gt;$A250,"",IFERROR(TEXT(TIMEVALUE($D250)+IF($C250="",0,$C250)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="252" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="252" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C252" s="33"/>
       <c r="D252" s="34">
         <f>IF($A252&lt;&gt;$A251,"",IFERROR(TEXT(TIMEVALUE($D251)+IF($C251="",0,$C251)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="253" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="253" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C253" s="33"/>
       <c r="D253" s="34">
         <f>IF($A253&lt;&gt;$A252,"",IFERROR(TEXT(TIMEVALUE($D252)+IF($C252="",0,$C252)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="254" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="254" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C254" s="33"/>
       <c r="D254" s="34">
         <f>IF($A254&lt;&gt;$A253,"",IFERROR(TEXT(TIMEVALUE($D253)+IF($C253="",0,$C253)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="255" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="255" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C255" s="33"/>
       <c r="D255" s="34">
         <f>IF($A255&lt;&gt;$A254,"",IFERROR(TEXT(TIMEVALUE($D254)+IF($C254="",0,$C254)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="256" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="256" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C256" s="33"/>
       <c r="D256" s="34">
         <f>IF($A256&lt;&gt;$A255,"",IFERROR(TEXT(TIMEVALUE($D255)+IF($C255="",0,$C255)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="257" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="257" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C257" s="33"/>
       <c r="D257" s="34">
         <f>IF($A257&lt;&gt;$A256,"",IFERROR(TEXT(TIMEVALUE($D256)+IF($C256="",0,$C256)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="258" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="258" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C258" s="33"/>
       <c r="D258" s="34">
         <f>IF($A258&lt;&gt;$A257,"",IFERROR(TEXT(TIMEVALUE($D257)+IF($C257="",0,$C257)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="259" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="259" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C259" s="33"/>
       <c r="D259" s="34">
         <f>IF($A259&lt;&gt;$A258,"",IFERROR(TEXT(TIMEVALUE($D258)+IF($C258="",0,$C258)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="260" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="260" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C260" s="33"/>
       <c r="D260" s="34">
         <f>IF($A260&lt;&gt;$A259,"",IFERROR(TEXT(TIMEVALUE($D259)+IF($C259="",0,$C259)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="261" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="261" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C261" s="33"/>
       <c r="D261" s="34">
         <f>IF($A261&lt;&gt;$A260,"",IFERROR(TEXT(TIMEVALUE($D260)+IF($C260="",0,$C260)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="262" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="262" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C262" s="33"/>
       <c r="D262" s="34">
         <f>IF($A262&lt;&gt;$A261,"",IFERROR(TEXT(TIMEVALUE($D261)+IF($C261="",0,$C261)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="263" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="263" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C263" s="33"/>
       <c r="D263" s="34">
         <f>IF($A263&lt;&gt;$A262,"",IFERROR(TEXT(TIMEVALUE($D262)+IF($C262="",0,$C262)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="264" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="264" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C264" s="33"/>
       <c r="D264" s="34">
         <f>IF($A264&lt;&gt;$A263,"",IFERROR(TEXT(TIMEVALUE($D263)+IF($C263="",0,$C263)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="265" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="265" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C265" s="33"/>
       <c r="D265" s="34">
         <f>IF($A265&lt;&gt;$A264,"",IFERROR(TEXT(TIMEVALUE($D264)+IF($C264="",0,$C264)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="266" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="266" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C266" s="33"/>
       <c r="D266" s="34">
         <f>IF($A266&lt;&gt;$A265,"",IFERROR(TEXT(TIMEVALUE($D265)+IF($C265="",0,$C265)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="267" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="267" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C267" s="33"/>
       <c r="D267" s="34">
         <f>IF($A267&lt;&gt;$A266,"",IFERROR(TEXT(TIMEVALUE($D266)+IF($C266="",0,$C266)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="268" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="268" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C268" s="33"/>
       <c r="D268" s="34">
         <f>IF($A268&lt;&gt;$A267,"",IFERROR(TEXT(TIMEVALUE($D267)+IF($C267="",0,$C267)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="269" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="269" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C269" s="33"/>
       <c r="D269" s="34">
         <f>IF($A269&lt;&gt;$A268,"",IFERROR(TEXT(TIMEVALUE($D268)+IF($C268="",0,$C268)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="270" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="270" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C270" s="33"/>
       <c r="D270" s="34">
         <f>IF($A270&lt;&gt;$A269,"",IFERROR(TEXT(TIMEVALUE($D269)+IF($C269="",0,$C269)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="271" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="271" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C271" s="33"/>
       <c r="D271" s="34">
         <f>IF($A271&lt;&gt;$A270,"",IFERROR(TEXT(TIMEVALUE($D270)+IF($C270="",0,$C270)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="272" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="272" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C272" s="33"/>
       <c r="D272" s="34">
         <f>IF($A272&lt;&gt;$A271,"",IFERROR(TEXT(TIMEVALUE($D271)+IF($C271="",0,$C271)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="273" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="273" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C273" s="33"/>
       <c r="D273" s="34">
         <f>IF($A273&lt;&gt;$A272,"",IFERROR(TEXT(TIMEVALUE($D272)+IF($C272="",0,$C272)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="274" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="274" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C274" s="33"/>
       <c r="D274" s="34">
         <f>IF($A274&lt;&gt;$A273,"",IFERROR(TEXT(TIMEVALUE($D273)+IF($C273="",0,$C273)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="275" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="275" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C275" s="33"/>
       <c r="D275" s="34">
         <f>IF($A275&lt;&gt;$A274,"",IFERROR(TEXT(TIMEVALUE($D274)+IF($C274="",0,$C274)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="276" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="276" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C276" s="33"/>
       <c r="D276" s="34">
         <f>IF($A276&lt;&gt;$A275,"",IFERROR(TEXT(TIMEVALUE($D275)+IF($C275="",0,$C275)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="277" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="277" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C277" s="33"/>
       <c r="D277" s="34">
         <f>IF($A277&lt;&gt;$A276,"",IFERROR(TEXT(TIMEVALUE($D276)+IF($C276="",0,$C276)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="278" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="278" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C278" s="33"/>
       <c r="D278" s="34">
         <f>IF($A278&lt;&gt;$A277,"",IFERROR(TEXT(TIMEVALUE($D277)+IF($C277="",0,$C277)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="279" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="279" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C279" s="33"/>
       <c r="D279" s="34">
         <f>IF($A279&lt;&gt;$A278,"",IFERROR(TEXT(TIMEVALUE($D278)+IF($C278="",0,$C278)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="280" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="280" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C280" s="33"/>
       <c r="D280" s="34">
         <f>IF($A280&lt;&gt;$A279,"",IFERROR(TEXT(TIMEVALUE($D279)+IF($C279="",0,$C279)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="281" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="281" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C281" s="33"/>
       <c r="D281" s="34">
         <f>IF($A281&lt;&gt;$A280,"",IFERROR(TEXT(TIMEVALUE($D280)+IF($C280="",0,$C280)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="282" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="282" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C282" s="33"/>
       <c r="D282" s="34">
         <f>IF($A282&lt;&gt;$A281,"",IFERROR(TEXT(TIMEVALUE($D281)+IF($C281="",0,$C281)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="283" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="283" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C283" s="33"/>
       <c r="D283" s="34">
         <f>IF($A283&lt;&gt;$A282,"",IFERROR(TEXT(TIMEVALUE($D282)+IF($C282="",0,$C282)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="284" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="284" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C284" s="33"/>
       <c r="D284" s="34">
         <f>IF($A284&lt;&gt;$A283,"",IFERROR(TEXT(TIMEVALUE($D283)+IF($C283="",0,$C283)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="285" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="285" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C285" s="33"/>
       <c r="D285" s="34">
         <f>IF($A285&lt;&gt;$A284,"",IFERROR(TEXT(TIMEVALUE($D284)+IF($C284="",0,$C284)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="286" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="286" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C286" s="33"/>
       <c r="D286" s="34">
         <f>IF($A286&lt;&gt;$A285,"",IFERROR(TEXT(TIMEVALUE($D285)+IF($C285="",0,$C285)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="287" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="287" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C287" s="33"/>
       <c r="D287" s="34">
         <f>IF($A287&lt;&gt;$A286,"",IFERROR(TEXT(TIMEVALUE($D286)+IF($C286="",0,$C286)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="288" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="288" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C288" s="33"/>
       <c r="D288" s="34">
         <f>IF($A288&lt;&gt;$A287,"",IFERROR(TEXT(TIMEVALUE($D287)+IF($C287="",0,$C287)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="289" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="289" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C289" s="33"/>
       <c r="D289" s="34">
         <f>IF($A289&lt;&gt;$A288,"",IFERROR(TEXT(TIMEVALUE($D288)+IF($C288="",0,$C288)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="290" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="290" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C290" s="33"/>
       <c r="D290" s="34">
         <f>IF($A290&lt;&gt;$A289,"",IFERROR(TEXT(TIMEVALUE($D289)+IF($C289="",0,$C289)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="291" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="291" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C291" s="33"/>
       <c r="D291" s="34">
         <f>IF($A291&lt;&gt;$A290,"",IFERROR(TEXT(TIMEVALUE($D290)+IF($C290="",0,$C290)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="292" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="292" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C292" s="33"/>
       <c r="D292" s="34">
         <f>IF($A292&lt;&gt;$A291,"",IFERROR(TEXT(TIMEVALUE($D291)+IF($C291="",0,$C291)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="293" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="293" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C293" s="33"/>
       <c r="D293" s="34">
         <f>IF($A293&lt;&gt;$A292,"",IFERROR(TEXT(TIMEVALUE($D292)+IF($C292="",0,$C292)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="294" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="294" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C294" s="33"/>
       <c r="D294" s="34">
         <f>IF($A294&lt;&gt;$A293,"",IFERROR(TEXT(TIMEVALUE($D293)+IF($C293="",0,$C293)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="295" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="295" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C295" s="33"/>
       <c r="D295" s="34">
         <f>IF($A295&lt;&gt;$A294,"",IFERROR(TEXT(TIMEVALUE($D294)+IF($C294="",0,$C294)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="296" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="296" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C296" s="33"/>
       <c r="D296" s="34">
         <f>IF($A296&lt;&gt;$A295,"",IFERROR(TEXT(TIMEVALUE($D295)+IF($C295="",0,$C295)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="297" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="297" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C297" s="33"/>
       <c r="D297" s="34">
         <f>IF($A297&lt;&gt;$A296,"",IFERROR(TEXT(TIMEVALUE($D296)+IF($C296="",0,$C296)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="298" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="298" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C298" s="33"/>
       <c r="D298" s="34">
         <f>IF($A298&lt;&gt;$A297,"",IFERROR(TEXT(TIMEVALUE($D297)+IF($C297="",0,$C297)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="299" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="299" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C299" s="33"/>
       <c r="D299" s="34">
         <f>IF($A299&lt;&gt;$A298,"",IFERROR(TEXT(TIMEVALUE($D298)+IF($C298="",0,$C298)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="300" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="300" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C300" s="33"/>
       <c r="D300" s="34">
         <f>IF($A300&lt;&gt;$A299,"",IFERROR(TEXT(TIMEVALUE($D299)+IF($C299="",0,$C299)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="301" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="301" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C301" s="33"/>
       <c r="D301" s="34">
         <f>IF($A301&lt;&gt;$A300,"",IFERROR(TEXT(TIMEVALUE($D300)+IF($C300="",0,$C300)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="302" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="302" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C302" s="33"/>
       <c r="D302" s="34">
         <f>IF($A302&lt;&gt;$A301,"",IFERROR(TEXT(TIMEVALUE($D301)+IF($C301="",0,$C301)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="303" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="303" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C303" s="33"/>
       <c r="D303" s="34">
         <f>IF($A303&lt;&gt;$A302,"",IFERROR(TEXT(TIMEVALUE($D302)+IF($C302="",0,$C302)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="304" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="304" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C304" s="33"/>
       <c r="D304" s="34">
         <f>IF($A304&lt;&gt;$A303,"",IFERROR(TEXT(TIMEVALUE($D303)+IF($C303="",0,$C303)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="305" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="305" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C305" s="33"/>
       <c r="D305" s="34">
         <f>IF($A305&lt;&gt;$A304,"",IFERROR(TEXT(TIMEVALUE($D304)+IF($C304="",0,$C304)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="306" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="306" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C306" s="33"/>
       <c r="D306" s="34">
         <f>IF($A306&lt;&gt;$A305,"",IFERROR(TEXT(TIMEVALUE($D305)+IF($C305="",0,$C305)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="307" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="307" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C307" s="33"/>
       <c r="D307" s="34">
         <f>IF($A307&lt;&gt;$A306,"",IFERROR(TEXT(TIMEVALUE($D306)+IF($C306="",0,$C306)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="308" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="308" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C308" s="33"/>
       <c r="D308" s="34">
         <f>IF($A308&lt;&gt;$A307,"",IFERROR(TEXT(TIMEVALUE($D307)+IF($C307="",0,$C307)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="309" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="309" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C309" s="33"/>
       <c r="D309" s="34">
         <f>IF($A309&lt;&gt;$A308,"",IFERROR(TEXT(TIMEVALUE($D308)+IF($C308="",0,$C308)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="310" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="310" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C310" s="33"/>
       <c r="D310" s="34">
         <f>IF($A310&lt;&gt;$A309,"",IFERROR(TEXT(TIMEVALUE($D309)+IF($C309="",0,$C309)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="311" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="311" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C311" s="33"/>
       <c r="D311" s="34">
         <f>IF($A311&lt;&gt;$A310,"",IFERROR(TEXT(TIMEVALUE($D310)+IF($C310="",0,$C310)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="312" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="312" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C312" s="33"/>
       <c r="D312" s="34">
         <f>IF($A312&lt;&gt;$A311,"",IFERROR(TEXT(TIMEVALUE($D311)+IF($C311="",0,$C311)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="313" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="313" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C313" s="33"/>
       <c r="D313" s="34">
         <f>IF($A313&lt;&gt;$A312,"",IFERROR(TEXT(TIMEVALUE($D312)+IF($C312="",0,$C312)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="314" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="314" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C314" s="33"/>
       <c r="D314" s="34">
         <f>IF($A314&lt;&gt;$A313,"",IFERROR(TEXT(TIMEVALUE($D313)+IF($C313="",0,$C313)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="315" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="315" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C315" s="33"/>
       <c r="D315" s="34">
         <f>IF($A315&lt;&gt;$A314,"",IFERROR(TEXT(TIMEVALUE($D314)+IF($C314="",0,$C314)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="316" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="316" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C316" s="33"/>
       <c r="D316" s="34">
         <f>IF($A316&lt;&gt;$A315,"",IFERROR(TEXT(TIMEVALUE($D315)+IF($C315="",0,$C315)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="317" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="317" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C317" s="33"/>
       <c r="D317" s="34">
         <f>IF($A317&lt;&gt;$A316,"",IFERROR(TEXT(TIMEVALUE($D316)+IF($C316="",0,$C316)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="318" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="318" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C318" s="33"/>
       <c r="D318" s="34">
         <f>IF($A318&lt;&gt;$A317,"",IFERROR(TEXT(TIMEVALUE($D317)+IF($C317="",0,$C317)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="319" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="319" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C319" s="33"/>
       <c r="D319" s="34">
         <f>IF($A319&lt;&gt;$A318,"",IFERROR(TEXT(TIMEVALUE($D318)+IF($C318="",0,$C318)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="320" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="320" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C320" s="33"/>
       <c r="D320" s="34">
         <f>IF($A320&lt;&gt;$A319,"",IFERROR(TEXT(TIMEVALUE($D319)+IF($C319="",0,$C319)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="321" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="321" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C321" s="33"/>
       <c r="D321" s="34">
         <f>IF($A321&lt;&gt;$A320,"",IFERROR(TEXT(TIMEVALUE($D320)+IF($C320="",0,$C320)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="322" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="322" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C322" s="33"/>
       <c r="D322" s="34">
         <f>IF($A322&lt;&gt;$A321,"",IFERROR(TEXT(TIMEVALUE($D321)+IF($C321="",0,$C321)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="323" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="323" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C323" s="33"/>
       <c r="D323" s="34">
         <f>IF($A323&lt;&gt;$A322,"",IFERROR(TEXT(TIMEVALUE($D322)+IF($C322="",0,$C322)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="324" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="324" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C324" s="33"/>
       <c r="D324" s="34">
         <f>IF($A324&lt;&gt;$A323,"",IFERROR(TEXT(TIMEVALUE($D323)+IF($C323="",0,$C323)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="325" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="325" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C325" s="33"/>
       <c r="D325" s="34">
         <f>IF($A325&lt;&gt;$A324,"",IFERROR(TEXT(TIMEVALUE($D324)+IF($C324="",0,$C324)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="326" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="326" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C326" s="33"/>
       <c r="D326" s="34">
         <f>IF($A326&lt;&gt;$A325,"",IFERROR(TEXT(TIMEVALUE($D325)+IF($C325="",0,$C325)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="327" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="327" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C327" s="33"/>
       <c r="D327" s="34">
         <f>IF($A327&lt;&gt;$A326,"",IFERROR(TEXT(TIMEVALUE($D326)+IF($C326="",0,$C326)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="328" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="328" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C328" s="33"/>
       <c r="D328" s="34">
         <f>IF($A328&lt;&gt;$A327,"",IFERROR(TEXT(TIMEVALUE($D327)+IF($C327="",0,$C327)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="329" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="329" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C329" s="33"/>
       <c r="D329" s="34">
         <f>IF($A329&lt;&gt;$A328,"",IFERROR(TEXT(TIMEVALUE($D328)+IF($C328="",0,$C328)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="330" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="330" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C330" s="33"/>
       <c r="D330" s="34">
         <f>IF($A330&lt;&gt;$A329,"",IFERROR(TEXT(TIMEVALUE($D329)+IF($C329="",0,$C329)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="331" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="331" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C331" s="33"/>
       <c r="D331" s="34">
         <f>IF($A331&lt;&gt;$A330,"",IFERROR(TEXT(TIMEVALUE($D330)+IF($C330="",0,$C330)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="332" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="332" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C332" s="33"/>
       <c r="D332" s="34">
         <f>IF($A332&lt;&gt;$A331,"",IFERROR(TEXT(TIMEVALUE($D331)+IF($C331="",0,$C331)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="333" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="333" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C333" s="33"/>
       <c r="D333" s="34">
         <f>IF($A333&lt;&gt;$A332,"",IFERROR(TEXT(TIMEVALUE($D332)+IF($C332="",0,$C332)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="334" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="334" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C334" s="33"/>
       <c r="D334" s="34">
         <f>IF($A334&lt;&gt;$A333,"",IFERROR(TEXT(TIMEVALUE($D333)+IF($C333="",0,$C333)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="335" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="335" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C335" s="33"/>
       <c r="D335" s="34">
         <f>IF($A335&lt;&gt;$A334,"",IFERROR(TEXT(TIMEVALUE($D334)+IF($C334="",0,$C334)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="336" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="336" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C336" s="33"/>
       <c r="D336" s="34">
         <f>IF($A336&lt;&gt;$A335,"",IFERROR(TEXT(TIMEVALUE($D335)+IF($C335="",0,$C335)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="337" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="337" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C337" s="33"/>
       <c r="D337" s="34">
         <f>IF($A337&lt;&gt;$A336,"",IFERROR(TEXT(TIMEVALUE($D336)+IF($C336="",0,$C336)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="338" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="338" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C338" s="33"/>
       <c r="D338" s="34">
         <f>IF($A338&lt;&gt;$A337,"",IFERROR(TEXT(TIMEVALUE($D337)+IF($C337="",0,$C337)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="339" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="339" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C339" s="33"/>
       <c r="D339" s="34">
         <f>IF($A339&lt;&gt;$A338,"",IFERROR(TEXT(TIMEVALUE($D338)+IF($C338="",0,$C338)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="340" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="340" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C340" s="33"/>
       <c r="D340" s="34">
         <f>IF($A340&lt;&gt;$A339,"",IFERROR(TEXT(TIMEVALUE($D339)+IF($C339="",0,$C339)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="341" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="341" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C341" s="33"/>
       <c r="D341" s="34">
         <f>IF($A341&lt;&gt;$A340,"",IFERROR(TEXT(TIMEVALUE($D340)+IF($C340="",0,$C340)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="342" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="342" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C342" s="33"/>
       <c r="D342" s="34">
         <f>IF($A342&lt;&gt;$A341,"",IFERROR(TEXT(TIMEVALUE($D341)+IF($C341="",0,$C341)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="343" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="343" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C343" s="33"/>
       <c r="D343" s="34">
         <f>IF($A343&lt;&gt;$A342,"",IFERROR(TEXT(TIMEVALUE($D342)+IF($C342="",0,$C342)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="344" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="344" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C344" s="33"/>
       <c r="D344" s="34">
         <f>IF($A344&lt;&gt;$A343,"",IFERROR(TEXT(TIMEVALUE($D343)+IF($C343="",0,$C343)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="345" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="345" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C345" s="33"/>
       <c r="D345" s="34">
         <f>IF($A345&lt;&gt;$A344,"",IFERROR(TEXT(TIMEVALUE($D344)+IF($C344="",0,$C344)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="346" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="346" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C346" s="33"/>
       <c r="D346" s="34">
         <f>IF($A346&lt;&gt;$A345,"",IFERROR(TEXT(TIMEVALUE($D345)+IF($C345="",0,$C345)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="347" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="347" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C347" s="33"/>
       <c r="D347" s="34">
         <f>IF($A347&lt;&gt;$A346,"",IFERROR(TEXT(TIMEVALUE($D346)+IF($C346="",0,$C346)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="348" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="348" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C348" s="33"/>
       <c r="D348" s="34">
         <f>IF($A348&lt;&gt;$A347,"",IFERROR(TEXT(TIMEVALUE($D347)+IF($C347="",0,$C347)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="349" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="349" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C349" s="33"/>
       <c r="D349" s="34">
         <f>IF($A349&lt;&gt;$A348,"",IFERROR(TEXT(TIMEVALUE($D348)+IF($C348="",0,$C348)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="350" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="350" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C350" s="33"/>
       <c r="D350" s="34">
         <f>IF($A350&lt;&gt;$A349,"",IFERROR(TEXT(TIMEVALUE($D349)+IF($C349="",0,$C349)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="351" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="351" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C351" s="33"/>
       <c r="D351" s="34">
         <f>IF($A351&lt;&gt;$A350,"",IFERROR(TEXT(TIMEVALUE($D350)+IF($C350="",0,$C350)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="352" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="352" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C352" s="33"/>
       <c r="D352" s="34">
         <f>IF($A352&lt;&gt;$A351,"",IFERROR(TEXT(TIMEVALUE($D351)+IF($C351="",0,$C351)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="353" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="353" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C353" s="33"/>
       <c r="D353" s="34">
         <f>IF($A353&lt;&gt;$A352,"",IFERROR(TEXT(TIMEVALUE($D352)+IF($C352="",0,$C352)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="354" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="354" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C354" s="33"/>
       <c r="D354" s="34">
         <f>IF($A354&lt;&gt;$A353,"",IFERROR(TEXT(TIMEVALUE($D353)+IF($C353="",0,$C353)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="355" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="355" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C355" s="33"/>
       <c r="D355" s="34">
         <f>IF($A355&lt;&gt;$A354,"",IFERROR(TEXT(TIMEVALUE($D354)+IF($C354="",0,$C354)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="356" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="356" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C356" s="33"/>
       <c r="D356" s="34">
         <f>IF($A356&lt;&gt;$A355,"",IFERROR(TEXT(TIMEVALUE($D355)+IF($C355="",0,$C355)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="357" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="357" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C357" s="33"/>
       <c r="D357" s="34">
         <f>IF($A357&lt;&gt;$A356,"",IFERROR(TEXT(TIMEVALUE($D356)+IF($C356="",0,$C356)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="358" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="358" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C358" s="33"/>
       <c r="D358" s="34">
         <f>IF($A358&lt;&gt;$A357,"",IFERROR(TEXT(TIMEVALUE($D357)+IF($C357="",0,$C357)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="359" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="359" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C359" s="33"/>
       <c r="D359" s="34">
         <f>IF($A359&lt;&gt;$A358,"",IFERROR(TEXT(TIMEVALUE($D358)+IF($C358="",0,$C358)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="360" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="360" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C360" s="33"/>
       <c r="D360" s="34">
         <f>IF($A360&lt;&gt;$A359,"",IFERROR(TEXT(TIMEVALUE($D359)+IF($C359="",0,$C359)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="361" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="361" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C361" s="33"/>
       <c r="D361" s="34">
         <f>IF($A361&lt;&gt;$A360,"",IFERROR(TEXT(TIMEVALUE($D360)+IF($C360="",0,$C360)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="362" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="362" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C362" s="33"/>
       <c r="D362" s="34">
         <f>IF($A362&lt;&gt;$A361,"",IFERROR(TEXT(TIMEVALUE($D361)+IF($C361="",0,$C361)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="363" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="363" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C363" s="33"/>
       <c r="D363" s="34">
         <f>IF($A363&lt;&gt;$A362,"",IFERROR(TEXT(TIMEVALUE($D362)+IF($C362="",0,$C362)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="364" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="364" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C364" s="33"/>
       <c r="D364" s="34">
         <f>IF($A364&lt;&gt;$A363,"",IFERROR(TEXT(TIMEVALUE($D363)+IF($C363="",0,$C363)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="365" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="365" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C365" s="33"/>
       <c r="D365" s="34">
         <f>IF($A365&lt;&gt;$A364,"",IFERROR(TEXT(TIMEVALUE($D364)+IF($C364="",0,$C364)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="366" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="366" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C366" s="33"/>
       <c r="D366" s="34">
         <f>IF($A366&lt;&gt;$A365,"",IFERROR(TEXT(TIMEVALUE($D365)+IF($C365="",0,$C365)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="367" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="367" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C367" s="33"/>
       <c r="D367" s="34">
         <f>IF($A367&lt;&gt;$A366,"",IFERROR(TEXT(TIMEVALUE($D366)+IF($C366="",0,$C366)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="368" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="368" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C368" s="33"/>
       <c r="D368" s="34">
         <f>IF($A368&lt;&gt;$A367,"",IFERROR(TEXT(TIMEVALUE($D367)+IF($C367="",0,$C367)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="369" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="369" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C369" s="33"/>
       <c r="D369" s="34">
         <f>IF($A369&lt;&gt;$A368,"",IFERROR(TEXT(TIMEVALUE($D368)+IF($C368="",0,$C368)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="370" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="370" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C370" s="33"/>
       <c r="D370" s="34">
         <f>IF($A370&lt;&gt;$A369,"",IFERROR(TEXT(TIMEVALUE($D369)+IF($C369="",0,$C369)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="371" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="371" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C371" s="33"/>
       <c r="D371" s="34">
         <f>IF($A371&lt;&gt;$A370,"",IFERROR(TEXT(TIMEVALUE($D370)+IF($C370="",0,$C370)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="372" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="372" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C372" s="33"/>
       <c r="D372" s="34">
         <f>IF($A372&lt;&gt;$A371,"",IFERROR(TEXT(TIMEVALUE($D371)+IF($C371="",0,$C371)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="373" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="373" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C373" s="33"/>
       <c r="D373" s="34">
         <f>IF($A373&lt;&gt;$A372,"",IFERROR(TEXT(TIMEVALUE($D372)+IF($C372="",0,$C372)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="374" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="374" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C374" s="33"/>
       <c r="D374" s="34">
         <f>IF($A374&lt;&gt;$A373,"",IFERROR(TEXT(TIMEVALUE($D373)+IF($C373="",0,$C373)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="375" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="375" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C375" s="33"/>
       <c r="D375" s="34">
         <f>IF($A375&lt;&gt;$A374,"",IFERROR(TEXT(TIMEVALUE($D374)+IF($C374="",0,$C374)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="376" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="376" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C376" s="33"/>
       <c r="D376" s="34">
         <f>IF($A376&lt;&gt;$A375,"",IFERROR(TEXT(TIMEVALUE($D375)+IF($C375="",0,$C375)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="377" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="377" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C377" s="33"/>
       <c r="D377" s="34">
         <f>IF($A377&lt;&gt;$A376,"",IFERROR(TEXT(TIMEVALUE($D376)+IF($C376="",0,$C376)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="378" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="378" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C378" s="33"/>
       <c r="D378" s="34">
         <f>IF($A378&lt;&gt;$A377,"",IFERROR(TEXT(TIMEVALUE($D377)+IF($C377="",0,$C377)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="379" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="379" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C379" s="33"/>
       <c r="D379" s="34">
         <f>IF($A379&lt;&gt;$A378,"",IFERROR(TEXT(TIMEVALUE($D378)+IF($C378="",0,$C378)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="380" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="380" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C380" s="33"/>
       <c r="D380" s="34">
         <f>IF($A380&lt;&gt;$A379,"",IFERROR(TEXT(TIMEVALUE($D379)+IF($C379="",0,$C379)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="381" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="381" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C381" s="33"/>
       <c r="D381" s="34">
         <f>IF($A381&lt;&gt;$A380,"",IFERROR(TEXT(TIMEVALUE($D380)+IF($C380="",0,$C380)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="382" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="382" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C382" s="33"/>
       <c r="D382" s="34">
         <f>IF($A382&lt;&gt;$A381,"",IFERROR(TEXT(TIMEVALUE($D381)+IF($C381="",0,$C381)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="383" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="383" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C383" s="33"/>
       <c r="D383" s="34">
         <f>IF($A383&lt;&gt;$A382,"",IFERROR(TEXT(TIMEVALUE($D382)+IF($C382="",0,$C382)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="384" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="384" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C384" s="33"/>
       <c r="D384" s="34">
         <f>IF($A384&lt;&gt;$A383,"",IFERROR(TEXT(TIMEVALUE($D383)+IF($C383="",0,$C383)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="385" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="385" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C385" s="33"/>
       <c r="D385" s="34">
         <f>IF($A385&lt;&gt;$A384,"",IFERROR(TEXT(TIMEVALUE($D384)+IF($C384="",0,$C384)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="386" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="386" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C386" s="33"/>
       <c r="D386" s="34">
         <f>IF($A386&lt;&gt;$A385,"",IFERROR(TEXT(TIMEVALUE($D385)+IF($C385="",0,$C385)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="387" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="387" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C387" s="33"/>
       <c r="D387" s="34">
         <f>IF($A387&lt;&gt;$A386,"",IFERROR(TEXT(TIMEVALUE($D386)+IF($C386="",0,$C386)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="388" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="388" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C388" s="33"/>
       <c r="D388" s="34">
         <f>IF($A388&lt;&gt;$A387,"",IFERROR(TEXT(TIMEVALUE($D387)+IF($C387="",0,$C387)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="389" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="389" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C389" s="33"/>
       <c r="D389" s="34">
         <f>IF($A389&lt;&gt;$A388,"",IFERROR(TEXT(TIMEVALUE($D388)+IF($C388="",0,$C388)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="390" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="390" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C390" s="33"/>
       <c r="D390" s="34">
         <f>IF($A390&lt;&gt;$A389,"",IFERROR(TEXT(TIMEVALUE($D389)+IF($C389="",0,$C389)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="391" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="391" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C391" s="33"/>
       <c r="D391" s="34">
         <f>IF($A391&lt;&gt;$A390,"",IFERROR(TEXT(TIMEVALUE($D390)+IF($C390="",0,$C390)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="392" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="392" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C392" s="33"/>
       <c r="D392" s="34">
         <f>IF($A392&lt;&gt;$A391,"",IFERROR(TEXT(TIMEVALUE($D391)+IF($C391="",0,$C391)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="393" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="393" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C393" s="33"/>
       <c r="D393" s="34">
         <f>IF($A393&lt;&gt;$A392,"",IFERROR(TEXT(TIMEVALUE($D392)+IF($C392="",0,$C392)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="394" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="394" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C394" s="33"/>
       <c r="D394" s="34">
         <f>IF($A394&lt;&gt;$A393,"",IFERROR(TEXT(TIMEVALUE($D393)+IF($C393="",0,$C393)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="395" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="395" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C395" s="33"/>
       <c r="D395" s="34">
         <f>IF($A395&lt;&gt;$A394,"",IFERROR(TEXT(TIMEVALUE($D394)+IF($C394="",0,$C394)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="396" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="396" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C396" s="33"/>
       <c r="D396" s="34">
         <f>IF($A396&lt;&gt;$A395,"",IFERROR(TEXT(TIMEVALUE($D395)+IF($C395="",0,$C395)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="397" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="397" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C397" s="33"/>
       <c r="D397" s="34">
         <f>IF($A397&lt;&gt;$A396,"",IFERROR(TEXT(TIMEVALUE($D396)+IF($C396="",0,$C396)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="398" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="398" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C398" s="33"/>
       <c r="D398" s="34">
         <f>IF($A398&lt;&gt;$A397,"",IFERROR(TEXT(TIMEVALUE($D397)+IF($C397="",0,$C397)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="399" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="399" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C399" s="33"/>
       <c r="D399" s="34">
         <f>IF($A399&lt;&gt;$A398,"",IFERROR(TEXT(TIMEVALUE($D398)+IF($C398="",0,$C398)/1440,"hh:mm"),""))</f>
       </c>
     </row>
-    <row r="400" ht="15" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="400" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C400" s="33"/>
       <c r="D400" s="34">
         <f>IF($A400&lt;&gt;$A399,"",IFERROR(TEXT(TIMEVALUE($D399)+IF($C399="",0,$C399)/1440,"hh:mm"),""))</f>
@@ -7753,44 +7774,44 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -7798,31 +7819,31 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -7830,31 +7851,31 @@
         <v>7</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="H6" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>414</v>
-      </c>
       <c r="I6" s="13" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -8094,11 +8115,12 @@
   <sheetPr>
     <tabColor rgb="FF1F5C99"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
     <col min="1" max="2" width="22" style="1" customWidth="1"/>
     <col min="3" max="3" width="46" style="1" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -8108,128 +8130,134 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>428</v>
+        <v>431</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -8366,26 +8394,26 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B5" s="13"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B6" s="13"/>
     </row>
@@ -8490,44 +8518,44 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="25"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="25"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="25"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="25"/>

--- a/builder/travel-template.xlsx
+++ b/builder/travel-template.xlsx
@@ -15,15 +15,15 @@
     <sheet sheetId="6" name="打包清單" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="常用片語" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="緊急資訊" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="購物清單" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="信用卡" state="visible" r:id="rId13"/>
+    <sheet sheetId="10" name="信用卡" state="visible" r:id="rId12"/>
+    <sheet sheetId="9" name="購物清單" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="493">
   <si>
     <t>旅遊網站資料模板</t>
   </si>
@@ -1929,42 +1929,6 @@
     <t>旅遊保險 24h 專線</t>
   </si>
   <si>
-    <t>想買的東西與優惠券。「圖片」填 img/ 底下的檔名，產生的網站上點圖就會放大給店員看，離線也打得開；要現場生成的券改填「連結」，會變成一顆跳轉按鈕。整張留空就不會有購物分頁。</t>
-  </si>
-  <si>
-    <t>群組</t>
-  </si>
-  <si>
-    <t>誰要的</t>
-  </si>
-  <si>
-    <t>圖片</t>
-  </si>
-  <si>
-    <t>折價券</t>
-  </si>
-  <si>
-    <t>鶴羽藥妝</t>
-  </si>
-  <si>
-    <t>img/tsuruha.jpg</t>
-  </si>
-  <si>
-    <t>唐吉訶德 Donki</t>
-  </si>
-  <si>
-    <t>https://japanportal.donki-global.com/coupon/cp001_zhtw.html</t>
-  </si>
-  <si>
-    <t>藥妝店</t>
-  </si>
-  <si>
-    <t>資生堂吸油面紙</t>
-  </si>
-  <si>
-    <t>媽媽</t>
-  </si>
-  <si>
     <t>刷卡攻略。重點不是「有哪些卡」，而是「這張還能刷多少才到上限」——「加碼額度」填回饋上限 ÷ 加碼%（例如每月上限 500 點、加碼 8% → 6250），留空代表沒有上限、網站就不畫進度條。整張留空就不會有這張卡片。</t>
   </si>
   <si>
@@ -2021,6 +1985,45 @@
   </si>
   <si>
     <t>切換「玩旅刷」模式，無上限。主力無腦刷。</t>
+  </si>
+  <si>
+    <t>想買的東西與優惠券。「圖片」填 img/ 底下的檔名，產生的網站上點圖就會放大給店員看，離線也打得開；要現場生成的券改填「連結」，會變成一顆跳轉按鈕。「類型」填「券」的那一組不會有數量與金額欄位——券是用掉的，不是買到的；整組看同一個值，填在哪一列都算。整張留空就不會有購物分頁。</t>
+  </si>
+  <si>
+    <t>群組</t>
+  </si>
+  <si>
+    <t>誰要的</t>
+  </si>
+  <si>
+    <t>圖片</t>
+  </si>
+  <si>
+    <t>折價券</t>
+  </si>
+  <si>
+    <t>券</t>
+  </si>
+  <si>
+    <t>鶴羽藥妝</t>
+  </si>
+  <si>
+    <t>img/tsuruha.jpg</t>
+  </si>
+  <si>
+    <t>唐吉訶德 Donki</t>
+  </si>
+  <si>
+    <t>https://japanportal.donki-global.com/coupon/cp001_zhtw.html</t>
+  </si>
+  <si>
+    <t>藥妝店</t>
+  </si>
+  <si>
+    <t>資生堂吸油面紙</t>
+  </si>
+  <si>
+    <t>媽媽</t>
   </si>
 </sst>
 </file>
@@ -2740,7 +2743,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" ht="21.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
       <c r="B23" s="14" t="s">
         <v>33</v>
       </c>
@@ -2751,7 +2755,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" ht="21.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
       <c r="B24" s="14" t="s">
         <v>35</v>
       </c>
@@ -3584,37 +3589,38 @@
     <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>473</v>
-      </c>
-    </row>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>214</v>
@@ -3622,52 +3628,52 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B5" s="16">
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E5" s="16">
         <v>6250</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B6" s="16">
         <v>3.3</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3912,7 +3918,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -12246,21 +12252,21 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>428</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -12840,14 +12846,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="52" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -12857,232 +12864,266 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>463</v>
-      </c>
       <c r="D4" s="12" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="E4" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="E5" s="16"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>485</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>468</v>
-      </c>
-      <c r="C6" s="16"/>
+        <v>485</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>488</v>
+      </c>
       <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="16"/>
+      <c r="F6" s="16" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>470</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>471</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="B7" s="16"/>
       <c r="C7" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="D7" s="16"/>
+        <v>491</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>492</v>
+      </c>
       <c r="E7" s="16"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="16"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="16"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="16"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="16"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="16"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="16"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="16"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="16"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="16"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="16"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="16"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="16"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="16"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="16"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="16"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="16"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="16"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/builder/travel-template.xlsx
+++ b/builder/travel-template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="512">
   <si>
     <t>旅遊網站資料模板</t>
   </si>
@@ -680,13 +680,13 @@
     <t>說明／備註</t>
   </si>
   <si>
-    <t>當下要知道的操作資訊：交通時間、停留多久、開放時間、要先預約。網站上直接顯示。</t>
+    <t>站在門口才需要看的：會卡住的事、要先做的事、備案。卡片上已經有的不要再寫（見最下方「說明／備註 的寫法」）。網站上直接顯示。</t>
   </si>
   <si>
     <t>介紹</t>
   </si>
   <si>
-    <t>這地方是什麼、為什麼值得看。網站上收合成「看介紹」，點了才展開，不會把一天的版面拉長。</t>
+    <t>這地方是什麼、為什麼值得看——在家讀完就不用再看的放這裡。網站上收合成「看介紹」，點了才展開，不會把一天的版面拉長。</t>
   </si>
   <si>
     <t>只有景點、餐飲、購物會顯示介紹。填在其他類型上產生器會提醒你。</t>
@@ -701,6 +701,66 @@
     <t>待辦事項如果要連到某個網站（例如線上填寫入境手續），把網址填在這一欄，網站上該項目旁邊會多一顆「開啟」。留空就是一般的勾選項目。</t>
   </si>
   <si>
+    <t>說明／備註 的寫法</t>
+  </si>
+  <si>
+    <t>判斷方法</t>
+  </si>
+  <si>
+    <t>站在門口才需要看 → 說明。在家讀完就不用再看 → 介紹。</t>
+  </si>
+  <si>
+    <t>一、卡片上有的不要寫</t>
+  </si>
+  <si>
+    <t>時間、停留、交通、地點、營業時間、費用、電話都有自己的欄位，網站會顯示。說明裡再寫一次就是重複。</t>
+  </si>
+  <si>
+    <t>二、一行一件事</t>
+  </si>
+  <si>
+    <t>不要用「・」把營業時間、電話、停車擠成一行。照這個順序寫：怎麼去（路線）→ 時間限制 → 要先做的 → ⚠️ 會卡住的 → 備案。</t>
+  </si>
+  <si>
+    <t>三、⚠️ 只給會出事的</t>
+  </si>
+  <si>
+    <t>不知道就會白跑一趟、趕不上、進不去，才用 ⚠️。「山頂風大帶外套」是提醒，不用 ⚠️。其他 emoji 不要放在行首。</t>
+  </si>
+  <si>
+    <t>四、不寫資料來源</t>
+  </si>
+  <si>
+    <t>不要寫「試算表上的」「重複推薦 2 次」。評分想留就直接寫 4.5★。</t>
+  </si>
+  <si>
+    <t>新欄位怎麼填</t>
+  </si>
+  <si>
+    <t>交通(分)</t>
+  </si>
+  <si>
+    <t>停留(分) 裡花在路上的分鐘數。停留(分) 照舊填總時間，網站自己扣：停留 230、交通 80 → 卡片顯示「🚗 車程 1 小時 20 分」「⏳ 停留 2 小時 30 分」。車程、步行、搭車看「交通方式」欄。</t>
+  </si>
+  <si>
+    <t>營業時間</t>
+  </si>
+  <si>
+    <t>一格寫完，多個設施用「／」分開，例：天神地下街 10:00–20:00／PARCO 10:00–20:30。住宿填 Check-in 與退房時間。</t>
+  </si>
+  <si>
+    <t>費用</t>
+  </si>
+  <si>
+    <t>門票、停車、要付的錢，含付款方式，例：¥500（現金）。</t>
+  </si>
+  <si>
+    <t>電話</t>
+  </si>
+  <si>
+    <t>只填號碼，網站上點了就能直接撥。</t>
+  </si>
+  <si>
     <t>項目</t>
   </si>
   <si>
@@ -836,7 +896,7 @@
     <t>李</t>
   </si>
   <si>
-    <t>一列一個項目，由上往下就是網站顯示順序。日期不用填，會由出發日推算。「停留(分)」填這個項目要花多久（交通就是移動時間），「時間」欄會自動累加，但每天第一列的時間要自己填。「分頁名稱」只填每天第一列，不用寫 D1、D2。「交通方式」只在改變時填，之後沿用。類型開頭有「→」代表附屬於上一列。底色會依「天」自動交替（單數天淺藍、雙數天淺綠），換天的地方有一條藍色分隔線；同一天內顏色較深的是「→」開頭的從屬行。底色全部由公式判斷，不用自己塗。</t>
+    <t>一列一個項目，由上往下就是網站顯示順序。日期不用填，會由出發日推算。「停留(分)」填這一列總共佔掉多久——開車或走過去的時間也算進去，「時間」欄靠它往下推。其中花在路上的另外填在「交通(分)」，網站會自己扣掉，卡片上才分得出車程與停留。「時間」欄會自動累加，但每天第一列的時間要自己填。「分頁名稱」只填每天第一列，不用寫 D1、D2。「交通方式」只在改變時填，之後沿用。類型開頭有「→」代表附屬於上一列。底色會依「天」自動交替（單數天淺藍、雙數天淺綠），換天的地方有一條藍色分隔線；同一天內顏色較深的是「→」開頭的從屬行。底色全部由公式判斷，不用自己塗。</t>
   </si>
   <si>
     <t>天</t>
@@ -1912,9 +1972,6 @@
   </si>
   <si>
     <t>內容</t>
-  </si>
-  <si>
-    <t>電話</t>
   </si>
   <si>
     <t>住處地址</t>
@@ -2292,7 +2349,46 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
+    <dxf>
+      <border>
+        <left/>
+        <right/>
+        <top style="medium">
+          <color rgb="FF4A7EBB"/>
+        </top>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD2E4F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE8F1FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8ECD6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEDF6EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border>
         <left/>
@@ -2525,7 +2621,7 @@
   <sheetPr>
     <tabColor rgb="FF154570"/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
@@ -3568,6 +3664,88 @@
         <v>174</v>
       </c>
       <c r="D110" s="1"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>194</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3596,84 +3774,84 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="B5" s="16">
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="E5" s="16">
         <v>6250</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="B6" s="16">
         <v>3.3</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3949,46 +4127,46 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3996,101 +4174,101 @@
         <v>112</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="24" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="24" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="24" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="24" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4099,7 +4277,7 @@
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4108,7 +4286,7 @@
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="24" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -4143,7 +4321,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -4153,35 +4331,35 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="B7" s="24"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="B8" s="24"/>
     </row>
@@ -4196,7 +4374,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:R400"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -4213,6 +4391,10 @@
     <col min="12" max="12" width="15" style="1" customWidth="1"/>
     <col min="13" max="13" width="30" style="1" customWidth="1"/>
     <col min="14" max="14" width="11" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -4234,7 +4416,7 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4264,33 +4446,33 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>224</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>204</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>39</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>93</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>167</v>
@@ -4299,57 +4481,73 @@
         <v>169</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="25">
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C5" s="26">
         <v>20</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="O5" s="26"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -4363,21 +4561,25 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
-    </row>
-    <row r="7" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" s="26"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="25">
         <v>1</v>
       </c>
@@ -4389,21 +4591,25 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
-    </row>
-    <row r="8" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" s="26"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <v>1</v>
       </c>
@@ -4415,23 +4621,27 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8" s="26"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="25">
         <v>1</v>
       </c>
@@ -4445,21 +4655,25 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
-    </row>
-    <row r="10" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9" s="26"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="25">
         <v>1</v>
       </c>
@@ -4471,21 +4685,25 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
-    </row>
-    <row r="11" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O10" s="26"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+    </row>
+    <row r="11" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="25">
         <v>1</v>
       </c>
@@ -4497,21 +4715,25 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="28" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
-    </row>
-    <row r="12" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O11" s="26"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+    </row>
+    <row r="12" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <v>1</v>
       </c>
@@ -4523,23 +4745,27 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
-    </row>
-    <row r="13" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O12" s="26"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="25">
         <v>1</v>
       </c>
@@ -4553,31 +4779,35 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="N13" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="14" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O13" s="26"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+    </row>
+    <row r="14" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <v>1</v>
       </c>
@@ -4589,58 +4819,66 @@
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="28" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="15" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="N14" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="15" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14" s="26"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+    </row>
+    <row r="15" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="25">
         <v>2</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="C15" s="26">
         <v>12</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
-    </row>
-    <row r="16" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O15" s="26"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+    </row>
+    <row r="16" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="25">
         <v>2</v>
       </c>
@@ -4652,21 +4890,25 @@
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
-    </row>
-    <row r="17" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O16" s="26"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+    </row>
+    <row r="17" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="25">
         <v>2</v>
       </c>
@@ -4678,23 +4920,27 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="28" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="15" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
-    </row>
-    <row r="18" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17" s="26"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+    </row>
+    <row r="18" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="25">
         <v>2</v>
       </c>
@@ -4706,23 +4952,27 @@
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
-    </row>
-    <row r="19" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="26"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+    </row>
+    <row r="19" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="25">
         <v>2</v>
       </c>
@@ -4736,32 +4986,36 @@
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="15" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K19" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="L19" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="L19" s="13" t="s">
-        <v>261</v>
-      </c>
       <c r="M19" s="13" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O19" s="26"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+    </row>
+    <row r="20" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="25">
         <v>2</v>
       </c>
@@ -4775,27 +5029,31 @@
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="O20" s="26"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+    </row>
+    <row r="21" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="25">
         <v>2</v>
       </c>
@@ -4809,30 +5067,34 @@
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="15" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="N21" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="22" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O21" s="26"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+    </row>
+    <row r="22" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="25">
         <v>2</v>
       </c>
@@ -4849,18 +5111,22 @@
         <v>61</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="15" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="J22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
-    </row>
-    <row r="23" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O22" s="26"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+    </row>
+    <row r="23" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="25">
         <v>2</v>
       </c>
@@ -4872,27 +5138,31 @@
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="28" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="L23" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="24" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23" s="26"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+    </row>
+    <row r="24" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="25">
         <v>2</v>
       </c>
@@ -4904,27 +5174,31 @@
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="28" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="L24" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="25" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24" s="26"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+    </row>
+    <row r="25" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="25">
         <v>2</v>
       </c>
@@ -4938,31 +5212,35 @@
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="28" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="N25" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="26" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25" s="26"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+    </row>
+    <row r="26" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="25">
         <v>2</v>
       </c>
@@ -4976,29 +5254,33 @@
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="15" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="27" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="26"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+    </row>
+    <row r="27" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="25">
         <v>2</v>
       </c>
@@ -5010,54 +5292,62 @@
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="28" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="L27" s="15" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="28" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+      <c r="O27" s="26"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+    </row>
+    <row r="28" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
         <v>3</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="C28" s="26">
         <v>150</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="15" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
-    </row>
-    <row r="29" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28" s="26"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+    </row>
+    <row r="29" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="25">
         <v>3</v>
       </c>
@@ -5071,31 +5361,35 @@
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29" s="26"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+    </row>
+    <row r="30" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="25">
         <v>3</v>
       </c>
@@ -5109,23 +5403,27 @@
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="15" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
-    </row>
-    <row r="31" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30" s="26"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+    </row>
+    <row r="31" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="25">
         <v>3</v>
       </c>
@@ -5139,21 +5437,25 @@
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="15" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
       <c r="N31" s="13"/>
-    </row>
-    <row r="32" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O31" s="26"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+    </row>
+    <row r="32" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="25">
         <v>3</v>
       </c>
@@ -5167,66 +5469,74 @@
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="N32" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="33" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" s="26"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+    </row>
+    <row r="33" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="25">
         <v>4</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="C33" s="26">
         <v>90</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
       <c r="N33" s="13"/>
-    </row>
-    <row r="34" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="26"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+    </row>
+    <row r="34" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="25">
         <v>4</v>
       </c>
@@ -5240,21 +5550,25 @@
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
       <c r="N34" s="13"/>
-    </row>
-    <row r="35" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34" s="26"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+    </row>
+    <row r="35" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="25">
         <v>4</v>
       </c>
@@ -5266,21 +5580,25 @@
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
       <c r="N35" s="13"/>
-    </row>
-    <row r="36" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O35" s="26"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+    </row>
+    <row r="36" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="25">
         <v>4</v>
       </c>
@@ -5292,23 +5610,27 @@
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
       <c r="N36" s="13"/>
-    </row>
-    <row r="37" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O36" s="26"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+    </row>
+    <row r="37" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="25">
         <v>4</v>
       </c>
@@ -5322,29 +5644,33 @@
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="J37" s="13"/>
       <c r="L37" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="N37" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="38" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O37" s="26"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+    </row>
+    <row r="38" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
         <v>4</v>
       </c>
@@ -5358,25 +5684,29 @@
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="28" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
       <c r="N38" s="13"/>
-    </row>
-    <row r="39" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="26"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+    </row>
+    <row r="39" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
         <v>4</v>
       </c>
@@ -5388,70 +5718,78 @@
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="28" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="N39" s="13" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="40" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39" s="26"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+    </row>
+    <row r="40" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
         <v>5</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="C40" s="26">
         <v>75</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="N40" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="41" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O40" s="26"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+    </row>
+    <row r="41" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
         <v>5</v>
       </c>
@@ -5465,21 +5803,25 @@
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="15" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
       <c r="N41" s="13"/>
-    </row>
-    <row r="42" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O41" s="26"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13"/>
+    </row>
+    <row r="42" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
         <v>5</v>
       </c>
@@ -5491,21 +5833,25 @@
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
       <c r="L42" s="13"/>
       <c r="M42" s="13"/>
       <c r="N42" s="13"/>
-    </row>
-    <row r="43" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O42" s="26"/>
+      <c r="P42" s="13"/>
+      <c r="Q42" s="13"/>
+      <c r="R42" s="13"/>
+    </row>
+    <row r="43" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
         <v>5</v>
       </c>
@@ -5517,23 +5863,27 @@
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="L43" s="13"/>
       <c r="M43" s="13"/>
       <c r="N43" s="13"/>
-    </row>
-    <row r="44" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="26"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="13"/>
+    </row>
+    <row r="44" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
         <v>5</v>
       </c>
@@ -5547,25 +5897,29 @@
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
       <c r="N44" s="13"/>
-    </row>
-    <row r="45" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44" s="26"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
+      <c r="R44" s="15"/>
+    </row>
+    <row r="45" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
         <v>5</v>
       </c>
@@ -5579,64 +5933,72 @@
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="28" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
       <c r="N45" s="13"/>
-    </row>
-    <row r="46" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O45" s="26"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15"/>
+      <c r="R45" s="15"/>
+    </row>
+    <row r="46" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
         <v>6</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C46" s="26">
         <v>180</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="28" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="N46" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="47" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="26"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+      <c r="R46" s="15"/>
+    </row>
+    <row r="47" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="25">
         <v>6</v>
       </c>
@@ -5650,21 +6012,25 @@
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="13" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
       <c r="N47" s="13"/>
-    </row>
-    <row r="48" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O47" s="26"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13"/>
+    </row>
+    <row r="48" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="25">
         <v>6</v>
       </c>
@@ -5676,21 +6042,25 @@
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
-    </row>
-    <row r="49" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O48" s="26"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="13"/>
+    </row>
+    <row r="49" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="25">
         <v>6</v>
       </c>
@@ -5702,21 +6072,25 @@
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="28" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="H49" s="15" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
-    </row>
-    <row r="50" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O49" s="26"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="13"/>
+    </row>
+    <row r="50" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="25">
         <v>6</v>
       </c>
@@ -5728,23 +6102,27 @@
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
-    </row>
-    <row r="51" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O50" s="26"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13"/>
+    </row>
+    <row r="51" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="25">
         <v>6</v>
       </c>
@@ -5758,31 +6136,35 @@
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="N51" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="52" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O51" s="26"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="R51" s="15"/>
+    </row>
+    <row r="52" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="25">
         <v>6</v>
       </c>
@@ -5796,62 +6178,70 @@
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="15" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
-    </row>
-    <row r="53" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O52" s="26"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+    </row>
+    <row r="53" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="25">
         <v>7</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="C53" s="26">
         <v>90</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="28" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="H53" s="15" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="N53" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="54" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O53" s="26"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="R53" s="15"/>
+    </row>
+    <row r="54" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="25">
         <v>7</v>
       </c>
@@ -5865,27 +6255,31 @@
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
       <c r="J54" s="13" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="N54" s="13" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="55" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O54" s="26"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
+    </row>
+    <row r="55" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="25">
         <v>7</v>
       </c>
@@ -5897,21 +6291,25 @@
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="H55" s="15" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
-    </row>
-    <row r="56" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O55" s="26"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13"/>
+    </row>
+    <row r="56" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="25">
         <v>7</v>
       </c>
@@ -5923,23 +6321,27 @@
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="28" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
       <c r="N56" s="13"/>
-    </row>
-    <row r="57" ht="31.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O56" s="26"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+      <c r="R56" s="13"/>
+    </row>
+    <row r="57" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="25">
         <v>7</v>
       </c>
@@ -5953,23 +6355,27 @@
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="28" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="15" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
       <c r="N57" s="13"/>
-    </row>
-    <row r="58" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O57" s="26"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="15"/>
+    </row>
+    <row r="58" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="30"/>
       <c r="B58" s="30"/>
       <c r="C58" s="31"/>
@@ -5985,8 +6391,12 @@
       <c r="L58" s="30"/>
       <c r="M58" s="30"/>
       <c r="N58" s="30"/>
-    </row>
-    <row r="59" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O58" s="31"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+    </row>
+    <row r="59" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="30"/>
       <c r="B59" s="30"/>
       <c r="C59" s="31"/>
@@ -6002,8 +6412,12 @@
       <c r="L59" s="30"/>
       <c r="M59" s="30"/>
       <c r="N59" s="30"/>
-    </row>
-    <row r="60" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O59" s="31"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="30"/>
+    </row>
+    <row r="60" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="30"/>
       <c r="B60" s="30"/>
       <c r="C60" s="31"/>
@@ -6019,8 +6433,12 @@
       <c r="L60" s="30"/>
       <c r="M60" s="30"/>
       <c r="N60" s="30"/>
-    </row>
-    <row r="61" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O60" s="31"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+    </row>
+    <row r="61" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="30"/>
       <c r="B61" s="30"/>
       <c r="C61" s="31"/>
@@ -6036,8 +6454,12 @@
       <c r="L61" s="30"/>
       <c r="M61" s="30"/>
       <c r="N61" s="30"/>
-    </row>
-    <row r="62" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O61" s="31"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+    </row>
+    <row r="62" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="30"/>
       <c r="B62" s="30"/>
       <c r="C62" s="31"/>
@@ -6053,8 +6475,12 @@
       <c r="L62" s="30"/>
       <c r="M62" s="30"/>
       <c r="N62" s="30"/>
-    </row>
-    <row r="63" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O62" s="31"/>
+      <c r="P62" s="30"/>
+      <c r="Q62" s="30"/>
+      <c r="R62" s="30"/>
+    </row>
+    <row r="63" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="30"/>
       <c r="B63" s="30"/>
       <c r="C63" s="31"/>
@@ -6070,8 +6496,12 @@
       <c r="L63" s="30"/>
       <c r="M63" s="30"/>
       <c r="N63" s="30"/>
-    </row>
-    <row r="64" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O63" s="31"/>
+      <c r="P63" s="30"/>
+      <c r="Q63" s="30"/>
+      <c r="R63" s="30"/>
+    </row>
+    <row r="64" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="30"/>
       <c r="B64" s="30"/>
       <c r="C64" s="31"/>
@@ -6087,8 +6517,12 @@
       <c r="L64" s="30"/>
       <c r="M64" s="30"/>
       <c r="N64" s="30"/>
-    </row>
-    <row r="65" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O64" s="31"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+    </row>
+    <row r="65" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="30"/>
       <c r="B65" s="30"/>
       <c r="C65" s="31"/>
@@ -6104,8 +6538,12 @@
       <c r="L65" s="30"/>
       <c r="M65" s="30"/>
       <c r="N65" s="30"/>
-    </row>
-    <row r="66" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O65" s="31"/>
+      <c r="P65" s="30"/>
+      <c r="Q65" s="30"/>
+      <c r="R65" s="30"/>
+    </row>
+    <row r="66" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="30"/>
       <c r="B66" s="30"/>
       <c r="C66" s="31"/>
@@ -6121,8 +6559,12 @@
       <c r="L66" s="30"/>
       <c r="M66" s="30"/>
       <c r="N66" s="30"/>
-    </row>
-    <row r="67" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O66" s="31"/>
+      <c r="P66" s="30"/>
+      <c r="Q66" s="30"/>
+      <c r="R66" s="30"/>
+    </row>
+    <row r="67" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="30"/>
       <c r="B67" s="30"/>
       <c r="C67" s="31"/>
@@ -6138,8 +6580,12 @@
       <c r="L67" s="30"/>
       <c r="M67" s="30"/>
       <c r="N67" s="30"/>
-    </row>
-    <row r="68" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O67" s="31"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+    </row>
+    <row r="68" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="30"/>
       <c r="B68" s="30"/>
       <c r="C68" s="31"/>
@@ -6155,8 +6601,12 @@
       <c r="L68" s="30"/>
       <c r="M68" s="30"/>
       <c r="N68" s="30"/>
-    </row>
-    <row r="69" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O68" s="31"/>
+      <c r="P68" s="30"/>
+      <c r="Q68" s="30"/>
+      <c r="R68" s="30"/>
+    </row>
+    <row r="69" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="30"/>
       <c r="B69" s="30"/>
       <c r="C69" s="31"/>
@@ -6172,8 +6622,12 @@
       <c r="L69" s="30"/>
       <c r="M69" s="30"/>
       <c r="N69" s="30"/>
-    </row>
-    <row r="70" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O69" s="31"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="30"/>
+      <c r="R69" s="30"/>
+    </row>
+    <row r="70" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="30"/>
       <c r="B70" s="30"/>
       <c r="C70" s="31"/>
@@ -6189,8 +6643,12 @@
       <c r="L70" s="30"/>
       <c r="M70" s="30"/>
       <c r="N70" s="30"/>
-    </row>
-    <row r="71" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O70" s="31"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+    </row>
+    <row r="71" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="30"/>
       <c r="B71" s="30"/>
       <c r="C71" s="31"/>
@@ -6206,8 +6664,12 @@
       <c r="L71" s="30"/>
       <c r="M71" s="30"/>
       <c r="N71" s="30"/>
-    </row>
-    <row r="72" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O71" s="31"/>
+      <c r="P71" s="30"/>
+      <c r="Q71" s="30"/>
+      <c r="R71" s="30"/>
+    </row>
+    <row r="72" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="30"/>
       <c r="B72" s="30"/>
       <c r="C72" s="31"/>
@@ -6223,8 +6685,12 @@
       <c r="L72" s="30"/>
       <c r="M72" s="30"/>
       <c r="N72" s="30"/>
-    </row>
-    <row r="73" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O72" s="31"/>
+      <c r="P72" s="30"/>
+      <c r="Q72" s="30"/>
+      <c r="R72" s="30"/>
+    </row>
+    <row r="73" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="30"/>
       <c r="B73" s="30"/>
       <c r="C73" s="31"/>
@@ -6240,8 +6706,12 @@
       <c r="L73" s="30"/>
       <c r="M73" s="30"/>
       <c r="N73" s="30"/>
-    </row>
-    <row r="74" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O73" s="31"/>
+      <c r="P73" s="30"/>
+      <c r="Q73" s="30"/>
+      <c r="R73" s="30"/>
+    </row>
+    <row r="74" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="30"/>
       <c r="B74" s="30"/>
       <c r="C74" s="31"/>
@@ -6257,8 +6727,12 @@
       <c r="L74" s="30"/>
       <c r="M74" s="30"/>
       <c r="N74" s="30"/>
-    </row>
-    <row r="75" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O74" s="31"/>
+      <c r="P74" s="30"/>
+      <c r="Q74" s="30"/>
+      <c r="R74" s="30"/>
+    </row>
+    <row r="75" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="30"/>
       <c r="B75" s="30"/>
       <c r="C75" s="31"/>
@@ -6274,8 +6748,12 @@
       <c r="L75" s="30"/>
       <c r="M75" s="30"/>
       <c r="N75" s="30"/>
-    </row>
-    <row r="76" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O75" s="31"/>
+      <c r="P75" s="30"/>
+      <c r="Q75" s="30"/>
+      <c r="R75" s="30"/>
+    </row>
+    <row r="76" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="30"/>
       <c r="B76" s="30"/>
       <c r="C76" s="31"/>
@@ -6291,8 +6769,12 @@
       <c r="L76" s="30"/>
       <c r="M76" s="30"/>
       <c r="N76" s="30"/>
-    </row>
-    <row r="77" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O76" s="31"/>
+      <c r="P76" s="30"/>
+      <c r="Q76" s="30"/>
+      <c r="R76" s="30"/>
+    </row>
+    <row r="77" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="30"/>
       <c r="B77" s="30"/>
       <c r="C77" s="31"/>
@@ -6308,8 +6790,12 @@
       <c r="L77" s="30"/>
       <c r="M77" s="30"/>
       <c r="N77" s="30"/>
-    </row>
-    <row r="78" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O77" s="31"/>
+      <c r="P77" s="30"/>
+      <c r="Q77" s="30"/>
+      <c r="R77" s="30"/>
+    </row>
+    <row r="78" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="30"/>
       <c r="B78" s="30"/>
       <c r="C78" s="31"/>
@@ -6325,8 +6811,12 @@
       <c r="L78" s="30"/>
       <c r="M78" s="30"/>
       <c r="N78" s="30"/>
-    </row>
-    <row r="79" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O78" s="31"/>
+      <c r="P78" s="30"/>
+      <c r="Q78" s="30"/>
+      <c r="R78" s="30"/>
+    </row>
+    <row r="79" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="30"/>
       <c r="B79" s="30"/>
       <c r="C79" s="31"/>
@@ -6342,8 +6832,12 @@
       <c r="L79" s="30"/>
       <c r="M79" s="30"/>
       <c r="N79" s="30"/>
-    </row>
-    <row r="80" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O79" s="31"/>
+      <c r="P79" s="30"/>
+      <c r="Q79" s="30"/>
+      <c r="R79" s="30"/>
+    </row>
+    <row r="80" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="30"/>
       <c r="B80" s="30"/>
       <c r="C80" s="31"/>
@@ -6359,8 +6853,12 @@
       <c r="L80" s="30"/>
       <c r="M80" s="30"/>
       <c r="N80" s="30"/>
-    </row>
-    <row r="81" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O80" s="31"/>
+      <c r="P80" s="30"/>
+      <c r="Q80" s="30"/>
+      <c r="R80" s="30"/>
+    </row>
+    <row r="81" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="30"/>
       <c r="B81" s="30"/>
       <c r="C81" s="31"/>
@@ -6376,8 +6874,12 @@
       <c r="L81" s="30"/>
       <c r="M81" s="30"/>
       <c r="N81" s="30"/>
-    </row>
-    <row r="82" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O81" s="31"/>
+      <c r="P81" s="30"/>
+      <c r="Q81" s="30"/>
+      <c r="R81" s="30"/>
+    </row>
+    <row r="82" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="30"/>
       <c r="B82" s="30"/>
       <c r="C82" s="31"/>
@@ -6393,8 +6895,12 @@
       <c r="L82" s="30"/>
       <c r="M82" s="30"/>
       <c r="N82" s="30"/>
-    </row>
-    <row r="83" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O82" s="31"/>
+      <c r="P82" s="30"/>
+      <c r="Q82" s="30"/>
+      <c r="R82" s="30"/>
+    </row>
+    <row r="83" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="30"/>
       <c r="B83" s="30"/>
       <c r="C83" s="31"/>
@@ -6410,8 +6916,12 @@
       <c r="L83" s="30"/>
       <c r="M83" s="30"/>
       <c r="N83" s="30"/>
-    </row>
-    <row r="84" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O83" s="31"/>
+      <c r="P83" s="30"/>
+      <c r="Q83" s="30"/>
+      <c r="R83" s="30"/>
+    </row>
+    <row r="84" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="30"/>
       <c r="B84" s="30"/>
       <c r="C84" s="31"/>
@@ -6427,8 +6937,12 @@
       <c r="L84" s="30"/>
       <c r="M84" s="30"/>
       <c r="N84" s="30"/>
-    </row>
-    <row r="85" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O84" s="31"/>
+      <c r="P84" s="30"/>
+      <c r="Q84" s="30"/>
+      <c r="R84" s="30"/>
+    </row>
+    <row r="85" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="30"/>
       <c r="B85" s="30"/>
       <c r="C85" s="31"/>
@@ -6444,8 +6958,12 @@
       <c r="L85" s="30"/>
       <c r="M85" s="30"/>
       <c r="N85" s="30"/>
-    </row>
-    <row r="86" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O85" s="31"/>
+      <c r="P85" s="30"/>
+      <c r="Q85" s="30"/>
+      <c r="R85" s="30"/>
+    </row>
+    <row r="86" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="30"/>
       <c r="B86" s="30"/>
       <c r="C86" s="31"/>
@@ -6461,8 +6979,12 @@
       <c r="L86" s="30"/>
       <c r="M86" s="30"/>
       <c r="N86" s="30"/>
-    </row>
-    <row r="87" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O86" s="31"/>
+      <c r="P86" s="30"/>
+      <c r="Q86" s="30"/>
+      <c r="R86" s="30"/>
+    </row>
+    <row r="87" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="30"/>
       <c r="B87" s="30"/>
       <c r="C87" s="31"/>
@@ -6478,8 +7000,12 @@
       <c r="L87" s="30"/>
       <c r="M87" s="30"/>
       <c r="N87" s="30"/>
-    </row>
-    <row r="88" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O87" s="31"/>
+      <c r="P87" s="30"/>
+      <c r="Q87" s="30"/>
+      <c r="R87" s="30"/>
+    </row>
+    <row r="88" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="30"/>
       <c r="B88" s="30"/>
       <c r="C88" s="31"/>
@@ -6495,8 +7021,12 @@
       <c r="L88" s="30"/>
       <c r="M88" s="30"/>
       <c r="N88" s="30"/>
-    </row>
-    <row r="89" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O88" s="31"/>
+      <c r="P88" s="30"/>
+      <c r="Q88" s="30"/>
+      <c r="R88" s="30"/>
+    </row>
+    <row r="89" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="30"/>
       <c r="B89" s="30"/>
       <c r="C89" s="31"/>
@@ -6512,8 +7042,12 @@
       <c r="L89" s="30"/>
       <c r="M89" s="30"/>
       <c r="N89" s="30"/>
-    </row>
-    <row r="90" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O89" s="31"/>
+      <c r="P89" s="30"/>
+      <c r="Q89" s="30"/>
+      <c r="R89" s="30"/>
+    </row>
+    <row r="90" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="30"/>
       <c r="B90" s="30"/>
       <c r="C90" s="31"/>
@@ -6529,8 +7063,12 @@
       <c r="L90" s="30"/>
       <c r="M90" s="30"/>
       <c r="N90" s="30"/>
-    </row>
-    <row r="91" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O90" s="31"/>
+      <c r="P90" s="30"/>
+      <c r="Q90" s="30"/>
+      <c r="R90" s="30"/>
+    </row>
+    <row r="91" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="30"/>
       <c r="B91" s="30"/>
       <c r="C91" s="31"/>
@@ -6546,8 +7084,12 @@
       <c r="L91" s="30"/>
       <c r="M91" s="30"/>
       <c r="N91" s="30"/>
-    </row>
-    <row r="92" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O91" s="31"/>
+      <c r="P91" s="30"/>
+      <c r="Q91" s="30"/>
+      <c r="R91" s="30"/>
+    </row>
+    <row r="92" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="30"/>
       <c r="B92" s="30"/>
       <c r="C92" s="31"/>
@@ -6563,8 +7105,12 @@
       <c r="L92" s="30"/>
       <c r="M92" s="30"/>
       <c r="N92" s="30"/>
-    </row>
-    <row r="93" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O92" s="31"/>
+      <c r="P92" s="30"/>
+      <c r="Q92" s="30"/>
+      <c r="R92" s="30"/>
+    </row>
+    <row r="93" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="30"/>
       <c r="B93" s="30"/>
       <c r="C93" s="31"/>
@@ -6580,8 +7126,12 @@
       <c r="L93" s="30"/>
       <c r="M93" s="30"/>
       <c r="N93" s="30"/>
-    </row>
-    <row r="94" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O93" s="31"/>
+      <c r="P93" s="30"/>
+      <c r="Q93" s="30"/>
+      <c r="R93" s="30"/>
+    </row>
+    <row r="94" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="30"/>
       <c r="B94" s="30"/>
       <c r="C94" s="31"/>
@@ -6597,8 +7147,12 @@
       <c r="L94" s="30"/>
       <c r="M94" s="30"/>
       <c r="N94" s="30"/>
-    </row>
-    <row r="95" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O94" s="31"/>
+      <c r="P94" s="30"/>
+      <c r="Q94" s="30"/>
+      <c r="R94" s="30"/>
+    </row>
+    <row r="95" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="30"/>
       <c r="B95" s="30"/>
       <c r="C95" s="31"/>
@@ -6614,8 +7168,12 @@
       <c r="L95" s="30"/>
       <c r="M95" s="30"/>
       <c r="N95" s="30"/>
-    </row>
-    <row r="96" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O95" s="31"/>
+      <c r="P95" s="30"/>
+      <c r="Q95" s="30"/>
+      <c r="R95" s="30"/>
+    </row>
+    <row r="96" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="30"/>
       <c r="B96" s="30"/>
       <c r="C96" s="31"/>
@@ -6631,8 +7189,12 @@
       <c r="L96" s="30"/>
       <c r="M96" s="30"/>
       <c r="N96" s="30"/>
-    </row>
-    <row r="97" ht="25.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O96" s="31"/>
+      <c r="P96" s="30"/>
+      <c r="Q96" s="30"/>
+      <c r="R96" s="30"/>
+    </row>
+    <row r="97" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="30"/>
       <c r="B97" s="30"/>
       <c r="C97" s="31"/>
@@ -6648,8 +7210,12 @@
       <c r="L97" s="30"/>
       <c r="M97" s="30"/>
       <c r="N97" s="30"/>
-    </row>
-    <row r="98" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O97" s="31"/>
+      <c r="P97" s="30"/>
+      <c r="Q97" s="30"/>
+      <c r="R97" s="30"/>
+    </row>
+    <row r="98" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="33"/>
@@ -6665,8 +7231,12 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
-    </row>
-    <row r="99" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O98" s="33"/>
+      <c r="P98" s="1"/>
+      <c r="Q98" s="1"/>
+      <c r="R98" s="1"/>
+    </row>
+    <row r="99" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="33"/>
@@ -6682,8 +7252,12 @@
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
-    </row>
-    <row r="100" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O99" s="33"/>
+      <c r="P99" s="1"/>
+      <c r="Q99" s="1"/>
+      <c r="R99" s="1"/>
+    </row>
+    <row r="100" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="33"/>
@@ -6699,8 +7273,12 @@
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
-    </row>
-    <row r="101" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O100" s="33"/>
+      <c r="P100" s="1"/>
+      <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+    </row>
+    <row r="101" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="33"/>
@@ -6716,8 +7294,12 @@
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
-    </row>
-    <row r="102" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O101" s="33"/>
+      <c r="P101" s="1"/>
+      <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+    </row>
+    <row r="102" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="33"/>
@@ -6733,8 +7315,12 @@
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
-    </row>
-    <row r="103" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O102" s="33"/>
+      <c r="P102" s="1"/>
+      <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+    </row>
+    <row r="103" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="33"/>
@@ -6750,8 +7336,12 @@
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
-    </row>
-    <row r="104" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O103" s="33"/>
+      <c r="P103" s="1"/>
+      <c r="Q103" s="1"/>
+      <c r="R103" s="1"/>
+    </row>
+    <row r="104" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="33"/>
@@ -6767,8 +7357,12 @@
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
-    </row>
-    <row r="105" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O104" s="33"/>
+      <c r="P104" s="1"/>
+      <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+    </row>
+    <row r="105" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="33"/>
@@ -6784,8 +7378,12 @@
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
-    </row>
-    <row r="106" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O105" s="33"/>
+      <c r="P105" s="1"/>
+      <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+    </row>
+    <row r="106" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="33"/>
@@ -6801,8 +7399,12 @@
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
-    </row>
-    <row r="107" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O106" s="33"/>
+      <c r="P106" s="1"/>
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+    </row>
+    <row r="107" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="33"/>
@@ -6818,8 +7420,12 @@
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
-    </row>
-    <row r="108" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O107" s="33"/>
+      <c r="P107" s="1"/>
+      <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+    </row>
+    <row r="108" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="33"/>
@@ -6835,8 +7441,12 @@
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
-    </row>
-    <row r="109" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O108" s="33"/>
+      <c r="P108" s="1"/>
+      <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+    </row>
+    <row r="109" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="33"/>
@@ -6852,8 +7462,12 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
-    </row>
-    <row r="110" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O109" s="33"/>
+      <c r="P109" s="1"/>
+      <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+    </row>
+    <row r="110" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="33"/>
@@ -6869,8 +7483,12 @@
       <c r="L110" s="1"/>
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
-    </row>
-    <row r="111" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O110" s="33"/>
+      <c r="P110" s="1"/>
+      <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+    </row>
+    <row r="111" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="33"/>
@@ -6886,8 +7504,12 @@
       <c r="L111" s="1"/>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
-    </row>
-    <row r="112" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O111" s="33"/>
+      <c r="P111" s="1"/>
+      <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+    </row>
+    <row r="112" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="33"/>
@@ -6903,8 +7525,12 @@
       <c r="L112" s="1"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
-    </row>
-    <row r="113" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O112" s="33"/>
+      <c r="P112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+    </row>
+    <row r="113" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="33"/>
@@ -6920,8 +7546,12 @@
       <c r="L113" s="1"/>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
-    </row>
-    <row r="114" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O113" s="33"/>
+      <c r="P113" s="1"/>
+      <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+    </row>
+    <row r="114" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="33"/>
@@ -6937,8 +7567,12 @@
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
       <c r="N114" s="1"/>
-    </row>
-    <row r="115" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O114" s="33"/>
+      <c r="P114" s="1"/>
+      <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+    </row>
+    <row r="115" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="33"/>
@@ -6954,8 +7588,12 @@
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
       <c r="N115" s="1"/>
-    </row>
-    <row r="116" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O115" s="33"/>
+      <c r="P115" s="1"/>
+      <c r="Q115" s="1"/>
+      <c r="R115" s="1"/>
+    </row>
+    <row r="116" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="33"/>
@@ -6971,8 +7609,12 @@
       <c r="L116" s="1"/>
       <c r="M116" s="1"/>
       <c r="N116" s="1"/>
-    </row>
-    <row r="117" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O116" s="33"/>
+      <c r="P116" s="1"/>
+      <c r="Q116" s="1"/>
+      <c r="R116" s="1"/>
+    </row>
+    <row r="117" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="33"/>
@@ -6988,8 +7630,12 @@
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
-    </row>
-    <row r="118" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O117" s="33"/>
+      <c r="P117" s="1"/>
+      <c r="Q117" s="1"/>
+      <c r="R117" s="1"/>
+    </row>
+    <row r="118" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="33"/>
@@ -7005,8 +7651,12 @@
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
-    </row>
-    <row r="119" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O118" s="33"/>
+      <c r="P118" s="1"/>
+      <c r="Q118" s="1"/>
+      <c r="R118" s="1"/>
+    </row>
+    <row r="119" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="33"/>
@@ -7022,8 +7672,12 @@
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
-    </row>
-    <row r="120" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O119" s="33"/>
+      <c r="P119" s="1"/>
+      <c r="Q119" s="1"/>
+      <c r="R119" s="1"/>
+    </row>
+    <row r="120" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="33"/>
@@ -7039,8 +7693,12 @@
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>
-    </row>
-    <row r="121" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O120" s="33"/>
+      <c r="P120" s="1"/>
+      <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+    </row>
+    <row r="121" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="33"/>
@@ -7056,8 +7714,12 @@
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
-    </row>
-    <row r="122" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O121" s="33"/>
+      <c r="P121" s="1"/>
+      <c r="Q121" s="1"/>
+      <c r="R121" s="1"/>
+    </row>
+    <row r="122" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="33"/>
@@ -7073,8 +7735,12 @@
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
-    </row>
-    <row r="123" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O122" s="33"/>
+      <c r="P122" s="1"/>
+      <c r="Q122" s="1"/>
+      <c r="R122" s="1"/>
+    </row>
+    <row r="123" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="33"/>
@@ -7090,8 +7756,12 @@
       <c r="L123" s="1"/>
       <c r="M123" s="1"/>
       <c r="N123" s="1"/>
-    </row>
-    <row r="124" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O123" s="33"/>
+      <c r="P123" s="1"/>
+      <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+    </row>
+    <row r="124" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="33"/>
@@ -7107,8 +7777,12 @@
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
       <c r="N124" s="1"/>
-    </row>
-    <row r="125" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O124" s="33"/>
+      <c r="P124" s="1"/>
+      <c r="Q124" s="1"/>
+      <c r="R124" s="1"/>
+    </row>
+    <row r="125" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="33"/>
@@ -7124,8 +7798,12 @@
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
       <c r="N125" s="1"/>
-    </row>
-    <row r="126" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O125" s="33"/>
+      <c r="P125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+    </row>
+    <row r="126" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="33"/>
@@ -7141,8 +7819,12 @@
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
-    </row>
-    <row r="127" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O126" s="33"/>
+      <c r="P126" s="1"/>
+      <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+    </row>
+    <row r="127" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="33"/>
@@ -7158,8 +7840,12 @@
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
-    </row>
-    <row r="128" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O127" s="33"/>
+      <c r="P127" s="1"/>
+      <c r="Q127" s="1"/>
+      <c r="R127" s="1"/>
+    </row>
+    <row r="128" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="33"/>
@@ -7175,8 +7861,12 @@
       <c r="L128" s="1"/>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
-    </row>
-    <row r="129" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O128" s="33"/>
+      <c r="P128" s="1"/>
+      <c r="Q128" s="1"/>
+      <c r="R128" s="1"/>
+    </row>
+    <row r="129" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="33"/>
@@ -7192,8 +7882,12 @@
       <c r="L129" s="1"/>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
-    </row>
-    <row r="130" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O129" s="33"/>
+      <c r="P129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+    </row>
+    <row r="130" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="33"/>
@@ -7209,8 +7903,12 @@
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
-    </row>
-    <row r="131" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O130" s="33"/>
+      <c r="P130" s="1"/>
+      <c r="Q130" s="1"/>
+      <c r="R130" s="1"/>
+    </row>
+    <row r="131" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="33"/>
@@ -7226,8 +7924,12 @@
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
-    </row>
-    <row r="132" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O131" s="33"/>
+      <c r="P131" s="1"/>
+      <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+    </row>
+    <row r="132" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="33"/>
@@ -7243,8 +7945,12 @@
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
-    </row>
-    <row r="133" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O132" s="33"/>
+      <c r="P132" s="1"/>
+      <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+    </row>
+    <row r="133" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="33"/>
@@ -7260,8 +7966,12 @@
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
-    </row>
-    <row r="134" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O133" s="33"/>
+      <c r="P133" s="1"/>
+      <c r="Q133" s="1"/>
+      <c r="R133" s="1"/>
+    </row>
+    <row r="134" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="33"/>
@@ -7277,8 +7987,12 @@
       <c r="L134" s="1"/>
       <c r="M134" s="1"/>
       <c r="N134" s="1"/>
-    </row>
-    <row r="135" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O134" s="33"/>
+      <c r="P134" s="1"/>
+      <c r="Q134" s="1"/>
+      <c r="R134" s="1"/>
+    </row>
+    <row r="135" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="33"/>
@@ -7294,8 +8008,12 @@
       <c r="L135" s="1"/>
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
-    </row>
-    <row r="136" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O135" s="33"/>
+      <c r="P135" s="1"/>
+      <c r="Q135" s="1"/>
+      <c r="R135" s="1"/>
+    </row>
+    <row r="136" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="33"/>
@@ -7311,8 +8029,12 @@
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
-    </row>
-    <row r="137" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O136" s="33"/>
+      <c r="P136" s="1"/>
+      <c r="Q136" s="1"/>
+      <c r="R136" s="1"/>
+    </row>
+    <row r="137" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="33"/>
@@ -7328,8 +8050,12 @@
       <c r="L137" s="1"/>
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
-    </row>
-    <row r="138" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O137" s="33"/>
+      <c r="P137" s="1"/>
+      <c r="Q137" s="1"/>
+      <c r="R137" s="1"/>
+    </row>
+    <row r="138" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="33"/>
@@ -7345,8 +8071,12 @@
       <c r="L138" s="1"/>
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
-    </row>
-    <row r="139" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O138" s="33"/>
+      <c r="P138" s="1"/>
+      <c r="Q138" s="1"/>
+      <c r="R138" s="1"/>
+    </row>
+    <row r="139" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="33"/>
@@ -7362,8 +8092,12 @@
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
-    </row>
-    <row r="140" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O139" s="33"/>
+      <c r="P139" s="1"/>
+      <c r="Q139" s="1"/>
+      <c r="R139" s="1"/>
+    </row>
+    <row r="140" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="33"/>
@@ -7379,8 +8113,12 @@
       <c r="L140" s="1"/>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
-    </row>
-    <row r="141" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O140" s="33"/>
+      <c r="P140" s="1"/>
+      <c r="Q140" s="1"/>
+      <c r="R140" s="1"/>
+    </row>
+    <row r="141" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="33"/>
@@ -7396,8 +8134,12 @@
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
       <c r="N141" s="1"/>
-    </row>
-    <row r="142" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O141" s="33"/>
+      <c r="P141" s="1"/>
+      <c r="Q141" s="1"/>
+      <c r="R141" s="1"/>
+    </row>
+    <row r="142" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="33"/>
@@ -7413,8 +8155,12 @@
       <c r="L142" s="1"/>
       <c r="M142" s="1"/>
       <c r="N142" s="1"/>
-    </row>
-    <row r="143" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O142" s="33"/>
+      <c r="P142" s="1"/>
+      <c r="Q142" s="1"/>
+      <c r="R142" s="1"/>
+    </row>
+    <row r="143" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="33"/>
@@ -7430,8 +8176,12 @@
       <c r="L143" s="1"/>
       <c r="M143" s="1"/>
       <c r="N143" s="1"/>
-    </row>
-    <row r="144" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O143" s="33"/>
+      <c r="P143" s="1"/>
+      <c r="Q143" s="1"/>
+      <c r="R143" s="1"/>
+    </row>
+    <row r="144" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="33"/>
@@ -7447,8 +8197,12 @@
       <c r="L144" s="1"/>
       <c r="M144" s="1"/>
       <c r="N144" s="1"/>
-    </row>
-    <row r="145" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O144" s="33"/>
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
+      <c r="R144" s="1"/>
+    </row>
+    <row r="145" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="33"/>
@@ -7464,8 +8218,12 @@
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
       <c r="N145" s="1"/>
-    </row>
-    <row r="146" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O145" s="33"/>
+      <c r="P145" s="1"/>
+      <c r="Q145" s="1"/>
+      <c r="R145" s="1"/>
+    </row>
+    <row r="146" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="33"/>
@@ -7481,8 +8239,12 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
-    </row>
-    <row r="147" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O146" s="33"/>
+      <c r="P146" s="1"/>
+      <c r="Q146" s="1"/>
+      <c r="R146" s="1"/>
+    </row>
+    <row r="147" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="33"/>
@@ -7498,8 +8260,12 @@
       <c r="L147" s="1"/>
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
-    </row>
-    <row r="148" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O147" s="33"/>
+      <c r="P147" s="1"/>
+      <c r="Q147" s="1"/>
+      <c r="R147" s="1"/>
+    </row>
+    <row r="148" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="33"/>
@@ -7515,8 +8281,12 @@
       <c r="L148" s="1"/>
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
-    </row>
-    <row r="149" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O148" s="33"/>
+      <c r="P148" s="1"/>
+      <c r="Q148" s="1"/>
+      <c r="R148" s="1"/>
+    </row>
+    <row r="149" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="33"/>
@@ -7532,8 +8302,12 @@
       <c r="L149" s="1"/>
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
-    </row>
-    <row r="150" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O149" s="33"/>
+      <c r="P149" s="1"/>
+      <c r="Q149" s="1"/>
+      <c r="R149" s="1"/>
+    </row>
+    <row r="150" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="33"/>
@@ -7549,8 +8323,12 @@
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
       <c r="N150" s="1"/>
-    </row>
-    <row r="151" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O150" s="33"/>
+      <c r="P150" s="1"/>
+      <c r="Q150" s="1"/>
+      <c r="R150" s="1"/>
+    </row>
+    <row r="151" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="33"/>
@@ -7566,8 +8344,12 @@
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
       <c r="N151" s="1"/>
-    </row>
-    <row r="152" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O151" s="33"/>
+      <c r="P151" s="1"/>
+      <c r="Q151" s="1"/>
+      <c r="R151" s="1"/>
+    </row>
+    <row r="152" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="33"/>
@@ -7583,8 +8365,12 @@
       <c r="L152" s="1"/>
       <c r="M152" s="1"/>
       <c r="N152" s="1"/>
-    </row>
-    <row r="153" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O152" s="33"/>
+      <c r="P152" s="1"/>
+      <c r="Q152" s="1"/>
+      <c r="R152" s="1"/>
+    </row>
+    <row r="153" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="33"/>
@@ -7600,8 +8386,12 @@
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
       <c r="N153" s="1"/>
-    </row>
-    <row r="154" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O153" s="33"/>
+      <c r="P153" s="1"/>
+      <c r="Q153" s="1"/>
+      <c r="R153" s="1"/>
+    </row>
+    <row r="154" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="33"/>
@@ -7617,8 +8407,12 @@
       <c r="L154" s="1"/>
       <c r="M154" s="1"/>
       <c r="N154" s="1"/>
-    </row>
-    <row r="155" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O154" s="33"/>
+      <c r="P154" s="1"/>
+      <c r="Q154" s="1"/>
+      <c r="R154" s="1"/>
+    </row>
+    <row r="155" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="33"/>
@@ -7634,8 +8428,12 @@
       <c r="L155" s="1"/>
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
-    </row>
-    <row r="156" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O155" s="33"/>
+      <c r="P155" s="1"/>
+      <c r="Q155" s="1"/>
+      <c r="R155" s="1"/>
+    </row>
+    <row r="156" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="33"/>
@@ -7651,8 +8449,12 @@
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
-    </row>
-    <row r="157" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O156" s="33"/>
+      <c r="P156" s="1"/>
+      <c r="Q156" s="1"/>
+      <c r="R156" s="1"/>
+    </row>
+    <row r="157" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="33"/>
@@ -7668,8 +8470,12 @@
       <c r="L157" s="1"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
-    </row>
-    <row r="158" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O157" s="33"/>
+      <c r="P157" s="1"/>
+      <c r="Q157" s="1"/>
+      <c r="R157" s="1"/>
+    </row>
+    <row r="158" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="33"/>
@@ -7685,8 +8491,12 @@
       <c r="L158" s="1"/>
       <c r="M158" s="1"/>
       <c r="N158" s="1"/>
-    </row>
-    <row r="159" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O158" s="33"/>
+      <c r="P158" s="1"/>
+      <c r="Q158" s="1"/>
+      <c r="R158" s="1"/>
+    </row>
+    <row r="159" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="33"/>
@@ -7702,8 +8512,12 @@
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
-    </row>
-    <row r="160" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O159" s="33"/>
+      <c r="P159" s="1"/>
+      <c r="Q159" s="1"/>
+      <c r="R159" s="1"/>
+    </row>
+    <row r="160" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="33"/>
@@ -7719,8 +8533,12 @@
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
-    </row>
-    <row r="161" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O160" s="33"/>
+      <c r="P160" s="1"/>
+      <c r="Q160" s="1"/>
+      <c r="R160" s="1"/>
+    </row>
+    <row r="161" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="33"/>
@@ -7736,8 +8554,12 @@
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
-    </row>
-    <row r="162" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O161" s="33"/>
+      <c r="P161" s="1"/>
+      <c r="Q161" s="1"/>
+      <c r="R161" s="1"/>
+    </row>
+    <row r="162" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="33"/>
@@ -7753,8 +8575,12 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
-    </row>
-    <row r="163" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O162" s="33"/>
+      <c r="P162" s="1"/>
+      <c r="Q162" s="1"/>
+      <c r="R162" s="1"/>
+    </row>
+    <row r="163" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="33"/>
@@ -7770,8 +8596,12 @@
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
-    </row>
-    <row r="164" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O163" s="33"/>
+      <c r="P163" s="1"/>
+      <c r="Q163" s="1"/>
+      <c r="R163" s="1"/>
+    </row>
+    <row r="164" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="33"/>
@@ -7787,8 +8617,12 @@
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
       <c r="N164" s="1"/>
-    </row>
-    <row r="165" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O164" s="33"/>
+      <c r="P164" s="1"/>
+      <c r="Q164" s="1"/>
+      <c r="R164" s="1"/>
+    </row>
+    <row r="165" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="33"/>
@@ -7804,8 +8638,12 @@
       <c r="L165" s="1"/>
       <c r="M165" s="1"/>
       <c r="N165" s="1"/>
-    </row>
-    <row r="166" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O165" s="33"/>
+      <c r="P165" s="1"/>
+      <c r="Q165" s="1"/>
+      <c r="R165" s="1"/>
+    </row>
+    <row r="166" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="33"/>
@@ -7821,8 +8659,12 @@
       <c r="L166" s="1"/>
       <c r="M166" s="1"/>
       <c r="N166" s="1"/>
-    </row>
-    <row r="167" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O166" s="33"/>
+      <c r="P166" s="1"/>
+      <c r="Q166" s="1"/>
+      <c r="R166" s="1"/>
+    </row>
+    <row r="167" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="33"/>
@@ -7838,8 +8680,12 @@
       <c r="L167" s="1"/>
       <c r="M167" s="1"/>
       <c r="N167" s="1"/>
-    </row>
-    <row r="168" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O167" s="33"/>
+      <c r="P167" s="1"/>
+      <c r="Q167" s="1"/>
+      <c r="R167" s="1"/>
+    </row>
+    <row r="168" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="33"/>
@@ -7855,8 +8701,12 @@
       <c r="L168" s="1"/>
       <c r="M168" s="1"/>
       <c r="N168" s="1"/>
-    </row>
-    <row r="169" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O168" s="33"/>
+      <c r="P168" s="1"/>
+      <c r="Q168" s="1"/>
+      <c r="R168" s="1"/>
+    </row>
+    <row r="169" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="33"/>
@@ -7872,8 +8722,12 @@
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
       <c r="N169" s="1"/>
-    </row>
-    <row r="170" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O169" s="33"/>
+      <c r="P169" s="1"/>
+      <c r="Q169" s="1"/>
+      <c r="R169" s="1"/>
+    </row>
+    <row r="170" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="33"/>
@@ -7889,8 +8743,12 @@
       <c r="L170" s="1"/>
       <c r="M170" s="1"/>
       <c r="N170" s="1"/>
-    </row>
-    <row r="171" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O170" s="33"/>
+      <c r="P170" s="1"/>
+      <c r="Q170" s="1"/>
+      <c r="R170" s="1"/>
+    </row>
+    <row r="171" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="33"/>
@@ -7906,8 +8764,12 @@
       <c r="L171" s="1"/>
       <c r="M171" s="1"/>
       <c r="N171" s="1"/>
-    </row>
-    <row r="172" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O171" s="33"/>
+      <c r="P171" s="1"/>
+      <c r="Q171" s="1"/>
+      <c r="R171" s="1"/>
+    </row>
+    <row r="172" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="33"/>
@@ -7923,8 +8785,12 @@
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
       <c r="N172" s="1"/>
-    </row>
-    <row r="173" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O172" s="33"/>
+      <c r="P172" s="1"/>
+      <c r="Q172" s="1"/>
+      <c r="R172" s="1"/>
+    </row>
+    <row r="173" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="33"/>
@@ -7940,8 +8806,12 @@
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
       <c r="N173" s="1"/>
-    </row>
-    <row r="174" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O173" s="33"/>
+      <c r="P173" s="1"/>
+      <c r="Q173" s="1"/>
+      <c r="R173" s="1"/>
+    </row>
+    <row r="174" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="33"/>
@@ -7957,8 +8827,12 @@
       <c r="L174" s="1"/>
       <c r="M174" s="1"/>
       <c r="N174" s="1"/>
-    </row>
-    <row r="175" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O174" s="33"/>
+      <c r="P174" s="1"/>
+      <c r="Q174" s="1"/>
+      <c r="R174" s="1"/>
+    </row>
+    <row r="175" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="33"/>
@@ -7974,8 +8848,12 @@
       <c r="L175" s="1"/>
       <c r="M175" s="1"/>
       <c r="N175" s="1"/>
-    </row>
-    <row r="176" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O175" s="33"/>
+      <c r="P175" s="1"/>
+      <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
+    </row>
+    <row r="176" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="33"/>
@@ -7991,8 +8869,12 @@
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
-    </row>
-    <row r="177" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O176" s="33"/>
+      <c r="P176" s="1"/>
+      <c r="Q176" s="1"/>
+      <c r="R176" s="1"/>
+    </row>
+    <row r="177" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="33"/>
@@ -8008,8 +8890,12 @@
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
       <c r="N177" s="1"/>
-    </row>
-    <row r="178" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O177" s="33"/>
+      <c r="P177" s="1"/>
+      <c r="Q177" s="1"/>
+      <c r="R177" s="1"/>
+    </row>
+    <row r="178" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="33"/>
@@ -8025,8 +8911,12 @@
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
-    </row>
-    <row r="179" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O178" s="33"/>
+      <c r="P178" s="1"/>
+      <c r="Q178" s="1"/>
+      <c r="R178" s="1"/>
+    </row>
+    <row r="179" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="33"/>
@@ -8042,8 +8932,12 @@
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
       <c r="N179" s="1"/>
-    </row>
-    <row r="180" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O179" s="33"/>
+      <c r="P179" s="1"/>
+      <c r="Q179" s="1"/>
+      <c r="R179" s="1"/>
+    </row>
+    <row r="180" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="33"/>
@@ -8059,8 +8953,12 @@
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
       <c r="N180" s="1"/>
-    </row>
-    <row r="181" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O180" s="33"/>
+      <c r="P180" s="1"/>
+      <c r="Q180" s="1"/>
+      <c r="R180" s="1"/>
+    </row>
+    <row r="181" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="33"/>
@@ -8076,8 +8974,12 @@
       <c r="L181" s="1"/>
       <c r="M181" s="1"/>
       <c r="N181" s="1"/>
-    </row>
-    <row r="182" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O181" s="33"/>
+      <c r="P181" s="1"/>
+      <c r="Q181" s="1"/>
+      <c r="R181" s="1"/>
+    </row>
+    <row r="182" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="33"/>
@@ -8093,8 +8995,12 @@
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
       <c r="N182" s="1"/>
-    </row>
-    <row r="183" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O182" s="33"/>
+      <c r="P182" s="1"/>
+      <c r="Q182" s="1"/>
+      <c r="R182" s="1"/>
+    </row>
+    <row r="183" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="33"/>
@@ -8110,8 +9016,12 @@
       <c r="L183" s="1"/>
       <c r="M183" s="1"/>
       <c r="N183" s="1"/>
-    </row>
-    <row r="184" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O183" s="33"/>
+      <c r="P183" s="1"/>
+      <c r="Q183" s="1"/>
+      <c r="R183" s="1"/>
+    </row>
+    <row r="184" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="33"/>
@@ -8127,8 +9037,12 @@
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
       <c r="N184" s="1"/>
-    </row>
-    <row r="185" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O184" s="33"/>
+      <c r="P184" s="1"/>
+      <c r="Q184" s="1"/>
+      <c r="R184" s="1"/>
+    </row>
+    <row r="185" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="33"/>
@@ -8144,8 +9058,12 @@
       <c r="L185" s="1"/>
       <c r="M185" s="1"/>
       <c r="N185" s="1"/>
-    </row>
-    <row r="186" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O185" s="33"/>
+      <c r="P185" s="1"/>
+      <c r="Q185" s="1"/>
+      <c r="R185" s="1"/>
+    </row>
+    <row r="186" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="33"/>
@@ -8161,8 +9079,12 @@
       <c r="L186" s="1"/>
       <c r="M186" s="1"/>
       <c r="N186" s="1"/>
-    </row>
-    <row r="187" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O186" s="33"/>
+      <c r="P186" s="1"/>
+      <c r="Q186" s="1"/>
+      <c r="R186" s="1"/>
+    </row>
+    <row r="187" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="33"/>
@@ -8178,8 +9100,12 @@
       <c r="L187" s="1"/>
       <c r="M187" s="1"/>
       <c r="N187" s="1"/>
-    </row>
-    <row r="188" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O187" s="33"/>
+      <c r="P187" s="1"/>
+      <c r="Q187" s="1"/>
+      <c r="R187" s="1"/>
+    </row>
+    <row r="188" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="33"/>
@@ -8195,8 +9121,12 @@
       <c r="L188" s="1"/>
       <c r="M188" s="1"/>
       <c r="N188" s="1"/>
-    </row>
-    <row r="189" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O188" s="33"/>
+      <c r="P188" s="1"/>
+      <c r="Q188" s="1"/>
+      <c r="R188" s="1"/>
+    </row>
+    <row r="189" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="33"/>
@@ -8212,8 +9142,12 @@
       <c r="L189" s="1"/>
       <c r="M189" s="1"/>
       <c r="N189" s="1"/>
-    </row>
-    <row r="190" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O189" s="33"/>
+      <c r="P189" s="1"/>
+      <c r="Q189" s="1"/>
+      <c r="R189" s="1"/>
+    </row>
+    <row r="190" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="33"/>
@@ -8229,8 +9163,12 @@
       <c r="L190" s="1"/>
       <c r="M190" s="1"/>
       <c r="N190" s="1"/>
-    </row>
-    <row r="191" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O190" s="33"/>
+      <c r="P190" s="1"/>
+      <c r="Q190" s="1"/>
+      <c r="R190" s="1"/>
+    </row>
+    <row r="191" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="33"/>
@@ -8246,8 +9184,12 @@
       <c r="L191" s="1"/>
       <c r="M191" s="1"/>
       <c r="N191" s="1"/>
-    </row>
-    <row r="192" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O191" s="33"/>
+      <c r="P191" s="1"/>
+      <c r="Q191" s="1"/>
+      <c r="R191" s="1"/>
+    </row>
+    <row r="192" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="33"/>
@@ -8263,8 +9205,12 @@
       <c r="L192" s="1"/>
       <c r="M192" s="1"/>
       <c r="N192" s="1"/>
-    </row>
-    <row r="193" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O192" s="33"/>
+      <c r="P192" s="1"/>
+      <c r="Q192" s="1"/>
+      <c r="R192" s="1"/>
+    </row>
+    <row r="193" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="33"/>
@@ -8280,8 +9226,12 @@
       <c r="L193" s="1"/>
       <c r="M193" s="1"/>
       <c r="N193" s="1"/>
-    </row>
-    <row r="194" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O193" s="33"/>
+      <c r="P193" s="1"/>
+      <c r="Q193" s="1"/>
+      <c r="R193" s="1"/>
+    </row>
+    <row r="194" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="33"/>
@@ -8297,8 +9247,12 @@
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
       <c r="N194" s="1"/>
-    </row>
-    <row r="195" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O194" s="33"/>
+      <c r="P194" s="1"/>
+      <c r="Q194" s="1"/>
+      <c r="R194" s="1"/>
+    </row>
+    <row r="195" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="33"/>
@@ -8314,8 +9268,12 @@
       <c r="L195" s="1"/>
       <c r="M195" s="1"/>
       <c r="N195" s="1"/>
-    </row>
-    <row r="196" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O195" s="33"/>
+      <c r="P195" s="1"/>
+      <c r="Q195" s="1"/>
+      <c r="R195" s="1"/>
+    </row>
+    <row r="196" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="33"/>
@@ -8331,8 +9289,12 @@
       <c r="L196" s="1"/>
       <c r="M196" s="1"/>
       <c r="N196" s="1"/>
-    </row>
-    <row r="197" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O196" s="33"/>
+      <c r="P196" s="1"/>
+      <c r="Q196" s="1"/>
+      <c r="R196" s="1"/>
+    </row>
+    <row r="197" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="33"/>
@@ -8348,8 +9310,12 @@
       <c r="L197" s="1"/>
       <c r="M197" s="1"/>
       <c r="N197" s="1"/>
-    </row>
-    <row r="198" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O197" s="33"/>
+      <c r="P197" s="1"/>
+      <c r="Q197" s="1"/>
+      <c r="R197" s="1"/>
+    </row>
+    <row r="198" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="33"/>
@@ -8365,8 +9331,12 @@
       <c r="L198" s="1"/>
       <c r="M198" s="1"/>
       <c r="N198" s="1"/>
-    </row>
-    <row r="199" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O198" s="33"/>
+      <c r="P198" s="1"/>
+      <c r="Q198" s="1"/>
+      <c r="R198" s="1"/>
+    </row>
+    <row r="199" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="33"/>
@@ -8382,8 +9352,12 @@
       <c r="L199" s="1"/>
       <c r="M199" s="1"/>
       <c r="N199" s="1"/>
-    </row>
-    <row r="200" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O199" s="33"/>
+      <c r="P199" s="1"/>
+      <c r="Q199" s="1"/>
+      <c r="R199" s="1"/>
+    </row>
+    <row r="200" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="33"/>
@@ -8399,8 +9373,12 @@
       <c r="L200" s="1"/>
       <c r="M200" s="1"/>
       <c r="N200" s="1"/>
-    </row>
-    <row r="201" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O200" s="33"/>
+      <c r="P200" s="1"/>
+      <c r="Q200" s="1"/>
+      <c r="R200" s="1"/>
+    </row>
+    <row r="201" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="33"/>
@@ -8416,8 +9394,12 @@
       <c r="L201" s="1"/>
       <c r="M201" s="1"/>
       <c r="N201" s="1"/>
-    </row>
-    <row r="202" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O201" s="33"/>
+      <c r="P201" s="1"/>
+      <c r="Q201" s="1"/>
+      <c r="R201" s="1"/>
+    </row>
+    <row r="202" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="33"/>
@@ -8433,8 +9415,12 @@
       <c r="L202" s="1"/>
       <c r="M202" s="1"/>
       <c r="N202" s="1"/>
-    </row>
-    <row r="203" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O202" s="33"/>
+      <c r="P202" s="1"/>
+      <c r="Q202" s="1"/>
+      <c r="R202" s="1"/>
+    </row>
+    <row r="203" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="33"/>
@@ -8450,8 +9436,12 @@
       <c r="L203" s="1"/>
       <c r="M203" s="1"/>
       <c r="N203" s="1"/>
-    </row>
-    <row r="204" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O203" s="33"/>
+      <c r="P203" s="1"/>
+      <c r="Q203" s="1"/>
+      <c r="R203" s="1"/>
+    </row>
+    <row r="204" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="33"/>
@@ -8467,8 +9457,12 @@
       <c r="L204" s="1"/>
       <c r="M204" s="1"/>
       <c r="N204" s="1"/>
-    </row>
-    <row r="205" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O204" s="33"/>
+      <c r="P204" s="1"/>
+      <c r="Q204" s="1"/>
+      <c r="R204" s="1"/>
+    </row>
+    <row r="205" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="33"/>
@@ -8484,8 +9478,12 @@
       <c r="L205" s="1"/>
       <c r="M205" s="1"/>
       <c r="N205" s="1"/>
-    </row>
-    <row r="206" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O205" s="33"/>
+      <c r="P205" s="1"/>
+      <c r="Q205" s="1"/>
+      <c r="R205" s="1"/>
+    </row>
+    <row r="206" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="33"/>
@@ -8501,8 +9499,12 @@
       <c r="L206" s="1"/>
       <c r="M206" s="1"/>
       <c r="N206" s="1"/>
-    </row>
-    <row r="207" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O206" s="33"/>
+      <c r="P206" s="1"/>
+      <c r="Q206" s="1"/>
+      <c r="R206" s="1"/>
+    </row>
+    <row r="207" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="33"/>
@@ -8518,8 +9520,12 @@
       <c r="L207" s="1"/>
       <c r="M207" s="1"/>
       <c r="N207" s="1"/>
-    </row>
-    <row r="208" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O207" s="33"/>
+      <c r="P207" s="1"/>
+      <c r="Q207" s="1"/>
+      <c r="R207" s="1"/>
+    </row>
+    <row r="208" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="33"/>
@@ -8535,8 +9541,12 @@
       <c r="L208" s="1"/>
       <c r="M208" s="1"/>
       <c r="N208" s="1"/>
-    </row>
-    <row r="209" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O208" s="33"/>
+      <c r="P208" s="1"/>
+      <c r="Q208" s="1"/>
+      <c r="R208" s="1"/>
+    </row>
+    <row r="209" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="33"/>
@@ -8552,8 +9562,12 @@
       <c r="L209" s="1"/>
       <c r="M209" s="1"/>
       <c r="N209" s="1"/>
-    </row>
-    <row r="210" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O209" s="33"/>
+      <c r="P209" s="1"/>
+      <c r="Q209" s="1"/>
+      <c r="R209" s="1"/>
+    </row>
+    <row r="210" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="33"/>
@@ -8569,8 +9583,12 @@
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
       <c r="N210" s="1"/>
-    </row>
-    <row r="211" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O210" s="33"/>
+      <c r="P210" s="1"/>
+      <c r="Q210" s="1"/>
+      <c r="R210" s="1"/>
+    </row>
+    <row r="211" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="33"/>
@@ -8586,8 +9604,12 @@
       <c r="L211" s="1"/>
       <c r="M211" s="1"/>
       <c r="N211" s="1"/>
-    </row>
-    <row r="212" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O211" s="33"/>
+      <c r="P211" s="1"/>
+      <c r="Q211" s="1"/>
+      <c r="R211" s="1"/>
+    </row>
+    <row r="212" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="33"/>
@@ -8603,8 +9625,12 @@
       <c r="L212" s="1"/>
       <c r="M212" s="1"/>
       <c r="N212" s="1"/>
-    </row>
-    <row r="213" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O212" s="33"/>
+      <c r="P212" s="1"/>
+      <c r="Q212" s="1"/>
+      <c r="R212" s="1"/>
+    </row>
+    <row r="213" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="33"/>
@@ -8620,8 +9646,12 @@
       <c r="L213" s="1"/>
       <c r="M213" s="1"/>
       <c r="N213" s="1"/>
-    </row>
-    <row r="214" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O213" s="33"/>
+      <c r="P213" s="1"/>
+      <c r="Q213" s="1"/>
+      <c r="R213" s="1"/>
+    </row>
+    <row r="214" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="33"/>
@@ -8637,8 +9667,12 @@
       <c r="L214" s="1"/>
       <c r="M214" s="1"/>
       <c r="N214" s="1"/>
-    </row>
-    <row r="215" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O214" s="33"/>
+      <c r="P214" s="1"/>
+      <c r="Q214" s="1"/>
+      <c r="R214" s="1"/>
+    </row>
+    <row r="215" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="33"/>
@@ -8654,8 +9688,12 @@
       <c r="L215" s="1"/>
       <c r="M215" s="1"/>
       <c r="N215" s="1"/>
-    </row>
-    <row r="216" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O215" s="33"/>
+      <c r="P215" s="1"/>
+      <c r="Q215" s="1"/>
+      <c r="R215" s="1"/>
+    </row>
+    <row r="216" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="33"/>
@@ -8671,8 +9709,12 @@
       <c r="L216" s="1"/>
       <c r="M216" s="1"/>
       <c r="N216" s="1"/>
-    </row>
-    <row r="217" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O216" s="33"/>
+      <c r="P216" s="1"/>
+      <c r="Q216" s="1"/>
+      <c r="R216" s="1"/>
+    </row>
+    <row r="217" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="33"/>
@@ -8688,8 +9730,12 @@
       <c r="L217" s="1"/>
       <c r="M217" s="1"/>
       <c r="N217" s="1"/>
-    </row>
-    <row r="218" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O217" s="33"/>
+      <c r="P217" s="1"/>
+      <c r="Q217" s="1"/>
+      <c r="R217" s="1"/>
+    </row>
+    <row r="218" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="33"/>
@@ -8705,8 +9751,12 @@
       <c r="L218" s="1"/>
       <c r="M218" s="1"/>
       <c r="N218" s="1"/>
-    </row>
-    <row r="219" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O218" s="33"/>
+      <c r="P218" s="1"/>
+      <c r="Q218" s="1"/>
+      <c r="R218" s="1"/>
+    </row>
+    <row r="219" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="33"/>
@@ -8722,8 +9772,12 @@
       <c r="L219" s="1"/>
       <c r="M219" s="1"/>
       <c r="N219" s="1"/>
-    </row>
-    <row r="220" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O219" s="33"/>
+      <c r="P219" s="1"/>
+      <c r="Q219" s="1"/>
+      <c r="R219" s="1"/>
+    </row>
+    <row r="220" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="33"/>
@@ -8739,8 +9793,12 @@
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
       <c r="N220" s="1"/>
-    </row>
-    <row r="221" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O220" s="33"/>
+      <c r="P220" s="1"/>
+      <c r="Q220" s="1"/>
+      <c r="R220" s="1"/>
+    </row>
+    <row r="221" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="33"/>
@@ -8756,8 +9814,12 @@
       <c r="L221" s="1"/>
       <c r="M221" s="1"/>
       <c r="N221" s="1"/>
-    </row>
-    <row r="222" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O221" s="33"/>
+      <c r="P221" s="1"/>
+      <c r="Q221" s="1"/>
+      <c r="R221" s="1"/>
+    </row>
+    <row r="222" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="33"/>
@@ -8773,8 +9835,12 @@
       <c r="L222" s="1"/>
       <c r="M222" s="1"/>
       <c r="N222" s="1"/>
-    </row>
-    <row r="223" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O222" s="33"/>
+      <c r="P222" s="1"/>
+      <c r="Q222" s="1"/>
+      <c r="R222" s="1"/>
+    </row>
+    <row r="223" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="33"/>
@@ -8790,8 +9856,12 @@
       <c r="L223" s="1"/>
       <c r="M223" s="1"/>
       <c r="N223" s="1"/>
-    </row>
-    <row r="224" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O223" s="33"/>
+      <c r="P223" s="1"/>
+      <c r="Q223" s="1"/>
+      <c r="R223" s="1"/>
+    </row>
+    <row r="224" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="33"/>
@@ -8807,8 +9877,12 @@
       <c r="L224" s="1"/>
       <c r="M224" s="1"/>
       <c r="N224" s="1"/>
-    </row>
-    <row r="225" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O224" s="33"/>
+      <c r="P224" s="1"/>
+      <c r="Q224" s="1"/>
+      <c r="R224" s="1"/>
+    </row>
+    <row r="225" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="33"/>
@@ -8824,8 +9898,12 @@
       <c r="L225" s="1"/>
       <c r="M225" s="1"/>
       <c r="N225" s="1"/>
-    </row>
-    <row r="226" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O225" s="33"/>
+      <c r="P225" s="1"/>
+      <c r="Q225" s="1"/>
+      <c r="R225" s="1"/>
+    </row>
+    <row r="226" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="33"/>
@@ -8841,8 +9919,12 @@
       <c r="L226" s="1"/>
       <c r="M226" s="1"/>
       <c r="N226" s="1"/>
-    </row>
-    <row r="227" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O226" s="33"/>
+      <c r="P226" s="1"/>
+      <c r="Q226" s="1"/>
+      <c r="R226" s="1"/>
+    </row>
+    <row r="227" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="33"/>
@@ -8858,8 +9940,12 @@
       <c r="L227" s="1"/>
       <c r="M227" s="1"/>
       <c r="N227" s="1"/>
-    </row>
-    <row r="228" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O227" s="33"/>
+      <c r="P227" s="1"/>
+      <c r="Q227" s="1"/>
+      <c r="R227" s="1"/>
+    </row>
+    <row r="228" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="33"/>
@@ -8875,8 +9961,12 @@
       <c r="L228" s="1"/>
       <c r="M228" s="1"/>
       <c r="N228" s="1"/>
-    </row>
-    <row r="229" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O228" s="33"/>
+      <c r="P228" s="1"/>
+      <c r="Q228" s="1"/>
+      <c r="R228" s="1"/>
+    </row>
+    <row r="229" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="33"/>
@@ -8892,8 +9982,12 @@
       <c r="L229" s="1"/>
       <c r="M229" s="1"/>
       <c r="N229" s="1"/>
-    </row>
-    <row r="230" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O229" s="33"/>
+      <c r="P229" s="1"/>
+      <c r="Q229" s="1"/>
+      <c r="R229" s="1"/>
+    </row>
+    <row r="230" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="33"/>
@@ -8909,8 +10003,12 @@
       <c r="L230" s="1"/>
       <c r="M230" s="1"/>
       <c r="N230" s="1"/>
-    </row>
-    <row r="231" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O230" s="33"/>
+      <c r="P230" s="1"/>
+      <c r="Q230" s="1"/>
+      <c r="R230" s="1"/>
+    </row>
+    <row r="231" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="33"/>
@@ -8926,8 +10024,12 @@
       <c r="L231" s="1"/>
       <c r="M231" s="1"/>
       <c r="N231" s="1"/>
-    </row>
-    <row r="232" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O231" s="33"/>
+      <c r="P231" s="1"/>
+      <c r="Q231" s="1"/>
+      <c r="R231" s="1"/>
+    </row>
+    <row r="232" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="33"/>
@@ -8943,8 +10045,12 @@
       <c r="L232" s="1"/>
       <c r="M232" s="1"/>
       <c r="N232" s="1"/>
-    </row>
-    <row r="233" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O232" s="33"/>
+      <c r="P232" s="1"/>
+      <c r="Q232" s="1"/>
+      <c r="R232" s="1"/>
+    </row>
+    <row r="233" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="33"/>
@@ -8960,8 +10066,12 @@
       <c r="L233" s="1"/>
       <c r="M233" s="1"/>
       <c r="N233" s="1"/>
-    </row>
-    <row r="234" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O233" s="33"/>
+      <c r="P233" s="1"/>
+      <c r="Q233" s="1"/>
+      <c r="R233" s="1"/>
+    </row>
+    <row r="234" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="33"/>
@@ -8977,8 +10087,12 @@
       <c r="L234" s="1"/>
       <c r="M234" s="1"/>
       <c r="N234" s="1"/>
-    </row>
-    <row r="235" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O234" s="33"/>
+      <c r="P234" s="1"/>
+      <c r="Q234" s="1"/>
+      <c r="R234" s="1"/>
+    </row>
+    <row r="235" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="33"/>
@@ -8994,8 +10108,12 @@
       <c r="L235" s="1"/>
       <c r="M235" s="1"/>
       <c r="N235" s="1"/>
-    </row>
-    <row r="236" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O235" s="33"/>
+      <c r="P235" s="1"/>
+      <c r="Q235" s="1"/>
+      <c r="R235" s="1"/>
+    </row>
+    <row r="236" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="33"/>
@@ -9011,8 +10129,12 @@
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
-    </row>
-    <row r="237" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O236" s="33"/>
+      <c r="P236" s="1"/>
+      <c r="Q236" s="1"/>
+      <c r="R236" s="1"/>
+    </row>
+    <row r="237" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="33"/>
@@ -9028,8 +10150,12 @@
       <c r="L237" s="1"/>
       <c r="M237" s="1"/>
       <c r="N237" s="1"/>
-    </row>
-    <row r="238" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O237" s="33"/>
+      <c r="P237" s="1"/>
+      <c r="Q237" s="1"/>
+      <c r="R237" s="1"/>
+    </row>
+    <row r="238" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="33"/>
@@ -9045,8 +10171,12 @@
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
       <c r="N238" s="1"/>
-    </row>
-    <row r="239" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O238" s="33"/>
+      <c r="P238" s="1"/>
+      <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+    </row>
+    <row r="239" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="33"/>
@@ -9062,8 +10192,12 @@
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
-    </row>
-    <row r="240" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O239" s="33"/>
+      <c r="P239" s="1"/>
+      <c r="Q239" s="1"/>
+      <c r="R239" s="1"/>
+    </row>
+    <row r="240" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="33"/>
@@ -9079,8 +10213,12 @@
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
-    </row>
-    <row r="241" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O240" s="33"/>
+      <c r="P240" s="1"/>
+      <c r="Q240" s="1"/>
+      <c r="R240" s="1"/>
+    </row>
+    <row r="241" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="33"/>
@@ -9096,8 +10234,12 @@
       <c r="L241" s="1"/>
       <c r="M241" s="1"/>
       <c r="N241" s="1"/>
-    </row>
-    <row r="242" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O241" s="33"/>
+      <c r="P241" s="1"/>
+      <c r="Q241" s="1"/>
+      <c r="R241" s="1"/>
+    </row>
+    <row r="242" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="33"/>
@@ -9113,8 +10255,12 @@
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
-    </row>
-    <row r="243" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O242" s="33"/>
+      <c r="P242" s="1"/>
+      <c r="Q242" s="1"/>
+      <c r="R242" s="1"/>
+    </row>
+    <row r="243" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="33"/>
@@ -9130,8 +10276,12 @@
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
       <c r="N243" s="1"/>
-    </row>
-    <row r="244" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O243" s="33"/>
+      <c r="P243" s="1"/>
+      <c r="Q243" s="1"/>
+      <c r="R243" s="1"/>
+    </row>
+    <row r="244" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="33"/>
@@ -9147,8 +10297,12 @@
       <c r="L244" s="1"/>
       <c r="M244" s="1"/>
       <c r="N244" s="1"/>
-    </row>
-    <row r="245" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O244" s="33"/>
+      <c r="P244" s="1"/>
+      <c r="Q244" s="1"/>
+      <c r="R244" s="1"/>
+    </row>
+    <row r="245" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="33"/>
@@ -9164,8 +10318,12 @@
       <c r="L245" s="1"/>
       <c r="M245" s="1"/>
       <c r="N245" s="1"/>
-    </row>
-    <row r="246" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O245" s="33"/>
+      <c r="P245" s="1"/>
+      <c r="Q245" s="1"/>
+      <c r="R245" s="1"/>
+    </row>
+    <row r="246" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="33"/>
@@ -9181,8 +10339,12 @@
       <c r="L246" s="1"/>
       <c r="M246" s="1"/>
       <c r="N246" s="1"/>
-    </row>
-    <row r="247" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O246" s="33"/>
+      <c r="P246" s="1"/>
+      <c r="Q246" s="1"/>
+      <c r="R246" s="1"/>
+    </row>
+    <row r="247" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="33"/>
@@ -9198,8 +10360,12 @@
       <c r="L247" s="1"/>
       <c r="M247" s="1"/>
       <c r="N247" s="1"/>
-    </row>
-    <row r="248" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O247" s="33"/>
+      <c r="P247" s="1"/>
+      <c r="Q247" s="1"/>
+      <c r="R247" s="1"/>
+    </row>
+    <row r="248" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="33"/>
@@ -9215,8 +10381,12 @@
       <c r="L248" s="1"/>
       <c r="M248" s="1"/>
       <c r="N248" s="1"/>
-    </row>
-    <row r="249" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O248" s="33"/>
+      <c r="P248" s="1"/>
+      <c r="Q248" s="1"/>
+      <c r="R248" s="1"/>
+    </row>
+    <row r="249" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="33"/>
@@ -9232,8 +10402,12 @@
       <c r="L249" s="1"/>
       <c r="M249" s="1"/>
       <c r="N249" s="1"/>
-    </row>
-    <row r="250" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O249" s="33"/>
+      <c r="P249" s="1"/>
+      <c r="Q249" s="1"/>
+      <c r="R249" s="1"/>
+    </row>
+    <row r="250" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="33"/>
@@ -9249,8 +10423,12 @@
       <c r="L250" s="1"/>
       <c r="M250" s="1"/>
       <c r="N250" s="1"/>
-    </row>
-    <row r="251" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O250" s="33"/>
+      <c r="P250" s="1"/>
+      <c r="Q250" s="1"/>
+      <c r="R250" s="1"/>
+    </row>
+    <row r="251" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="33"/>
@@ -9266,8 +10444,12 @@
       <c r="L251" s="1"/>
       <c r="M251" s="1"/>
       <c r="N251" s="1"/>
-    </row>
-    <row r="252" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O251" s="33"/>
+      <c r="P251" s="1"/>
+      <c r="Q251" s="1"/>
+      <c r="R251" s="1"/>
+    </row>
+    <row r="252" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="33"/>
@@ -9283,8 +10465,12 @@
       <c r="L252" s="1"/>
       <c r="M252" s="1"/>
       <c r="N252" s="1"/>
-    </row>
-    <row r="253" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O252" s="33"/>
+      <c r="P252" s="1"/>
+      <c r="Q252" s="1"/>
+      <c r="R252" s="1"/>
+    </row>
+    <row r="253" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="33"/>
@@ -9300,8 +10486,12 @@
       <c r="L253" s="1"/>
       <c r="M253" s="1"/>
       <c r="N253" s="1"/>
-    </row>
-    <row r="254" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O253" s="33"/>
+      <c r="P253" s="1"/>
+      <c r="Q253" s="1"/>
+      <c r="R253" s="1"/>
+    </row>
+    <row r="254" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="33"/>
@@ -9317,8 +10507,12 @@
       <c r="L254" s="1"/>
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
-    </row>
-    <row r="255" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O254" s="33"/>
+      <c r="P254" s="1"/>
+      <c r="Q254" s="1"/>
+      <c r="R254" s="1"/>
+    </row>
+    <row r="255" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="33"/>
@@ -9334,8 +10528,12 @@
       <c r="L255" s="1"/>
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>
-    </row>
-    <row r="256" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O255" s="33"/>
+      <c r="P255" s="1"/>
+      <c r="Q255" s="1"/>
+      <c r="R255" s="1"/>
+    </row>
+    <row r="256" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="33"/>
@@ -9351,8 +10549,12 @@
       <c r="L256" s="1"/>
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
-    </row>
-    <row r="257" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O256" s="33"/>
+      <c r="P256" s="1"/>
+      <c r="Q256" s="1"/>
+      <c r="R256" s="1"/>
+    </row>
+    <row r="257" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="33"/>
@@ -9368,8 +10570,12 @@
       <c r="L257" s="1"/>
       <c r="M257" s="1"/>
       <c r="N257" s="1"/>
-    </row>
-    <row r="258" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O257" s="33"/>
+      <c r="P257" s="1"/>
+      <c r="Q257" s="1"/>
+      <c r="R257" s="1"/>
+    </row>
+    <row r="258" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="33"/>
@@ -9385,8 +10591,12 @@
       <c r="L258" s="1"/>
       <c r="M258" s="1"/>
       <c r="N258" s="1"/>
-    </row>
-    <row r="259" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O258" s="33"/>
+      <c r="P258" s="1"/>
+      <c r="Q258" s="1"/>
+      <c r="R258" s="1"/>
+    </row>
+    <row r="259" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="33"/>
@@ -9402,8 +10612,12 @@
       <c r="L259" s="1"/>
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
-    </row>
-    <row r="260" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O259" s="33"/>
+      <c r="P259" s="1"/>
+      <c r="Q259" s="1"/>
+      <c r="R259" s="1"/>
+    </row>
+    <row r="260" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="33"/>
@@ -9419,8 +10633,12 @@
       <c r="L260" s="1"/>
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
-    </row>
-    <row r="261" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O260" s="33"/>
+      <c r="P260" s="1"/>
+      <c r="Q260" s="1"/>
+      <c r="R260" s="1"/>
+    </row>
+    <row r="261" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="33"/>
@@ -9436,8 +10654,12 @@
       <c r="L261" s="1"/>
       <c r="M261" s="1"/>
       <c r="N261" s="1"/>
-    </row>
-    <row r="262" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O261" s="33"/>
+      <c r="P261" s="1"/>
+      <c r="Q261" s="1"/>
+      <c r="R261" s="1"/>
+    </row>
+    <row r="262" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="33"/>
@@ -9453,8 +10675,12 @@
       <c r="L262" s="1"/>
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
-    </row>
-    <row r="263" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O262" s="33"/>
+      <c r="P262" s="1"/>
+      <c r="Q262" s="1"/>
+      <c r="R262" s="1"/>
+    </row>
+    <row r="263" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="33"/>
@@ -9470,8 +10696,12 @@
       <c r="L263" s="1"/>
       <c r="M263" s="1"/>
       <c r="N263" s="1"/>
-    </row>
-    <row r="264" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O263" s="33"/>
+      <c r="P263" s="1"/>
+      <c r="Q263" s="1"/>
+      <c r="R263" s="1"/>
+    </row>
+    <row r="264" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="33"/>
@@ -9487,8 +10717,12 @@
       <c r="L264" s="1"/>
       <c r="M264" s="1"/>
       <c r="N264" s="1"/>
-    </row>
-    <row r="265" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O264" s="33"/>
+      <c r="P264" s="1"/>
+      <c r="Q264" s="1"/>
+      <c r="R264" s="1"/>
+    </row>
+    <row r="265" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="33"/>
@@ -9504,8 +10738,12 @@
       <c r="L265" s="1"/>
       <c r="M265" s="1"/>
       <c r="N265" s="1"/>
-    </row>
-    <row r="266" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O265" s="33"/>
+      <c r="P265" s="1"/>
+      <c r="Q265" s="1"/>
+      <c r="R265" s="1"/>
+    </row>
+    <row r="266" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="33"/>
@@ -9521,8 +10759,12 @@
       <c r="L266" s="1"/>
       <c r="M266" s="1"/>
       <c r="N266" s="1"/>
-    </row>
-    <row r="267" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O266" s="33"/>
+      <c r="P266" s="1"/>
+      <c r="Q266" s="1"/>
+      <c r="R266" s="1"/>
+    </row>
+    <row r="267" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="33"/>
@@ -9538,8 +10780,12 @@
       <c r="L267" s="1"/>
       <c r="M267" s="1"/>
       <c r="N267" s="1"/>
-    </row>
-    <row r="268" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O267" s="33"/>
+      <c r="P267" s="1"/>
+      <c r="Q267" s="1"/>
+      <c r="R267" s="1"/>
+    </row>
+    <row r="268" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="33"/>
@@ -9555,8 +10801,12 @@
       <c r="L268" s="1"/>
       <c r="M268" s="1"/>
       <c r="N268" s="1"/>
-    </row>
-    <row r="269" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O268" s="33"/>
+      <c r="P268" s="1"/>
+      <c r="Q268" s="1"/>
+      <c r="R268" s="1"/>
+    </row>
+    <row r="269" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="33"/>
@@ -9572,8 +10822,12 @@
       <c r="L269" s="1"/>
       <c r="M269" s="1"/>
       <c r="N269" s="1"/>
-    </row>
-    <row r="270" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O269" s="33"/>
+      <c r="P269" s="1"/>
+      <c r="Q269" s="1"/>
+      <c r="R269" s="1"/>
+    </row>
+    <row r="270" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="33"/>
@@ -9589,8 +10843,12 @@
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
       <c r="N270" s="1"/>
-    </row>
-    <row r="271" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O270" s="33"/>
+      <c r="P270" s="1"/>
+      <c r="Q270" s="1"/>
+      <c r="R270" s="1"/>
+    </row>
+    <row r="271" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="33"/>
@@ -9606,8 +10864,12 @@
       <c r="L271" s="1"/>
       <c r="M271" s="1"/>
       <c r="N271" s="1"/>
-    </row>
-    <row r="272" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O271" s="33"/>
+      <c r="P271" s="1"/>
+      <c r="Q271" s="1"/>
+      <c r="R271" s="1"/>
+    </row>
+    <row r="272" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="33"/>
@@ -9623,8 +10885,12 @@
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
-    </row>
-    <row r="273" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O272" s="33"/>
+      <c r="P272" s="1"/>
+      <c r="Q272" s="1"/>
+      <c r="R272" s="1"/>
+    </row>
+    <row r="273" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="33"/>
@@ -9640,8 +10906,12 @@
       <c r="L273" s="1"/>
       <c r="M273" s="1"/>
       <c r="N273" s="1"/>
-    </row>
-    <row r="274" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O273" s="33"/>
+      <c r="P273" s="1"/>
+      <c r="Q273" s="1"/>
+      <c r="R273" s="1"/>
+    </row>
+    <row r="274" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="33"/>
@@ -9657,8 +10927,12 @@
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
       <c r="N274" s="1"/>
-    </row>
-    <row r="275" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O274" s="33"/>
+      <c r="P274" s="1"/>
+      <c r="Q274" s="1"/>
+      <c r="R274" s="1"/>
+    </row>
+    <row r="275" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="33"/>
@@ -9674,8 +10948,12 @@
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
       <c r="N275" s="1"/>
-    </row>
-    <row r="276" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O275" s="33"/>
+      <c r="P275" s="1"/>
+      <c r="Q275" s="1"/>
+      <c r="R275" s="1"/>
+    </row>
+    <row r="276" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="33"/>
@@ -9691,8 +10969,12 @@
       <c r="L276" s="1"/>
       <c r="M276" s="1"/>
       <c r="N276" s="1"/>
-    </row>
-    <row r="277" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O276" s="33"/>
+      <c r="P276" s="1"/>
+      <c r="Q276" s="1"/>
+      <c r="R276" s="1"/>
+    </row>
+    <row r="277" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="33"/>
@@ -9708,8 +10990,12 @@
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
       <c r="N277" s="1"/>
-    </row>
-    <row r="278" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O277" s="33"/>
+      <c r="P277" s="1"/>
+      <c r="Q277" s="1"/>
+      <c r="R277" s="1"/>
+    </row>
+    <row r="278" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="33"/>
@@ -9725,8 +11011,12 @@
       <c r="L278" s="1"/>
       <c r="M278" s="1"/>
       <c r="N278" s="1"/>
-    </row>
-    <row r="279" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O278" s="33"/>
+      <c r="P278" s="1"/>
+      <c r="Q278" s="1"/>
+      <c r="R278" s="1"/>
+    </row>
+    <row r="279" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="33"/>
@@ -9742,8 +11032,12 @@
       <c r="L279" s="1"/>
       <c r="M279" s="1"/>
       <c r="N279" s="1"/>
-    </row>
-    <row r="280" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O279" s="33"/>
+      <c r="P279" s="1"/>
+      <c r="Q279" s="1"/>
+      <c r="R279" s="1"/>
+    </row>
+    <row r="280" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="33"/>
@@ -9759,8 +11053,12 @@
       <c r="L280" s="1"/>
       <c r="M280" s="1"/>
       <c r="N280" s="1"/>
-    </row>
-    <row r="281" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O280" s="33"/>
+      <c r="P280" s="1"/>
+      <c r="Q280" s="1"/>
+      <c r="R280" s="1"/>
+    </row>
+    <row r="281" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="33"/>
@@ -9776,8 +11074,12 @@
       <c r="L281" s="1"/>
       <c r="M281" s="1"/>
       <c r="N281" s="1"/>
-    </row>
-    <row r="282" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O281" s="33"/>
+      <c r="P281" s="1"/>
+      <c r="Q281" s="1"/>
+      <c r="R281" s="1"/>
+    </row>
+    <row r="282" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="33"/>
@@ -9793,8 +11095,12 @@
       <c r="L282" s="1"/>
       <c r="M282" s="1"/>
       <c r="N282" s="1"/>
-    </row>
-    <row r="283" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O282" s="33"/>
+      <c r="P282" s="1"/>
+      <c r="Q282" s="1"/>
+      <c r="R282" s="1"/>
+    </row>
+    <row r="283" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="33"/>
@@ -9810,8 +11116,12 @@
       <c r="L283" s="1"/>
       <c r="M283" s="1"/>
       <c r="N283" s="1"/>
-    </row>
-    <row r="284" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O283" s="33"/>
+      <c r="P283" s="1"/>
+      <c r="Q283" s="1"/>
+      <c r="R283" s="1"/>
+    </row>
+    <row r="284" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="33"/>
@@ -9827,8 +11137,12 @@
       <c r="L284" s="1"/>
       <c r="M284" s="1"/>
       <c r="N284" s="1"/>
-    </row>
-    <row r="285" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O284" s="33"/>
+      <c r="P284" s="1"/>
+      <c r="Q284" s="1"/>
+      <c r="R284" s="1"/>
+    </row>
+    <row r="285" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="33"/>
@@ -9844,8 +11158,12 @@
       <c r="L285" s="1"/>
       <c r="M285" s="1"/>
       <c r="N285" s="1"/>
-    </row>
-    <row r="286" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O285" s="33"/>
+      <c r="P285" s="1"/>
+      <c r="Q285" s="1"/>
+      <c r="R285" s="1"/>
+    </row>
+    <row r="286" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="33"/>
@@ -9861,8 +11179,12 @@
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
-    </row>
-    <row r="287" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O286" s="33"/>
+      <c r="P286" s="1"/>
+      <c r="Q286" s="1"/>
+      <c r="R286" s="1"/>
+    </row>
+    <row r="287" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="33"/>
@@ -9878,8 +11200,12 @@
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
-    </row>
-    <row r="288" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O287" s="33"/>
+      <c r="P287" s="1"/>
+      <c r="Q287" s="1"/>
+      <c r="R287" s="1"/>
+    </row>
+    <row r="288" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="33"/>
@@ -9895,8 +11221,12 @@
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
-    </row>
-    <row r="289" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O288" s="33"/>
+      <c r="P288" s="1"/>
+      <c r="Q288" s="1"/>
+      <c r="R288" s="1"/>
+    </row>
+    <row r="289" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="33"/>
@@ -9912,8 +11242,12 @@
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
-    </row>
-    <row r="290" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O289" s="33"/>
+      <c r="P289" s="1"/>
+      <c r="Q289" s="1"/>
+      <c r="R289" s="1"/>
+    </row>
+    <row r="290" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="33"/>
@@ -9929,8 +11263,12 @@
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
       <c r="N290" s="1"/>
-    </row>
-    <row r="291" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O290" s="33"/>
+      <c r="P290" s="1"/>
+      <c r="Q290" s="1"/>
+      <c r="R290" s="1"/>
+    </row>
+    <row r="291" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="33"/>
@@ -9946,8 +11284,12 @@
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
-    </row>
-    <row r="292" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O291" s="33"/>
+      <c r="P291" s="1"/>
+      <c r="Q291" s="1"/>
+      <c r="R291" s="1"/>
+    </row>
+    <row r="292" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="33"/>
@@ -9963,8 +11305,12 @@
       <c r="L292" s="1"/>
       <c r="M292" s="1"/>
       <c r="N292" s="1"/>
-    </row>
-    <row r="293" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O292" s="33"/>
+      <c r="P292" s="1"/>
+      <c r="Q292" s="1"/>
+      <c r="R292" s="1"/>
+    </row>
+    <row r="293" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="33"/>
@@ -9980,8 +11326,12 @@
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
-    </row>
-    <row r="294" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O293" s="33"/>
+      <c r="P293" s="1"/>
+      <c r="Q293" s="1"/>
+      <c r="R293" s="1"/>
+    </row>
+    <row r="294" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="33"/>
@@ -9997,8 +11347,12 @@
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
       <c r="N294" s="1"/>
-    </row>
-    <row r="295" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O294" s="33"/>
+      <c r="P294" s="1"/>
+      <c r="Q294" s="1"/>
+      <c r="R294" s="1"/>
+    </row>
+    <row r="295" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="33"/>
@@ -10014,8 +11368,12 @@
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
       <c r="N295" s="1"/>
-    </row>
-    <row r="296" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O295" s="33"/>
+      <c r="P295" s="1"/>
+      <c r="Q295" s="1"/>
+      <c r="R295" s="1"/>
+    </row>
+    <row r="296" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="33"/>
@@ -10031,8 +11389,12 @@
       <c r="L296" s="1"/>
       <c r="M296" s="1"/>
       <c r="N296" s="1"/>
-    </row>
-    <row r="297" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O296" s="33"/>
+      <c r="P296" s="1"/>
+      <c r="Q296" s="1"/>
+      <c r="R296" s="1"/>
+    </row>
+    <row r="297" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="33"/>
@@ -10048,8 +11410,12 @@
       <c r="L297" s="1"/>
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
-    </row>
-    <row r="298" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O297" s="33"/>
+      <c r="P297" s="1"/>
+      <c r="Q297" s="1"/>
+      <c r="R297" s="1"/>
+    </row>
+    <row r="298" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="33"/>
@@ -10065,8 +11431,12 @@
       <c r="L298" s="1"/>
       <c r="M298" s="1"/>
       <c r="N298" s="1"/>
-    </row>
-    <row r="299" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O298" s="33"/>
+      <c r="P298" s="1"/>
+      <c r="Q298" s="1"/>
+      <c r="R298" s="1"/>
+    </row>
+    <row r="299" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="33"/>
@@ -10082,8 +11452,12 @@
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
       <c r="N299" s="1"/>
-    </row>
-    <row r="300" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O299" s="33"/>
+      <c r="P299" s="1"/>
+      <c r="Q299" s="1"/>
+      <c r="R299" s="1"/>
+    </row>
+    <row r="300" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="33"/>
@@ -10099,8 +11473,12 @@
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
-    </row>
-    <row r="301" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O300" s="33"/>
+      <c r="P300" s="1"/>
+      <c r="Q300" s="1"/>
+      <c r="R300" s="1"/>
+    </row>
+    <row r="301" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="33"/>
@@ -10116,8 +11494,12 @@
       <c r="L301" s="1"/>
       <c r="M301" s="1"/>
       <c r="N301" s="1"/>
-    </row>
-    <row r="302" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O301" s="33"/>
+      <c r="P301" s="1"/>
+      <c r="Q301" s="1"/>
+      <c r="R301" s="1"/>
+    </row>
+    <row r="302" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="33"/>
@@ -10133,8 +11515,12 @@
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
-    </row>
-    <row r="303" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O302" s="33"/>
+      <c r="P302" s="1"/>
+      <c r="Q302" s="1"/>
+      <c r="R302" s="1"/>
+    </row>
+    <row r="303" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="33"/>
@@ -10150,8 +11536,12 @@
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
-    </row>
-    <row r="304" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O303" s="33"/>
+      <c r="P303" s="1"/>
+      <c r="Q303" s="1"/>
+      <c r="R303" s="1"/>
+    </row>
+    <row r="304" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="33"/>
@@ -10167,8 +11557,12 @@
       <c r="L304" s="1"/>
       <c r="M304" s="1"/>
       <c r="N304" s="1"/>
-    </row>
-    <row r="305" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O304" s="33"/>
+      <c r="P304" s="1"/>
+      <c r="Q304" s="1"/>
+      <c r="R304" s="1"/>
+    </row>
+    <row r="305" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="33"/>
@@ -10184,8 +11578,12 @@
       <c r="L305" s="1"/>
       <c r="M305" s="1"/>
       <c r="N305" s="1"/>
-    </row>
-    <row r="306" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O305" s="33"/>
+      <c r="P305" s="1"/>
+      <c r="Q305" s="1"/>
+      <c r="R305" s="1"/>
+    </row>
+    <row r="306" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="33"/>
@@ -10201,8 +11599,12 @@
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
-    </row>
-    <row r="307" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O306" s="33"/>
+      <c r="P306" s="1"/>
+      <c r="Q306" s="1"/>
+      <c r="R306" s="1"/>
+    </row>
+    <row r="307" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="33"/>
@@ -10218,8 +11620,12 @@
       <c r="L307" s="1"/>
       <c r="M307" s="1"/>
       <c r="N307" s="1"/>
-    </row>
-    <row r="308" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O307" s="33"/>
+      <c r="P307" s="1"/>
+      <c r="Q307" s="1"/>
+      <c r="R307" s="1"/>
+    </row>
+    <row r="308" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="33"/>
@@ -10235,8 +11641,12 @@
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
-    </row>
-    <row r="309" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O308" s="33"/>
+      <c r="P308" s="1"/>
+      <c r="Q308" s="1"/>
+      <c r="R308" s="1"/>
+    </row>
+    <row r="309" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="33"/>
@@ -10252,8 +11662,12 @@
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
-    </row>
-    <row r="310" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O309" s="33"/>
+      <c r="P309" s="1"/>
+      <c r="Q309" s="1"/>
+      <c r="R309" s="1"/>
+    </row>
+    <row r="310" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="33"/>
@@ -10269,8 +11683,12 @@
       <c r="L310" s="1"/>
       <c r="M310" s="1"/>
       <c r="N310" s="1"/>
-    </row>
-    <row r="311" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O310" s="33"/>
+      <c r="P310" s="1"/>
+      <c r="Q310" s="1"/>
+      <c r="R310" s="1"/>
+    </row>
+    <row r="311" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="33"/>
@@ -10286,8 +11704,12 @@
       <c r="L311" s="1"/>
       <c r="M311" s="1"/>
       <c r="N311" s="1"/>
-    </row>
-    <row r="312" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O311" s="33"/>
+      <c r="P311" s="1"/>
+      <c r="Q311" s="1"/>
+      <c r="R311" s="1"/>
+    </row>
+    <row r="312" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="33"/>
@@ -10303,8 +11725,12 @@
       <c r="L312" s="1"/>
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
-    </row>
-    <row r="313" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O312" s="33"/>
+      <c r="P312" s="1"/>
+      <c r="Q312" s="1"/>
+      <c r="R312" s="1"/>
+    </row>
+    <row r="313" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="33"/>
@@ -10320,8 +11746,12 @@
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
-    </row>
-    <row r="314" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O313" s="33"/>
+      <c r="P313" s="1"/>
+      <c r="Q313" s="1"/>
+      <c r="R313" s="1"/>
+    </row>
+    <row r="314" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="33"/>
@@ -10337,8 +11767,12 @@
       <c r="L314" s="1"/>
       <c r="M314" s="1"/>
       <c r="N314" s="1"/>
-    </row>
-    <row r="315" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O314" s="33"/>
+      <c r="P314" s="1"/>
+      <c r="Q314" s="1"/>
+      <c r="R314" s="1"/>
+    </row>
+    <row r="315" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="33"/>
@@ -10354,8 +11788,12 @@
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
-    </row>
-    <row r="316" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O315" s="33"/>
+      <c r="P315" s="1"/>
+      <c r="Q315" s="1"/>
+      <c r="R315" s="1"/>
+    </row>
+    <row r="316" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="33"/>
@@ -10371,8 +11809,12 @@
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
       <c r="N316" s="1"/>
-    </row>
-    <row r="317" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O316" s="33"/>
+      <c r="P316" s="1"/>
+      <c r="Q316" s="1"/>
+      <c r="R316" s="1"/>
+    </row>
+    <row r="317" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="33"/>
@@ -10388,8 +11830,12 @@
       <c r="L317" s="1"/>
       <c r="M317" s="1"/>
       <c r="N317" s="1"/>
-    </row>
-    <row r="318" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O317" s="33"/>
+      <c r="P317" s="1"/>
+      <c r="Q317" s="1"/>
+      <c r="R317" s="1"/>
+    </row>
+    <row r="318" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="33"/>
@@ -10405,8 +11851,12 @@
       <c r="L318" s="1"/>
       <c r="M318" s="1"/>
       <c r="N318" s="1"/>
-    </row>
-    <row r="319" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O318" s="33"/>
+      <c r="P318" s="1"/>
+      <c r="Q318" s="1"/>
+      <c r="R318" s="1"/>
+    </row>
+    <row r="319" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="33"/>
@@ -10422,8 +11872,12 @@
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
       <c r="N319" s="1"/>
-    </row>
-    <row r="320" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O319" s="33"/>
+      <c r="P319" s="1"/>
+      <c r="Q319" s="1"/>
+      <c r="R319" s="1"/>
+    </row>
+    <row r="320" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="33"/>
@@ -10439,8 +11893,12 @@
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
       <c r="N320" s="1"/>
-    </row>
-    <row r="321" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O320" s="33"/>
+      <c r="P320" s="1"/>
+      <c r="Q320" s="1"/>
+      <c r="R320" s="1"/>
+    </row>
+    <row r="321" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="33"/>
@@ -10456,8 +11914,12 @@
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
-    </row>
-    <row r="322" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O321" s="33"/>
+      <c r="P321" s="1"/>
+      <c r="Q321" s="1"/>
+      <c r="R321" s="1"/>
+    </row>
+    <row r="322" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="33"/>
@@ -10473,8 +11935,12 @@
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
       <c r="N322" s="1"/>
-    </row>
-    <row r="323" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O322" s="33"/>
+      <c r="P322" s="1"/>
+      <c r="Q322" s="1"/>
+      <c r="R322" s="1"/>
+    </row>
+    <row r="323" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="33"/>
@@ -10490,8 +11956,12 @@
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
-    </row>
-    <row r="324" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O323" s="33"/>
+      <c r="P323" s="1"/>
+      <c r="Q323" s="1"/>
+      <c r="R323" s="1"/>
+    </row>
+    <row r="324" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="33"/>
@@ -10507,8 +11977,12 @@
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
       <c r="N324" s="1"/>
-    </row>
-    <row r="325" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O324" s="33"/>
+      <c r="P324" s="1"/>
+      <c r="Q324" s="1"/>
+      <c r="R324" s="1"/>
+    </row>
+    <row r="325" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="33"/>
@@ -10524,8 +11998,12 @@
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
       <c r="N325" s="1"/>
-    </row>
-    <row r="326" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O325" s="33"/>
+      <c r="P325" s="1"/>
+      <c r="Q325" s="1"/>
+      <c r="R325" s="1"/>
+    </row>
+    <row r="326" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="33"/>
@@ -10541,8 +12019,12 @@
       <c r="L326" s="1"/>
       <c r="M326" s="1"/>
       <c r="N326" s="1"/>
-    </row>
-    <row r="327" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O326" s="33"/>
+      <c r="P326" s="1"/>
+      <c r="Q326" s="1"/>
+      <c r="R326" s="1"/>
+    </row>
+    <row r="327" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="33"/>
@@ -10558,8 +12040,12 @@
       <c r="L327" s="1"/>
       <c r="M327" s="1"/>
       <c r="N327" s="1"/>
-    </row>
-    <row r="328" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O327" s="33"/>
+      <c r="P327" s="1"/>
+      <c r="Q327" s="1"/>
+      <c r="R327" s="1"/>
+    </row>
+    <row r="328" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="33"/>
@@ -10575,8 +12061,12 @@
       <c r="L328" s="1"/>
       <c r="M328" s="1"/>
       <c r="N328" s="1"/>
-    </row>
-    <row r="329" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O328" s="33"/>
+      <c r="P328" s="1"/>
+      <c r="Q328" s="1"/>
+      <c r="R328" s="1"/>
+    </row>
+    <row r="329" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="33"/>
@@ -10592,8 +12082,12 @@
       <c r="L329" s="1"/>
       <c r="M329" s="1"/>
       <c r="N329" s="1"/>
-    </row>
-    <row r="330" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O329" s="33"/>
+      <c r="P329" s="1"/>
+      <c r="Q329" s="1"/>
+      <c r="R329" s="1"/>
+    </row>
+    <row r="330" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="33"/>
@@ -10609,8 +12103,12 @@
       <c r="L330" s="1"/>
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
-    </row>
-    <row r="331" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O330" s="33"/>
+      <c r="P330" s="1"/>
+      <c r="Q330" s="1"/>
+      <c r="R330" s="1"/>
+    </row>
+    <row r="331" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="33"/>
@@ -10626,8 +12124,12 @@
       <c r="L331" s="1"/>
       <c r="M331" s="1"/>
       <c r="N331" s="1"/>
-    </row>
-    <row r="332" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O331" s="33"/>
+      <c r="P331" s="1"/>
+      <c r="Q331" s="1"/>
+      <c r="R331" s="1"/>
+    </row>
+    <row r="332" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="33"/>
@@ -10643,8 +12145,12 @@
       <c r="L332" s="1"/>
       <c r="M332" s="1"/>
       <c r="N332" s="1"/>
-    </row>
-    <row r="333" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O332" s="33"/>
+      <c r="P332" s="1"/>
+      <c r="Q332" s="1"/>
+      <c r="R332" s="1"/>
+    </row>
+    <row r="333" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="33"/>
@@ -10660,8 +12166,12 @@
       <c r="L333" s="1"/>
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
-    </row>
-    <row r="334" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O333" s="33"/>
+      <c r="P333" s="1"/>
+      <c r="Q333" s="1"/>
+      <c r="R333" s="1"/>
+    </row>
+    <row r="334" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="33"/>
@@ -10677,8 +12187,12 @@
       <c r="L334" s="1"/>
       <c r="M334" s="1"/>
       <c r="N334" s="1"/>
-    </row>
-    <row r="335" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O334" s="33"/>
+      <c r="P334" s="1"/>
+      <c r="Q334" s="1"/>
+      <c r="R334" s="1"/>
+    </row>
+    <row r="335" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="33"/>
@@ -10694,8 +12208,12 @@
       <c r="L335" s="1"/>
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
-    </row>
-    <row r="336" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O335" s="33"/>
+      <c r="P335" s="1"/>
+      <c r="Q335" s="1"/>
+      <c r="R335" s="1"/>
+    </row>
+    <row r="336" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="33"/>
@@ -10711,8 +12229,12 @@
       <c r="L336" s="1"/>
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
-    </row>
-    <row r="337" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O336" s="33"/>
+      <c r="P336" s="1"/>
+      <c r="Q336" s="1"/>
+      <c r="R336" s="1"/>
+    </row>
+    <row r="337" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="33"/>
@@ -10728,8 +12250,12 @@
       <c r="L337" s="1"/>
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
-    </row>
-    <row r="338" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O337" s="33"/>
+      <c r="P337" s="1"/>
+      <c r="Q337" s="1"/>
+      <c r="R337" s="1"/>
+    </row>
+    <row r="338" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="33"/>
@@ -10745,8 +12271,12 @@
       <c r="L338" s="1"/>
       <c r="M338" s="1"/>
       <c r="N338" s="1"/>
-    </row>
-    <row r="339" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O338" s="33"/>
+      <c r="P338" s="1"/>
+      <c r="Q338" s="1"/>
+      <c r="R338" s="1"/>
+    </row>
+    <row r="339" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="33"/>
@@ -10762,8 +12292,12 @@
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
-    </row>
-    <row r="340" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O339" s="33"/>
+      <c r="P339" s="1"/>
+      <c r="Q339" s="1"/>
+      <c r="R339" s="1"/>
+    </row>
+    <row r="340" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="33"/>
@@ -10779,8 +12313,12 @@
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
-    </row>
-    <row r="341" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O340" s="33"/>
+      <c r="P340" s="1"/>
+      <c r="Q340" s="1"/>
+      <c r="R340" s="1"/>
+    </row>
+    <row r="341" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="33"/>
@@ -10796,8 +12334,12 @@
       <c r="L341" s="1"/>
       <c r="M341" s="1"/>
       <c r="N341" s="1"/>
-    </row>
-    <row r="342" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O341" s="33"/>
+      <c r="P341" s="1"/>
+      <c r="Q341" s="1"/>
+      <c r="R341" s="1"/>
+    </row>
+    <row r="342" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="33"/>
@@ -10813,8 +12355,12 @@
       <c r="L342" s="1"/>
       <c r="M342" s="1"/>
       <c r="N342" s="1"/>
-    </row>
-    <row r="343" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O342" s="33"/>
+      <c r="P342" s="1"/>
+      <c r="Q342" s="1"/>
+      <c r="R342" s="1"/>
+    </row>
+    <row r="343" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="33"/>
@@ -10830,8 +12376,12 @@
       <c r="L343" s="1"/>
       <c r="M343" s="1"/>
       <c r="N343" s="1"/>
-    </row>
-    <row r="344" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O343" s="33"/>
+      <c r="P343" s="1"/>
+      <c r="Q343" s="1"/>
+      <c r="R343" s="1"/>
+    </row>
+    <row r="344" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="33"/>
@@ -10847,8 +12397,12 @@
       <c r="L344" s="1"/>
       <c r="M344" s="1"/>
       <c r="N344" s="1"/>
-    </row>
-    <row r="345" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O344" s="33"/>
+      <c r="P344" s="1"/>
+      <c r="Q344" s="1"/>
+      <c r="R344" s="1"/>
+    </row>
+    <row r="345" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="33"/>
@@ -10864,8 +12418,12 @@
       <c r="L345" s="1"/>
       <c r="M345" s="1"/>
       <c r="N345" s="1"/>
-    </row>
-    <row r="346" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O345" s="33"/>
+      <c r="P345" s="1"/>
+      <c r="Q345" s="1"/>
+      <c r="R345" s="1"/>
+    </row>
+    <row r="346" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="33"/>
@@ -10881,8 +12439,12 @@
       <c r="L346" s="1"/>
       <c r="M346" s="1"/>
       <c r="N346" s="1"/>
-    </row>
-    <row r="347" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O346" s="33"/>
+      <c r="P346" s="1"/>
+      <c r="Q346" s="1"/>
+      <c r="R346" s="1"/>
+    </row>
+    <row r="347" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="33"/>
@@ -10898,8 +12460,12 @@
       <c r="L347" s="1"/>
       <c r="M347" s="1"/>
       <c r="N347" s="1"/>
-    </row>
-    <row r="348" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O347" s="33"/>
+      <c r="P347" s="1"/>
+      <c r="Q347" s="1"/>
+      <c r="R347" s="1"/>
+    </row>
+    <row r="348" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="33"/>
@@ -10915,8 +12481,12 @@
       <c r="L348" s="1"/>
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
-    </row>
-    <row r="349" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O348" s="33"/>
+      <c r="P348" s="1"/>
+      <c r="Q348" s="1"/>
+      <c r="R348" s="1"/>
+    </row>
+    <row r="349" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="33"/>
@@ -10932,8 +12502,12 @@
       <c r="L349" s="1"/>
       <c r="M349" s="1"/>
       <c r="N349" s="1"/>
-    </row>
-    <row r="350" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O349" s="33"/>
+      <c r="P349" s="1"/>
+      <c r="Q349" s="1"/>
+      <c r="R349" s="1"/>
+    </row>
+    <row r="350" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="33"/>
@@ -10949,8 +12523,12 @@
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
       <c r="N350" s="1"/>
-    </row>
-    <row r="351" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O350" s="33"/>
+      <c r="P350" s="1"/>
+      <c r="Q350" s="1"/>
+      <c r="R350" s="1"/>
+    </row>
+    <row r="351" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="33"/>
@@ -10966,8 +12544,12 @@
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
       <c r="N351" s="1"/>
-    </row>
-    <row r="352" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O351" s="33"/>
+      <c r="P351" s="1"/>
+      <c r="Q351" s="1"/>
+      <c r="R351" s="1"/>
+    </row>
+    <row r="352" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="33"/>
@@ -10983,8 +12565,12 @@
       <c r="L352" s="1"/>
       <c r="M352" s="1"/>
       <c r="N352" s="1"/>
-    </row>
-    <row r="353" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O352" s="33"/>
+      <c r="P352" s="1"/>
+      <c r="Q352" s="1"/>
+      <c r="R352" s="1"/>
+    </row>
+    <row r="353" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="33"/>
@@ -11000,8 +12586,12 @@
       <c r="L353" s="1"/>
       <c r="M353" s="1"/>
       <c r="N353" s="1"/>
-    </row>
-    <row r="354" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O353" s="33"/>
+      <c r="P353" s="1"/>
+      <c r="Q353" s="1"/>
+      <c r="R353" s="1"/>
+    </row>
+    <row r="354" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="33"/>
@@ -11017,8 +12607,12 @@
       <c r="L354" s="1"/>
       <c r="M354" s="1"/>
       <c r="N354" s="1"/>
-    </row>
-    <row r="355" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O354" s="33"/>
+      <c r="P354" s="1"/>
+      <c r="Q354" s="1"/>
+      <c r="R354" s="1"/>
+    </row>
+    <row r="355" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="33"/>
@@ -11034,8 +12628,12 @@
       <c r="L355" s="1"/>
       <c r="M355" s="1"/>
       <c r="N355" s="1"/>
-    </row>
-    <row r="356" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O355" s="33"/>
+      <c r="P355" s="1"/>
+      <c r="Q355" s="1"/>
+      <c r="R355" s="1"/>
+    </row>
+    <row r="356" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="33"/>
@@ -11051,8 +12649,12 @@
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
       <c r="N356" s="1"/>
-    </row>
-    <row r="357" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O356" s="33"/>
+      <c r="P356" s="1"/>
+      <c r="Q356" s="1"/>
+      <c r="R356" s="1"/>
+    </row>
+    <row r="357" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="33"/>
@@ -11068,8 +12670,12 @@
       <c r="L357" s="1"/>
       <c r="M357" s="1"/>
       <c r="N357" s="1"/>
-    </row>
-    <row r="358" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O357" s="33"/>
+      <c r="P357" s="1"/>
+      <c r="Q357" s="1"/>
+      <c r="R357" s="1"/>
+    </row>
+    <row r="358" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="33"/>
@@ -11085,8 +12691,12 @@
       <c r="L358" s="1"/>
       <c r="M358" s="1"/>
       <c r="N358" s="1"/>
-    </row>
-    <row r="359" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O358" s="33"/>
+      <c r="P358" s="1"/>
+      <c r="Q358" s="1"/>
+      <c r="R358" s="1"/>
+    </row>
+    <row r="359" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="33"/>
@@ -11102,8 +12712,12 @@
       <c r="L359" s="1"/>
       <c r="M359" s="1"/>
       <c r="N359" s="1"/>
-    </row>
-    <row r="360" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O359" s="33"/>
+      <c r="P359" s="1"/>
+      <c r="Q359" s="1"/>
+      <c r="R359" s="1"/>
+    </row>
+    <row r="360" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="33"/>
@@ -11119,8 +12733,12 @@
       <c r="L360" s="1"/>
       <c r="M360" s="1"/>
       <c r="N360" s="1"/>
-    </row>
-    <row r="361" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O360" s="33"/>
+      <c r="P360" s="1"/>
+      <c r="Q360" s="1"/>
+      <c r="R360" s="1"/>
+    </row>
+    <row r="361" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="33"/>
@@ -11136,8 +12754,12 @@
       <c r="L361" s="1"/>
       <c r="M361" s="1"/>
       <c r="N361" s="1"/>
-    </row>
-    <row r="362" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O361" s="33"/>
+      <c r="P361" s="1"/>
+      <c r="Q361" s="1"/>
+      <c r="R361" s="1"/>
+    </row>
+    <row r="362" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="33"/>
@@ -11153,8 +12775,12 @@
       <c r="L362" s="1"/>
       <c r="M362" s="1"/>
       <c r="N362" s="1"/>
-    </row>
-    <row r="363" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O362" s="33"/>
+      <c r="P362" s="1"/>
+      <c r="Q362" s="1"/>
+      <c r="R362" s="1"/>
+    </row>
+    <row r="363" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="33"/>
@@ -11170,8 +12796,12 @@
       <c r="L363" s="1"/>
       <c r="M363" s="1"/>
       <c r="N363" s="1"/>
-    </row>
-    <row r="364" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O363" s="33"/>
+      <c r="P363" s="1"/>
+      <c r="Q363" s="1"/>
+      <c r="R363" s="1"/>
+    </row>
+    <row r="364" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="33"/>
@@ -11187,8 +12817,12 @@
       <c r="L364" s="1"/>
       <c r="M364" s="1"/>
       <c r="N364" s="1"/>
-    </row>
-    <row r="365" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O364" s="33"/>
+      <c r="P364" s="1"/>
+      <c r="Q364" s="1"/>
+      <c r="R364" s="1"/>
+    </row>
+    <row r="365" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="33"/>
@@ -11204,8 +12838,12 @@
       <c r="L365" s="1"/>
       <c r="M365" s="1"/>
       <c r="N365" s="1"/>
-    </row>
-    <row r="366" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O365" s="33"/>
+      <c r="P365" s="1"/>
+      <c r="Q365" s="1"/>
+      <c r="R365" s="1"/>
+    </row>
+    <row r="366" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="33"/>
@@ -11221,8 +12859,12 @@
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
-    </row>
-    <row r="367" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O366" s="33"/>
+      <c r="P366" s="1"/>
+      <c r="Q366" s="1"/>
+      <c r="R366" s="1"/>
+    </row>
+    <row r="367" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="33"/>
@@ -11238,8 +12880,12 @@
       <c r="L367" s="1"/>
       <c r="M367" s="1"/>
       <c r="N367" s="1"/>
-    </row>
-    <row r="368" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O367" s="33"/>
+      <c r="P367" s="1"/>
+      <c r="Q367" s="1"/>
+      <c r="R367" s="1"/>
+    </row>
+    <row r="368" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="33"/>
@@ -11255,8 +12901,12 @@
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
       <c r="N368" s="1"/>
-    </row>
-    <row r="369" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O368" s="33"/>
+      <c r="P368" s="1"/>
+      <c r="Q368" s="1"/>
+      <c r="R368" s="1"/>
+    </row>
+    <row r="369" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="33"/>
@@ -11272,8 +12922,12 @@
       <c r="L369" s="1"/>
       <c r="M369" s="1"/>
       <c r="N369" s="1"/>
-    </row>
-    <row r="370" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O369" s="33"/>
+      <c r="P369" s="1"/>
+      <c r="Q369" s="1"/>
+      <c r="R369" s="1"/>
+    </row>
+    <row r="370" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="33"/>
@@ -11289,8 +12943,12 @@
       <c r="L370" s="1"/>
       <c r="M370" s="1"/>
       <c r="N370" s="1"/>
-    </row>
-    <row r="371" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O370" s="33"/>
+      <c r="P370" s="1"/>
+      <c r="Q370" s="1"/>
+      <c r="R370" s="1"/>
+    </row>
+    <row r="371" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="33"/>
@@ -11306,8 +12964,12 @@
       <c r="L371" s="1"/>
       <c r="M371" s="1"/>
       <c r="N371" s="1"/>
-    </row>
-    <row r="372" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O371" s="33"/>
+      <c r="P371" s="1"/>
+      <c r="Q371" s="1"/>
+      <c r="R371" s="1"/>
+    </row>
+    <row r="372" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="33"/>
@@ -11323,8 +12985,12 @@
       <c r="L372" s="1"/>
       <c r="M372" s="1"/>
       <c r="N372" s="1"/>
-    </row>
-    <row r="373" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O372" s="33"/>
+      <c r="P372" s="1"/>
+      <c r="Q372" s="1"/>
+      <c r="R372" s="1"/>
+    </row>
+    <row r="373" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="33"/>
@@ -11340,8 +13006,12 @@
       <c r="L373" s="1"/>
       <c r="M373" s="1"/>
       <c r="N373" s="1"/>
-    </row>
-    <row r="374" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O373" s="33"/>
+      <c r="P373" s="1"/>
+      <c r="Q373" s="1"/>
+      <c r="R373" s="1"/>
+    </row>
+    <row r="374" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="33"/>
@@ -11357,8 +13027,12 @@
       <c r="L374" s="1"/>
       <c r="M374" s="1"/>
       <c r="N374" s="1"/>
-    </row>
-    <row r="375" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O374" s="33"/>
+      <c r="P374" s="1"/>
+      <c r="Q374" s="1"/>
+      <c r="R374" s="1"/>
+    </row>
+    <row r="375" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="33"/>
@@ -11374,8 +13048,12 @@
       <c r="L375" s="1"/>
       <c r="M375" s="1"/>
       <c r="N375" s="1"/>
-    </row>
-    <row r="376" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O375" s="33"/>
+      <c r="P375" s="1"/>
+      <c r="Q375" s="1"/>
+      <c r="R375" s="1"/>
+    </row>
+    <row r="376" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="33"/>
@@ -11391,8 +13069,12 @@
       <c r="L376" s="1"/>
       <c r="M376" s="1"/>
       <c r="N376" s="1"/>
-    </row>
-    <row r="377" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O376" s="33"/>
+      <c r="P376" s="1"/>
+      <c r="Q376" s="1"/>
+      <c r="R376" s="1"/>
+    </row>
+    <row r="377" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="33"/>
@@ -11408,8 +13090,12 @@
       <c r="L377" s="1"/>
       <c r="M377" s="1"/>
       <c r="N377" s="1"/>
-    </row>
-    <row r="378" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O377" s="33"/>
+      <c r="P377" s="1"/>
+      <c r="Q377" s="1"/>
+      <c r="R377" s="1"/>
+    </row>
+    <row r="378" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="33"/>
@@ -11425,8 +13111,12 @@
       <c r="L378" s="1"/>
       <c r="M378" s="1"/>
       <c r="N378" s="1"/>
-    </row>
-    <row r="379" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O378" s="33"/>
+      <c r="P378" s="1"/>
+      <c r="Q378" s="1"/>
+      <c r="R378" s="1"/>
+    </row>
+    <row r="379" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="33"/>
@@ -11442,8 +13132,12 @@
       <c r="L379" s="1"/>
       <c r="M379" s="1"/>
       <c r="N379" s="1"/>
-    </row>
-    <row r="380" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O379" s="33"/>
+      <c r="P379" s="1"/>
+      <c r="Q379" s="1"/>
+      <c r="R379" s="1"/>
+    </row>
+    <row r="380" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="33"/>
@@ -11459,8 +13153,12 @@
       <c r="L380" s="1"/>
       <c r="M380" s="1"/>
       <c r="N380" s="1"/>
-    </row>
-    <row r="381" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O380" s="33"/>
+      <c r="P380" s="1"/>
+      <c r="Q380" s="1"/>
+      <c r="R380" s="1"/>
+    </row>
+    <row r="381" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="33"/>
@@ -11476,8 +13174,12 @@
       <c r="L381" s="1"/>
       <c r="M381" s="1"/>
       <c r="N381" s="1"/>
-    </row>
-    <row r="382" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O381" s="33"/>
+      <c r="P381" s="1"/>
+      <c r="Q381" s="1"/>
+      <c r="R381" s="1"/>
+    </row>
+    <row r="382" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="33"/>
@@ -11493,8 +13195,12 @@
       <c r="L382" s="1"/>
       <c r="M382" s="1"/>
       <c r="N382" s="1"/>
-    </row>
-    <row r="383" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O382" s="33"/>
+      <c r="P382" s="1"/>
+      <c r="Q382" s="1"/>
+      <c r="R382" s="1"/>
+    </row>
+    <row r="383" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="33"/>
@@ -11510,8 +13216,12 @@
       <c r="L383" s="1"/>
       <c r="M383" s="1"/>
       <c r="N383" s="1"/>
-    </row>
-    <row r="384" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O383" s="33"/>
+      <c r="P383" s="1"/>
+      <c r="Q383" s="1"/>
+      <c r="R383" s="1"/>
+    </row>
+    <row r="384" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="33"/>
@@ -11527,8 +13237,12 @@
       <c r="L384" s="1"/>
       <c r="M384" s="1"/>
       <c r="N384" s="1"/>
-    </row>
-    <row r="385" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O384" s="33"/>
+      <c r="P384" s="1"/>
+      <c r="Q384" s="1"/>
+      <c r="R384" s="1"/>
+    </row>
+    <row r="385" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="33"/>
@@ -11544,8 +13258,12 @@
       <c r="L385" s="1"/>
       <c r="M385" s="1"/>
       <c r="N385" s="1"/>
-    </row>
-    <row r="386" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O385" s="33"/>
+      <c r="P385" s="1"/>
+      <c r="Q385" s="1"/>
+      <c r="R385" s="1"/>
+    </row>
+    <row r="386" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="33"/>
@@ -11561,8 +13279,12 @@
       <c r="L386" s="1"/>
       <c r="M386" s="1"/>
       <c r="N386" s="1"/>
-    </row>
-    <row r="387" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O386" s="33"/>
+      <c r="P386" s="1"/>
+      <c r="Q386" s="1"/>
+      <c r="R386" s="1"/>
+    </row>
+    <row r="387" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="33"/>
@@ -11578,8 +13300,12 @@
       <c r="L387" s="1"/>
       <c r="M387" s="1"/>
       <c r="N387" s="1"/>
-    </row>
-    <row r="388" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O387" s="33"/>
+      <c r="P387" s="1"/>
+      <c r="Q387" s="1"/>
+      <c r="R387" s="1"/>
+    </row>
+    <row r="388" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="33"/>
@@ -11595,8 +13321,12 @@
       <c r="L388" s="1"/>
       <c r="M388" s="1"/>
       <c r="N388" s="1"/>
-    </row>
-    <row r="389" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O388" s="33"/>
+      <c r="P388" s="1"/>
+      <c r="Q388" s="1"/>
+      <c r="R388" s="1"/>
+    </row>
+    <row r="389" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="33"/>
@@ -11612,8 +13342,12 @@
       <c r="L389" s="1"/>
       <c r="M389" s="1"/>
       <c r="N389" s="1"/>
-    </row>
-    <row r="390" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O389" s="33"/>
+      <c r="P389" s="1"/>
+      <c r="Q389" s="1"/>
+      <c r="R389" s="1"/>
+    </row>
+    <row r="390" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="33"/>
@@ -11629,8 +13363,12 @@
       <c r="L390" s="1"/>
       <c r="M390" s="1"/>
       <c r="N390" s="1"/>
-    </row>
-    <row r="391" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O390" s="33"/>
+      <c r="P390" s="1"/>
+      <c r="Q390" s="1"/>
+      <c r="R390" s="1"/>
+    </row>
+    <row r="391" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="33"/>
@@ -11646,8 +13384,12 @@
       <c r="L391" s="1"/>
       <c r="M391" s="1"/>
       <c r="N391" s="1"/>
-    </row>
-    <row r="392" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O391" s="33"/>
+      <c r="P391" s="1"/>
+      <c r="Q391" s="1"/>
+      <c r="R391" s="1"/>
+    </row>
+    <row r="392" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="33"/>
@@ -11663,8 +13405,12 @@
       <c r="L392" s="1"/>
       <c r="M392" s="1"/>
       <c r="N392" s="1"/>
-    </row>
-    <row r="393" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O392" s="33"/>
+      <c r="P392" s="1"/>
+      <c r="Q392" s="1"/>
+      <c r="R392" s="1"/>
+    </row>
+    <row r="393" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="33"/>
@@ -11680,8 +13426,12 @@
       <c r="L393" s="1"/>
       <c r="M393" s="1"/>
       <c r="N393" s="1"/>
-    </row>
-    <row r="394" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O393" s="33"/>
+      <c r="P393" s="1"/>
+      <c r="Q393" s="1"/>
+      <c r="R393" s="1"/>
+    </row>
+    <row r="394" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="33"/>
@@ -11697,8 +13447,12 @@
       <c r="L394" s="1"/>
       <c r="M394" s="1"/>
       <c r="N394" s="1"/>
-    </row>
-    <row r="395" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O394" s="33"/>
+      <c r="P394" s="1"/>
+      <c r="Q394" s="1"/>
+      <c r="R394" s="1"/>
+    </row>
+    <row r="395" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="33"/>
@@ -11714,8 +13468,12 @@
       <c r="L395" s="1"/>
       <c r="M395" s="1"/>
       <c r="N395" s="1"/>
-    </row>
-    <row r="396" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O395" s="33"/>
+      <c r="P395" s="1"/>
+      <c r="Q395" s="1"/>
+      <c r="R395" s="1"/>
+    </row>
+    <row r="396" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="33"/>
@@ -11731,8 +13489,12 @@
       <c r="L396" s="1"/>
       <c r="M396" s="1"/>
       <c r="N396" s="1"/>
-    </row>
-    <row r="397" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O396" s="33"/>
+      <c r="P396" s="1"/>
+      <c r="Q396" s="1"/>
+      <c r="R396" s="1"/>
+    </row>
+    <row r="397" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="33"/>
@@ -11748,8 +13510,12 @@
       <c r="L397" s="1"/>
       <c r="M397" s="1"/>
       <c r="N397" s="1"/>
-    </row>
-    <row r="398" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O397" s="33"/>
+      <c r="P397" s="1"/>
+      <c r="Q397" s="1"/>
+      <c r="R397" s="1"/>
+    </row>
+    <row r="398" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="33"/>
@@ -11765,8 +13531,12 @@
       <c r="L398" s="1"/>
       <c r="M398" s="1"/>
       <c r="N398" s="1"/>
-    </row>
-    <row r="399" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O398" s="33"/>
+      <c r="P398" s="1"/>
+      <c r="Q398" s="1"/>
+      <c r="R398" s="1"/>
+    </row>
+    <row r="399" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="33"/>
@@ -11782,8 +13552,12 @@
       <c r="L399" s="1"/>
       <c r="M399" s="1"/>
       <c r="N399" s="1"/>
-    </row>
-    <row r="400" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O399" s="33"/>
+      <c r="P399" s="1"/>
+      <c r="Q399" s="1"/>
+      <c r="R399" s="1"/>
+    </row>
+    <row r="400" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="33"/>
@@ -11799,6 +13573,10 @@
       <c r="L400" s="1"/>
       <c r="M400" s="1"/>
       <c r="N400" s="1"/>
+      <c r="O400" s="33"/>
+      <c r="P400" s="1"/>
+      <c r="Q400" s="1"/>
+      <c r="R400" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:M400">
@@ -11817,6 +13595,23 @@
       <formula>AND(COUNTA($A5:$C5,$E5:$M5)&gt;0,MOD(N(LOOKUP(2,1/($A$5:$A5&lt;&gt;""),$A$5:$A5)),2)=0,LEFT($F5,1)="→")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="6">
+      <formula>AND(COUNTA($A5:$C5,$E5:$M5)&gt;0,MOD(N(LOOKUP(2,1/($A$5:$A5&lt;&gt;""),$A$5:$A5)),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:R400">
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>AND($A5&lt;&gt;"",$A5&lt;&gt;LOOKUP(2,1/($A$4:$A4&lt;&gt;""),$A$4:$A4))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND(COUNTA($A5:$C5,$E5:$M5)&gt;0,MOD(N(LOOKUP(2,1/($A$5:$A5&lt;&gt;""),$A$5:$A5)),2)=1,LEFT($F5,1)="→")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>AND(COUNTA($A5:$C5,$E5:$M5)&gt;0,MOD(N(LOOKUP(2,1/($A$5:$A5&lt;&gt;""),$A$5:$A5)),2)=1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>AND(COUNTA($A5:$C5,$E5:$M5)&gt;0,MOD(N(LOOKUP(2,1/($A$5:$A5&lt;&gt;""),$A$5:$A5)),2)=0,LEFT($F5,1)="→")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>AND(COUNTA($A5:$C5,$E5:$M5)&gt;0,MOD(N(LOOKUP(2,1/($A$5:$A5&lt;&gt;""),$A$5:$A5)),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11884,7 +13679,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -11898,7 +13693,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -11912,34 +13707,34 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -11947,31 +13742,31 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -11979,31 +13774,31 @@
         <v>7</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -12261,7 +14056,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -12273,16 +14068,16 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>137</v>
@@ -12290,124 +14085,124 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E5" s="15"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E6" s="15"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="E7" s="15"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E8" s="15"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="E9" s="15"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="E10" s="15"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="E11" s="15"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="E12" s="15"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="E13" s="15"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="E14" s="15"/>
     </row>
@@ -12568,7 +14363,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -12578,21 +14373,21 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="B5" s="13"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="B6" s="13"/>
     </row>
@@ -12699,7 +14494,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -12711,39 +14506,39 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>456</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="25"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="25"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="25"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="25"/>
@@ -12857,78 +14652,79 @@
     <col min="6" max="6" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="F5" s="16"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
@@ -13127,6 +14923,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/builder/travel-template.xlsx
+++ b/builder/travel-template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="513">
   <si>
     <t>旅遊網站資料模板</t>
   </si>
@@ -1875,7 +1875,7 @@
     <t>21:40</t>
   </si>
   <si>
-    <t>這裡只要填「這趟專屬」的東西。證件、電子、藥品、盥洗、季節衣物與轉接頭規格，產生時會依出發月份與目的地氣候自動併進「行李清單」，已經填過的不會重複加。</t>
+    <t>這裡只要填「這趟專屬」的東西。證件、電子、藥品、盥洗、季節衣物與轉接頭規格，產生時會依出發月份與目的地氣候自動併進「行李清單」，行李的「分類」請用這五個：證件與錢、電子產品、衣物與鞋、盥洗與藥品、隨身雜物——跟自動補的擺在同一區，萬一重複了一眼就看得到。已經填過的不會重複加，意思相同的也算（例如填了「保暖外套」就不會再補「可穿脫的薄外套」）。「出發前準備」放要做的事，「行李清單」放要帶的東西。</t>
   </si>
   <si>
     <t>清單名稱</t>
@@ -1929,19 +1929,22 @@
     <t>行李清單</t>
   </si>
   <si>
-    <t>個人物品</t>
+    <t>盥洗與藥品</t>
   </si>
   <si>
     <t>隱形眼鏡與藥水</t>
   </si>
   <si>
+    <t>隨身雜物</t>
+  </si>
+  <si>
     <t>眼鏡或備用眼鏡</t>
   </si>
   <si>
     <t>慣用的枕頭套或眼罩</t>
   </si>
   <si>
-    <t>這趟專用</t>
+    <t>衣物與鞋</t>
   </si>
   <si>
     <t>滑雪手套</t>
@@ -3665,87 +3668,123 @@
       </c>
       <c r="D110" s="1"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="1"/>
       <c r="B112" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="1"/>
       <c r="B113" s="13" t="s">
         <v>176</v>
       </c>
       <c r="C113" s="13" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D113" s="1"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="1"/>
       <c r="B114" s="13" t="s">
         <v>178</v>
       </c>
       <c r="C114" s="13" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D114" s="1"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
       <c r="B115" s="13" t="s">
         <v>180</v>
       </c>
       <c r="C115" s="13" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D115" s="1"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
       <c r="B116" s="13" t="s">
         <v>182</v>
       </c>
       <c r="C116" s="13" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D116" s="1"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
       <c r="B117" s="13" t="s">
         <v>184</v>
       </c>
       <c r="C117" s="13" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="D117" s="1"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
       <c r="B119" s="4" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="1"/>
       <c r="B120" s="13" t="s">
         <v>187</v>
       </c>
       <c r="C120" s="13" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D120" s="1"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="1"/>
       <c r="B121" s="13" t="s">
         <v>189</v>
       </c>
       <c r="C121" s="13" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D121" s="1"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="1"/>
       <c r="B122" s="13" t="s">
         <v>191</v>
       </c>
       <c r="C122" s="13" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D122" s="1"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="1"/>
       <c r="B123" s="13" t="s">
         <v>193</v>
       </c>
       <c r="C123" s="13" t="s">
         <v>194</v>
       </c>
+      <c r="D123" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3774,31 +3813,31 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>234</v>
@@ -3806,52 +3845,52 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B5" s="16">
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E5" s="16">
         <v>6250</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B6" s="16">
         <v>3.3</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4397,7 +4436,7 @@
     <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -4414,7 +4453,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" ht="19.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>240</v>
       </c>
@@ -4431,7 +4470,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -14163,10 +14202,10 @@
         <v>460</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E11" s="15"/>
     </row>
@@ -14175,10 +14214,10 @@
         <v>460</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E12" s="15"/>
     </row>
@@ -14187,10 +14226,10 @@
         <v>460</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E13" s="15"/>
     </row>
@@ -14199,10 +14238,10 @@
         <v>460</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E14" s="15"/>
     </row>
@@ -14363,7 +14402,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -14373,21 +14412,21 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B5" s="13"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B6" s="13"/>
     </row>
@@ -14494,7 +14533,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14506,10 +14545,10 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>193</v>
@@ -14517,28 +14556,28 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="25"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="25"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="25"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="25"/>
@@ -14659,13 +14698,13 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>39</v>
@@ -14674,10 +14713,10 @@
         <v>195</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>451</v>
@@ -14685,46 +14724,46 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F5" s="16"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>

--- a/builder/travel-template.xlsx
+++ b/builder/travel-template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="515">
   <si>
     <t>旅遊網站資料模板</t>
   </si>
@@ -870,6 +870,12 @@
   </si>
   <si>
     <t>留空即可，產生時自動查當日牌價。要自己指定就只填數字</t>
+  </si>
+  <si>
+    <t>Google 地圖嵌入金鑰</t>
+  </si>
+  <si>
+    <t>選填。電腦版右側會顯示當天的路線地圖，留空就不顯示。到 Google Cloud 啟用 Maps Embed API（要綁帳單帳戶，但這個 API 不收費），建一把新金鑰並加兩個限制：API 限制只勾 Maps Embed API、網站限制只填自己的網域（例如 heatherchou58.github.io/*）。這把金鑰會公開在網站上，加了限制就沒有風險。</t>
   </si>
   <si>
     <t>記帳分攤時會出現的名單，2～8 人。</t>
@@ -3813,84 +3819,84 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B5" s="16">
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E5" s="16">
         <v>6250</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B6" s="16">
         <v>3.3</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4144,7 +4150,7 @@
   <sheetPr>
     <tabColor rgb="FF1F5C99"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -4326,6 +4332,15 @@
       <c r="B18" s="23"/>
       <c r="C18" s="24" t="s">
         <v>231</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -4360,7 +4375,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -4370,35 +4385,35 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B7" s="24"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B8" s="24"/>
     </row>
@@ -4455,7 +4470,7 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4487,16 +4502,16 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>224</v>
@@ -4505,13 +4520,13 @@
         <v>39</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>93</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>167</v>
@@ -4520,13 +4535,13 @@
         <v>169</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>187</v>
@@ -4546,40 +4561,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C5" s="26">
         <v>20</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>225</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O5" s="26"/>
       <c r="P5" s="15"/>
@@ -4600,15 +4615,15 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
@@ -4630,13 +4645,13 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
@@ -4660,17 +4675,17 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
@@ -4694,15 +4709,15 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
@@ -4724,13 +4739,13 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -4754,13 +4769,13 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -4784,17 +4799,17 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
@@ -4818,25 +4833,25 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N13" s="13" t="s">
         <v>81</v>
@@ -4858,23 +4873,23 @@
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N14" s="13" t="s">
         <v>81</v>
@@ -4889,25 +4904,25 @@
         <v>2</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C15" s="26">
         <v>12</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
@@ -4929,13 +4944,13 @@
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -4959,17 +4974,17 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
@@ -4991,17 +5006,17 @@
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
@@ -5025,26 +5040,26 @@
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>81</v>
@@ -5068,24 +5083,24 @@
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O20" s="26"/>
       <c r="P20" s="13"/>
@@ -5106,24 +5121,24 @@
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N21" s="13" t="s">
         <v>81</v>
@@ -5150,11 +5165,11 @@
         <v>61</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J22" s="13"/>
       <c r="L22" s="13"/>
@@ -5177,21 +5192,21 @@
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="L23" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>81</v>
@@ -5213,21 +5228,21 @@
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="L24" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>81</v>
@@ -5251,25 +5266,25 @@
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N25" s="13" t="s">
         <v>81</v>
@@ -5293,23 +5308,23 @@
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>81</v>
@@ -5331,20 +5346,20 @@
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="28" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="L27" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O27" s="26"/>
       <c r="P27" s="13"/>
@@ -5356,27 +5371,27 @@
         <v>3</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C28" s="26">
         <v>150</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
@@ -5400,25 +5415,25 @@
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>84</v>
@@ -5442,17 +5457,17 @@
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
@@ -5476,15 +5491,15 @@
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
@@ -5508,25 +5523,25 @@
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="I32" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="G32" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>274</v>
-      </c>
       <c r="J32" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N32" s="13" t="s">
         <v>81</v>
@@ -5541,31 +5556,31 @@
         <v>4</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C33" s="26">
         <v>90</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>225</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
@@ -5589,15 +5604,15 @@
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
@@ -5619,13 +5634,13 @@
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
@@ -5649,17 +5664,17 @@
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
@@ -5683,23 +5698,23 @@
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J37" s="13"/>
       <c r="L37" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N37" s="13" t="s">
         <v>81</v>
@@ -5723,19 +5738,19 @@
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
@@ -5757,25 +5772,25 @@
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N39" s="13" t="s">
         <v>75</v>
@@ -5790,35 +5805,35 @@
         <v>5</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C40" s="26">
         <v>75</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N40" s="13" t="s">
         <v>81</v>
@@ -5842,15 +5857,15 @@
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="15" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
@@ -5872,13 +5887,13 @@
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
@@ -5902,17 +5917,17 @@
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L43" s="13"/>
       <c r="M43" s="13"/>
@@ -5936,19 +5951,19 @@
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
@@ -5972,19 +5987,19 @@
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
@@ -5999,35 +6014,35 @@
         <v>6</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C46" s="26">
         <v>180</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N46" s="13" t="s">
         <v>81</v>
@@ -6051,15 +6066,15 @@
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
@@ -6081,13 +6096,13 @@
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
@@ -6111,13 +6126,13 @@
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H49" s="15" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
@@ -6141,17 +6156,17 @@
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
@@ -6175,25 +6190,25 @@
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N51" s="13" t="s">
         <v>81</v>
@@ -6217,17 +6232,17 @@
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
@@ -6242,35 +6257,35 @@
         <v>7</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C53" s="26">
         <v>90</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H53" s="15" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N53" s="13" t="s">
         <v>81</v>
@@ -6294,21 +6309,21 @@
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
       <c r="J54" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N54" s="13" t="s">
         <v>84</v>
@@ -6330,13 +6345,13 @@
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H55" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
@@ -6360,17 +6375,17 @@
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
@@ -6394,17 +6409,17 @@
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
@@ -13718,7 +13733,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -13732,7 +13747,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -13746,34 +13761,34 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13781,31 +13796,31 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13813,31 +13828,31 @@
         <v>7</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="H6" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>440</v>
-      </c>
       <c r="I6" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -14095,7 +14110,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14107,16 +14122,16 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>195</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>137</v>
@@ -14124,124 +14139,124 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E5" s="15"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E6" s="15"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E7" s="15"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E8" s="15"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E9" s="15"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E10" s="15"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E11" s="15"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E12" s="15"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E13" s="15"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E14" s="15"/>
     </row>
@@ -14402,7 +14417,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -14412,21 +14427,21 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B5" s="13"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B6" s="13"/>
     </row>
@@ -14533,7 +14548,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14545,10 +14560,10 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>193</v>
@@ -14556,28 +14571,28 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="25"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="25"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="25"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="25"/>
@@ -14698,13 +14713,13 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>39</v>
@@ -14713,57 +14728,57 @@
         <v>195</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F5" s="16"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>

--- a/builder/travel-template.xlsx
+++ b/builder/travel-template.xlsx
@@ -2065,7 +2065,7 @@
     <t>圖片</t>
   </si>
   <si>
-    <t>折價券</t>
+    <t>優惠券</t>
   </si>
   <si>
     <t>券</t>
@@ -3812,17 +3812,16 @@
     <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>484</v>
@@ -4451,7 +4450,7 @@
     <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -4468,7 +4467,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" ht="19.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>242</v>
       </c>
@@ -4485,7 +4484,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -14101,21 +14100,21 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>450</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -14706,17 +14705,16 @@
     <col min="6" max="6" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>503</v>

--- a/builder/travel-template.xlsx
+++ b/builder/travel-template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="524">
   <si>
     <t>旅遊網站資料模板</t>
   </si>
@@ -680,16 +680,16 @@
     <t>說明／備註</t>
   </si>
   <si>
-    <t>站在門口才需要看的：會卡住的事、要先做的事、備案。卡片上已經有的不要再寫（見最下方「說明／備註 的寫法」）。網站上直接顯示。</t>
+    <t>站在門口才需要看的：怎麼去、幾點前要到、要帶什麼、要先預約、推薦點什麼、會卡住的事、備案。卡片上已經有欄位的不要再寫。網站上直接顯示。</t>
   </si>
   <si>
     <t>介紹</t>
   </si>
   <si>
-    <t>這地方是什麼、為什麼值得看——在家讀完就不用再看的放這裡。網站上收合成「看介紹」，點了才展開，不會把一天的版面拉長。</t>
-  </si>
-  <si>
-    <t>只有景點、餐飲、購物會顯示介紹。填在其他類型上產生器會提醒你。</t>
+    <t>這個地方本身的背景：什麼時候蓋的、為什麼有名、看點在哪——在家讀完就不用再看的放這裡。網站上收合成「看介紹」，點了才展開，不會把一天的版面拉長。</t>
+  </si>
+  <si>
+    <t>只有景點、餐飲、購物會顯示介紹。流程性的項目（取車、還車、退房、接人、轉車、辦理登機）就算掛在餐飲類型上也不要寫介紹。填在其他類型上產生器會提醒你。</t>
   </si>
   <si>
     <t>同一格裡換行，網站上就會分段。</t>
@@ -707,13 +707,13 @@
     <t>判斷方法</t>
   </si>
   <si>
-    <t>站在門口才需要看 → 說明。在家讀完就不用再看 → 介紹。</t>
+    <t>照順序問三個問題。① 卡片上已經有欄位了嗎（時間、停留、交通、地點、營業時間、費用、電話）→ 填那個欄位，說明與介紹都不要寫。② 這句話會改變我在現場的行為嗎（會走錯、買錯、錯過、要先準備）→ 寫說明。③ 剩下的是「這個地方本身」的背景嗎 → 寫介紹；如果是在講整趟旅行或某個國家的通則（靠左行駛、要帶現金、山路彎多），兩邊都不寫，那些屬於行前分頁。</t>
   </si>
   <si>
     <t>一、卡片上有的不要寫</t>
   </si>
   <si>
-    <t>時間、停留、交通、地點、營業時間、費用、電話都有自己的欄位，網站會顯示。說明裡再寫一次就是重複。</t>
+    <t>時間、停留、交通、地點、營業時間、費用、電話都有自己的欄位，網站會顯示。說明裡再寫一次就是重複。同一件事也不能說明與介紹各寫一遍，撞到時留說明、刪介紹。</t>
   </si>
   <si>
     <t>二、一行一件事</t>
@@ -759,6 +759,33 @@
   </si>
   <si>
     <t>只填號碼，網站上點了就能直接撥。</t>
+  </si>
+  <si>
+    <t>介紹 的寫法</t>
+  </si>
+  <si>
+    <t>一、只給會停下來的地方</t>
+  </si>
+  <si>
+    <t>取車、還車、退房、接人、轉車、辦理登機不寫。只是拿了就走的店也不寫——買個麵包上車吃，說明寫「推薦點什麼」就夠了。</t>
+  </si>
+  <si>
+    <t>二、只寫這個地方本身</t>
+  </si>
+  <si>
+    <t>不要寫整趟旅行的安排，也不要寫某個國家的通則（靠左行駛、收費站只收現金、山路彎多）。那些是行前要知道的，放行前分頁。</t>
+  </si>
+  <si>
+    <t>三、不寫會過期的</t>
+  </si>
+  <si>
+    <t>價格、營業時間、公休日不要寫進介紹——它們有自己的欄位，而且會變。季節性的現象（紅葉、雲海、光之道）要寫成不會過期的說法，例如「出發前查官方情報」。</t>
+  </si>
+  <si>
+    <t>四、2～4 句就好</t>
+  </si>
+  <si>
+    <t>約 100～250 字。同一格裡換行，網站上就會分段。沒把握的數字（幾座燈籠、哪一年）查不到就不要寫。</t>
   </si>
   <si>
     <t>項目</t>
@@ -2630,7 +2657,7 @@
   <sheetPr>
     <tabColor rgb="FF154570"/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
@@ -3791,6 +3818,43 @@
         <v>194</v>
       </c>
       <c r="D123" s="1"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>203</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3819,83 +3883,83 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B5" s="16">
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E5" s="16">
         <v>6250</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B6" s="16">
         <v>3.3</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4171,46 +4235,46 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4218,101 +4282,101 @@
         <v>112</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="24" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="24" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="24" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="24" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4321,7 +4385,7 @@
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4330,16 +4394,16 @@
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="24" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B19" s="23"/>
       <c r="C19" s="24" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4374,7 +4438,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -4384,35 +4448,35 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B7" s="24"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B8" s="24"/>
     </row>
@@ -4469,7 +4533,7 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4501,31 +4565,31 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>39</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>93</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>167</v>
@@ -4534,13 +4598,13 @@
         <v>169</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>187</v>
@@ -4560,40 +4624,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C5" s="26">
         <v>20</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="O5" s="26"/>
       <c r="P5" s="15"/>
@@ -4614,15 +4678,15 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
@@ -4644,13 +4708,13 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
@@ -4674,17 +4738,17 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
@@ -4708,15 +4772,15 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
@@ -4738,13 +4802,13 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -4768,13 +4832,13 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="28" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -4798,17 +4862,17 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
@@ -4832,25 +4896,25 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="28" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="N13" s="13" t="s">
         <v>81</v>
@@ -4872,23 +4936,23 @@
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="28" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="15" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="N14" s="13" t="s">
         <v>81</v>
@@ -4903,25 +4967,25 @@
         <v>2</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C15" s="26">
         <v>12</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
@@ -4943,13 +5007,13 @@
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -4973,17 +5037,17 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="28" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="15" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
@@ -5005,17 +5069,17 @@
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
@@ -5039,26 +5103,26 @@
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="28" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="15" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>81</v>
@@ -5082,24 +5146,24 @@
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="O20" s="26"/>
       <c r="P20" s="13"/>
@@ -5120,24 +5184,24 @@
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="15" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N21" s="13" t="s">
         <v>81</v>
@@ -5164,11 +5228,11 @@
         <v>61</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="15" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="J22" s="13"/>
       <c r="L22" s="13"/>
@@ -5191,21 +5255,21 @@
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="28" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="L23" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>81</v>
@@ -5227,21 +5291,21 @@
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="28" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="L24" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>81</v>
@@ -5265,25 +5329,25 @@
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="28" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="N25" s="13" t="s">
         <v>81</v>
@@ -5307,23 +5371,23 @@
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="15" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>81</v>
@@ -5345,20 +5409,20 @@
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="28" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="L27" s="15" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="O27" s="26"/>
       <c r="P27" s="13"/>
@@ -5370,27 +5434,27 @@
         <v>3</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C28" s="26">
         <v>150</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="15" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
@@ -5414,25 +5478,25 @@
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>84</v>
@@ -5456,17 +5520,17 @@
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="28" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="15" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
@@ -5490,15 +5554,15 @@
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="15" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
@@ -5522,25 +5586,25 @@
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="28" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="N32" s="13" t="s">
         <v>81</v>
@@ -5555,31 +5619,31 @@
         <v>4</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C33" s="26">
         <v>90</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
@@ -5603,15 +5667,15 @@
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
@@ -5633,13 +5697,13 @@
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
@@ -5663,17 +5727,17 @@
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
@@ -5697,23 +5761,23 @@
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="28" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="J37" s="13"/>
       <c r="L37" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="N37" s="13" t="s">
         <v>81</v>
@@ -5737,19 +5801,19 @@
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="28" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
@@ -5771,25 +5835,25 @@
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="28" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="G39" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="H39" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>363</v>
-      </c>
       <c r="J39" s="13" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="N39" s="13" t="s">
         <v>75</v>
@@ -5804,35 +5868,35 @@
         <v>5</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C40" s="26">
         <v>75</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="28" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="N40" s="13" t="s">
         <v>81</v>
@@ -5856,15 +5920,15 @@
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="15" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
@@ -5886,13 +5950,13 @@
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
@@ -5916,17 +5980,17 @@
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="L43" s="13"/>
       <c r="M43" s="13"/>
@@ -5950,19 +6014,19 @@
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
@@ -5986,19 +6050,19 @@
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="28" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
@@ -6013,35 +6077,35 @@
         <v>6</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C46" s="26">
         <v>180</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="28" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="N46" s="13" t="s">
         <v>81</v>
@@ -6065,15 +6129,15 @@
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="13" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
@@ -6095,13 +6159,13 @@
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
@@ -6125,13 +6189,13 @@
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="28" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="H49" s="15" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
@@ -6155,17 +6219,17 @@
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
@@ -6189,25 +6253,25 @@
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="28" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="N51" s="13" t="s">
         <v>81</v>
@@ -6231,17 +6295,17 @@
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="15" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
@@ -6256,35 +6320,35 @@
         <v>7</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C53" s="26">
         <v>90</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="28" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="H53" s="15" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="N53" s="13" t="s">
         <v>81</v>
@@ -6308,21 +6372,21 @@
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="28" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
       <c r="J54" s="13" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="N54" s="13" t="s">
         <v>84</v>
@@ -6344,13 +6408,13 @@
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="H55" s="15" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
@@ -6374,17 +6438,17 @@
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
@@ -6408,17 +6472,17 @@
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="28" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="15" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
@@ -13732,7 +13796,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -13746,7 +13810,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -13760,34 +13824,34 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13795,31 +13859,31 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13827,31 +13891,31 @@
         <v>7</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -14109,7 +14173,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14121,16 +14185,16 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>137</v>
@@ -14138,124 +14202,124 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E5" s="15"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E6" s="15"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="E7" s="15"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="E8" s="15"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="E9" s="15"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="E10" s="15"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="E11" s="15"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="E12" s="15"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="E13" s="15"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="E14" s="15"/>
     </row>
@@ -14416,7 +14480,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -14426,21 +14490,21 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="B5" s="13"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="B6" s="13"/>
     </row>
@@ -14547,7 +14611,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14559,10 +14623,10 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>193</v>
@@ -14570,28 +14634,28 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="25"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="25"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="25"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="25"/>
@@ -14712,71 +14776,71 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="F5" s="16"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
